--- a/BRISAS/EXPENSAS/2026/MARZO/BRISAS-MARZO.xlsx
+++ b/BRISAS/EXPENSAS/2026/MARZO/BRISAS-MARZO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\MARZO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847FEF85-19BB-4671-BC15-71D599B31DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6815EA7-4CE5-477B-B6E9-DEF4657F849D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="518">
   <si>
     <t>Dpto.</t>
   </si>
@@ -1615,6 +1615,15 @@
   </si>
   <si>
     <t>El imperio RYL - Articulos de limpieza - Fc. 0000012597</t>
+  </si>
+  <si>
+    <t>El lote 71 hizo dos depositos : $1.392.000 y $592.000 el dia 30/03</t>
+  </si>
+  <si>
+    <t>El lote 109 deposito : $780.000 el dia 30/03</t>
+  </si>
+  <si>
+    <t>Transfirio $700.000 el dia 30/03</t>
   </si>
 </sst>
 </file>
@@ -3175,6 +3184,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3201,12 +3216,6 @@
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11113,11 +11122,11 @@
     </row>
     <row r="76" spans="1:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="16"/>
-      <c r="B76" s="16">
+      <c r="B76" s="181">
         <f t="shared" si="29"/>
         <v>71</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C76" s="181" t="s">
         <v>89</v>
       </c>
       <c r="D76" s="80">
@@ -12791,11 +12800,11 @@
     </row>
     <row r="100" spans="1:22" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="16"/>
-      <c r="B100" s="16">
+      <c r="B100" s="181">
         <f t="shared" si="29"/>
         <v>95</v>
       </c>
-      <c r="C100" s="16" t="s">
+      <c r="C100" s="181" t="s">
         <v>105</v>
       </c>
       <c r="D100" s="80">
@@ -13758,11 +13767,11 @@
     </row>
     <row r="114" spans="1:25" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="181"/>
-      <c r="B114" s="16">
+      <c r="B114" s="181">
         <f t="shared" si="29"/>
         <v>109</v>
       </c>
-      <c r="C114" s="16" t="s">
+      <c r="C114" s="181" t="s">
         <v>118</v>
       </c>
       <c r="D114" s="80">
@@ -17157,7 +17166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D69DBA-AA88-413A-80A7-A9BAAE7F2C32}">
-  <dimension ref="C2:N234"/>
+  <dimension ref="C2:N261"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="10.88671875" customWidth="1"/>
@@ -17251,16 +17260,16 @@
       <c r="N6" s="440"/>
     </row>
     <row r="7" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C7" s="428" t="s">
+      <c r="C7" s="430" t="s">
         <v>320</v>
       </c>
-      <c r="D7" s="429"/>
-      <c r="E7" s="429"/>
-      <c r="F7" s="429"/>
-      <c r="G7" s="429"/>
-      <c r="H7" s="429"/>
-      <c r="I7" s="429"/>
-      <c r="J7" s="430"/>
+      <c r="D7" s="431"/>
+      <c r="E7" s="431"/>
+      <c r="F7" s="431"/>
+      <c r="G7" s="431"/>
+      <c r="H7" s="431"/>
+      <c r="I7" s="431"/>
+      <c r="J7" s="432"/>
       <c r="K7" s="441" t="s">
         <v>336</v>
       </c>
@@ -17269,28 +17278,28 @@
       <c r="N7" s="442"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C8" s="431"/>
-      <c r="D8" s="432"/>
-      <c r="E8" s="432"/>
-      <c r="F8" s="432"/>
-      <c r="G8" s="432"/>
-      <c r="H8" s="432"/>
-      <c r="I8" s="432"/>
-      <c r="J8" s="433"/>
+      <c r="C8" s="433"/>
+      <c r="D8" s="434"/>
+      <c r="E8" s="434"/>
+      <c r="F8" s="434"/>
+      <c r="G8" s="434"/>
+      <c r="H8" s="434"/>
+      <c r="I8" s="434"/>
+      <c r="J8" s="435"/>
       <c r="K8" s="441"/>
       <c r="L8" s="442"/>
       <c r="M8" s="442"/>
       <c r="N8" s="442"/>
     </row>
     <row r="9" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="434"/>
-      <c r="D9" s="435"/>
-      <c r="E9" s="435"/>
-      <c r="F9" s="435"/>
-      <c r="G9" s="435"/>
-      <c r="H9" s="435"/>
-      <c r="I9" s="435"/>
-      <c r="J9" s="436"/>
+      <c r="C9" s="436"/>
+      <c r="D9" s="437"/>
+      <c r="E9" s="437"/>
+      <c r="F9" s="437"/>
+      <c r="G9" s="437"/>
+      <c r="H9" s="437"/>
+      <c r="I9" s="437"/>
+      <c r="J9" s="438"/>
       <c r="K9" s="441"/>
       <c r="L9" s="442"/>
       <c r="M9" s="442"/>
@@ -17361,36 +17370,36 @@
       <c r="J15" s="69"/>
     </row>
     <row r="16" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C16" s="428" t="s">
+      <c r="C16" s="430" t="s">
         <v>421</v>
       </c>
-      <c r="D16" s="429"/>
-      <c r="E16" s="429"/>
-      <c r="F16" s="429"/>
-      <c r="G16" s="429"/>
-      <c r="H16" s="429"/>
-      <c r="I16" s="429"/>
-      <c r="J16" s="430"/>
+      <c r="D16" s="431"/>
+      <c r="E16" s="431"/>
+      <c r="F16" s="431"/>
+      <c r="G16" s="431"/>
+      <c r="H16" s="431"/>
+      <c r="I16" s="431"/>
+      <c r="J16" s="432"/>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C17" s="431"/>
-      <c r="D17" s="432"/>
-      <c r="E17" s="432"/>
-      <c r="F17" s="432"/>
-      <c r="G17" s="432"/>
-      <c r="H17" s="432"/>
-      <c r="I17" s="432"/>
-      <c r="J17" s="433"/>
+      <c r="C17" s="433"/>
+      <c r="D17" s="434"/>
+      <c r="E17" s="434"/>
+      <c r="F17" s="434"/>
+      <c r="G17" s="434"/>
+      <c r="H17" s="434"/>
+      <c r="I17" s="434"/>
+      <c r="J17" s="435"/>
     </row>
     <row r="18" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18" s="434"/>
-      <c r="D18" s="435"/>
-      <c r="E18" s="435"/>
-      <c r="F18" s="435"/>
-      <c r="G18" s="435"/>
-      <c r="H18" s="435"/>
-      <c r="I18" s="435"/>
-      <c r="J18" s="436"/>
+      <c r="C18" s="436"/>
+      <c r="D18" s="437"/>
+      <c r="E18" s="437"/>
+      <c r="F18" s="437"/>
+      <c r="G18" s="437"/>
+      <c r="H18" s="437"/>
+      <c r="I18" s="437"/>
+      <c r="J18" s="438"/>
     </row>
     <row r="20" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="3:10" x14ac:dyDescent="0.3">
@@ -17457,36 +17466,36 @@
       <c r="J24" s="69"/>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C25" s="428" t="s">
+      <c r="C25" s="430" t="s">
         <v>422</v>
       </c>
-      <c r="D25" s="429"/>
-      <c r="E25" s="429"/>
-      <c r="F25" s="429"/>
-      <c r="G25" s="429"/>
-      <c r="H25" s="429"/>
-      <c r="I25" s="429"/>
-      <c r="J25" s="430"/>
+      <c r="D25" s="431"/>
+      <c r="E25" s="431"/>
+      <c r="F25" s="431"/>
+      <c r="G25" s="431"/>
+      <c r="H25" s="431"/>
+      <c r="I25" s="431"/>
+      <c r="J25" s="432"/>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="431"/>
-      <c r="D26" s="432"/>
-      <c r="E26" s="432"/>
-      <c r="F26" s="432"/>
-      <c r="G26" s="432"/>
-      <c r="H26" s="432"/>
-      <c r="I26" s="432"/>
-      <c r="J26" s="433"/>
+      <c r="C26" s="433"/>
+      <c r="D26" s="434"/>
+      <c r="E26" s="434"/>
+      <c r="F26" s="434"/>
+      <c r="G26" s="434"/>
+      <c r="H26" s="434"/>
+      <c r="I26" s="434"/>
+      <c r="J26" s="435"/>
     </row>
     <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C27" s="434"/>
-      <c r="D27" s="435"/>
-      <c r="E27" s="435"/>
-      <c r="F27" s="435"/>
-      <c r="G27" s="435"/>
-      <c r="H27" s="435"/>
-      <c r="I27" s="435"/>
-      <c r="J27" s="436"/>
+      <c r="C27" s="436"/>
+      <c r="D27" s="437"/>
+      <c r="E27" s="437"/>
+      <c r="F27" s="437"/>
+      <c r="G27" s="437"/>
+      <c r="H27" s="437"/>
+      <c r="I27" s="437"/>
+      <c r="J27" s="438"/>
     </row>
     <row r="29" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="3:10" x14ac:dyDescent="0.3">
@@ -17536,11 +17545,11 @@
       <c r="G32" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H32" s="437" t="s">
+      <c r="H32" s="428" t="s">
         <v>425</v>
       </c>
-      <c r="I32" s="437"/>
-      <c r="J32" s="438"/>
+      <c r="I32" s="428"/>
+      <c r="J32" s="429"/>
     </row>
     <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="260" t="s">
@@ -17555,36 +17564,36 @@
       <c r="J33" s="69"/>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C34" s="428" t="s">
+      <c r="C34" s="430" t="s">
         <v>424</v>
       </c>
-      <c r="D34" s="429"/>
-      <c r="E34" s="429"/>
-      <c r="F34" s="429"/>
-      <c r="G34" s="429"/>
-      <c r="H34" s="429"/>
-      <c r="I34" s="429"/>
-      <c r="J34" s="430"/>
+      <c r="D34" s="431"/>
+      <c r="E34" s="431"/>
+      <c r="F34" s="431"/>
+      <c r="G34" s="431"/>
+      <c r="H34" s="431"/>
+      <c r="I34" s="431"/>
+      <c r="J34" s="432"/>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C35" s="431"/>
-      <c r="D35" s="432"/>
-      <c r="E35" s="432"/>
-      <c r="F35" s="432"/>
-      <c r="G35" s="432"/>
-      <c r="H35" s="432"/>
-      <c r="I35" s="432"/>
-      <c r="J35" s="433"/>
+      <c r="C35" s="433"/>
+      <c r="D35" s="434"/>
+      <c r="E35" s="434"/>
+      <c r="F35" s="434"/>
+      <c r="G35" s="434"/>
+      <c r="H35" s="434"/>
+      <c r="I35" s="434"/>
+      <c r="J35" s="435"/>
     </row>
     <row r="36" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="434"/>
-      <c r="D36" s="435"/>
-      <c r="E36" s="435"/>
-      <c r="F36" s="435"/>
-      <c r="G36" s="435"/>
-      <c r="H36" s="435"/>
-      <c r="I36" s="435"/>
-      <c r="J36" s="436"/>
+      <c r="C36" s="436"/>
+      <c r="D36" s="437"/>
+      <c r="E36" s="437"/>
+      <c r="F36" s="437"/>
+      <c r="G36" s="437"/>
+      <c r="H36" s="437"/>
+      <c r="I36" s="437"/>
+      <c r="J36" s="438"/>
     </row>
     <row r="38" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="3:10" x14ac:dyDescent="0.3">
@@ -17634,11 +17643,11 @@
       <c r="G41" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H41" s="437">
+      <c r="H41" s="428">
         <v>146</v>
       </c>
-      <c r="I41" s="437"/>
-      <c r="J41" s="438"/>
+      <c r="I41" s="428"/>
+      <c r="J41" s="429"/>
     </row>
     <row r="42" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C42" s="295" t="s">
@@ -17653,36 +17662,36 @@
       <c r="J42" s="69"/>
     </row>
     <row r="43" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C43" s="428" t="s">
+      <c r="C43" s="430" t="s">
         <v>427</v>
       </c>
-      <c r="D43" s="429"/>
-      <c r="E43" s="429"/>
-      <c r="F43" s="429"/>
-      <c r="G43" s="429"/>
-      <c r="H43" s="429"/>
-      <c r="I43" s="429"/>
-      <c r="J43" s="430"/>
+      <c r="D43" s="431"/>
+      <c r="E43" s="431"/>
+      <c r="F43" s="431"/>
+      <c r="G43" s="431"/>
+      <c r="H43" s="431"/>
+      <c r="I43" s="431"/>
+      <c r="J43" s="432"/>
     </row>
     <row r="44" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C44" s="431"/>
-      <c r="D44" s="432"/>
-      <c r="E44" s="432"/>
-      <c r="F44" s="432"/>
-      <c r="G44" s="432"/>
-      <c r="H44" s="432"/>
-      <c r="I44" s="432"/>
-      <c r="J44" s="433"/>
+      <c r="C44" s="433"/>
+      <c r="D44" s="434"/>
+      <c r="E44" s="434"/>
+      <c r="F44" s="434"/>
+      <c r="G44" s="434"/>
+      <c r="H44" s="434"/>
+      <c r="I44" s="434"/>
+      <c r="J44" s="435"/>
     </row>
     <row r="45" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C45" s="434"/>
-      <c r="D45" s="435"/>
-      <c r="E45" s="435"/>
-      <c r="F45" s="435"/>
-      <c r="G45" s="435"/>
-      <c r="H45" s="435"/>
-      <c r="I45" s="435"/>
-      <c r="J45" s="436"/>
+      <c r="C45" s="436"/>
+      <c r="D45" s="437"/>
+      <c r="E45" s="437"/>
+      <c r="F45" s="437"/>
+      <c r="G45" s="437"/>
+      <c r="H45" s="437"/>
+      <c r="I45" s="437"/>
+      <c r="J45" s="438"/>
     </row>
     <row r="47" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="48" spans="3:10" x14ac:dyDescent="0.3">
@@ -17732,11 +17741,11 @@
       <c r="G50" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H50" s="437">
+      <c r="H50" s="428">
         <v>14</v>
       </c>
-      <c r="I50" s="437"/>
-      <c r="J50" s="438"/>
+      <c r="I50" s="428"/>
+      <c r="J50" s="429"/>
     </row>
     <row r="51" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="300" t="s">
@@ -17751,36 +17760,36 @@
       <c r="J51" s="69"/>
     </row>
     <row r="52" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C52" s="428" t="s">
+      <c r="C52" s="430" t="s">
         <v>429</v>
       </c>
-      <c r="D52" s="429"/>
-      <c r="E52" s="429"/>
-      <c r="F52" s="429"/>
-      <c r="G52" s="429"/>
-      <c r="H52" s="429"/>
-      <c r="I52" s="429"/>
-      <c r="J52" s="430"/>
+      <c r="D52" s="431"/>
+      <c r="E52" s="431"/>
+      <c r="F52" s="431"/>
+      <c r="G52" s="431"/>
+      <c r="H52" s="431"/>
+      <c r="I52" s="431"/>
+      <c r="J52" s="432"/>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C53" s="431"/>
-      <c r="D53" s="432"/>
-      <c r="E53" s="432"/>
-      <c r="F53" s="432"/>
-      <c r="G53" s="432"/>
-      <c r="H53" s="432"/>
-      <c r="I53" s="432"/>
-      <c r="J53" s="433"/>
+      <c r="C53" s="433"/>
+      <c r="D53" s="434"/>
+      <c r="E53" s="434"/>
+      <c r="F53" s="434"/>
+      <c r="G53" s="434"/>
+      <c r="H53" s="434"/>
+      <c r="I53" s="434"/>
+      <c r="J53" s="435"/>
     </row>
     <row r="54" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C54" s="434"/>
-      <c r="D54" s="435"/>
-      <c r="E54" s="435"/>
-      <c r="F54" s="435"/>
-      <c r="G54" s="435"/>
-      <c r="H54" s="435"/>
-      <c r="I54" s="435"/>
-      <c r="J54" s="436"/>
+      <c r="C54" s="436"/>
+      <c r="D54" s="437"/>
+      <c r="E54" s="437"/>
+      <c r="F54" s="437"/>
+      <c r="G54" s="437"/>
+      <c r="H54" s="437"/>
+      <c r="I54" s="437"/>
+      <c r="J54" s="438"/>
     </row>
     <row r="56" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="3:10" x14ac:dyDescent="0.3">
@@ -17828,11 +17837,11 @@
       <c r="G59" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H59" s="437">
+      <c r="H59" s="428">
         <v>53</v>
       </c>
-      <c r="I59" s="437"/>
-      <c r="J59" s="438"/>
+      <c r="I59" s="428"/>
+      <c r="J59" s="429"/>
     </row>
     <row r="60" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C60" s="304" t="s">
@@ -17847,36 +17856,36 @@
       <c r="J60" s="69"/>
     </row>
     <row r="61" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C61" s="428" t="s">
+      <c r="C61" s="430" t="s">
         <v>431</v>
       </c>
-      <c r="D61" s="429"/>
-      <c r="E61" s="429"/>
-      <c r="F61" s="429"/>
-      <c r="G61" s="429"/>
-      <c r="H61" s="429"/>
-      <c r="I61" s="429"/>
-      <c r="J61" s="430"/>
+      <c r="D61" s="431"/>
+      <c r="E61" s="431"/>
+      <c r="F61" s="431"/>
+      <c r="G61" s="431"/>
+      <c r="H61" s="431"/>
+      <c r="I61" s="431"/>
+      <c r="J61" s="432"/>
     </row>
     <row r="62" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C62" s="431"/>
-      <c r="D62" s="432"/>
-      <c r="E62" s="432"/>
-      <c r="F62" s="432"/>
-      <c r="G62" s="432"/>
-      <c r="H62" s="432"/>
-      <c r="I62" s="432"/>
-      <c r="J62" s="433"/>
+      <c r="C62" s="433"/>
+      <c r="D62" s="434"/>
+      <c r="E62" s="434"/>
+      <c r="F62" s="434"/>
+      <c r="G62" s="434"/>
+      <c r="H62" s="434"/>
+      <c r="I62" s="434"/>
+      <c r="J62" s="435"/>
     </row>
     <row r="63" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C63" s="434"/>
-      <c r="D63" s="435"/>
-      <c r="E63" s="435"/>
-      <c r="F63" s="435"/>
-      <c r="G63" s="435"/>
-      <c r="H63" s="435"/>
-      <c r="I63" s="435"/>
-      <c r="J63" s="436"/>
+      <c r="C63" s="436"/>
+      <c r="D63" s="437"/>
+      <c r="E63" s="437"/>
+      <c r="F63" s="437"/>
+      <c r="G63" s="437"/>
+      <c r="H63" s="437"/>
+      <c r="I63" s="437"/>
+      <c r="J63" s="438"/>
     </row>
     <row r="65" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="66" spans="3:10" x14ac:dyDescent="0.3">
@@ -17926,11 +17935,11 @@
       <c r="G68" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H68" s="437" t="s">
+      <c r="H68" s="428" t="s">
         <v>433</v>
       </c>
-      <c r="I68" s="437"/>
-      <c r="J68" s="438"/>
+      <c r="I68" s="428"/>
+      <c r="J68" s="429"/>
     </row>
     <row r="69" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C69" s="308" t="s">
@@ -17945,36 +17954,36 @@
       <c r="J69" s="69"/>
     </row>
     <row r="70" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C70" s="428" t="s">
+      <c r="C70" s="430" t="s">
         <v>434</v>
       </c>
-      <c r="D70" s="429"/>
-      <c r="E70" s="429"/>
-      <c r="F70" s="429"/>
-      <c r="G70" s="429"/>
-      <c r="H70" s="429"/>
-      <c r="I70" s="429"/>
-      <c r="J70" s="430"/>
+      <c r="D70" s="431"/>
+      <c r="E70" s="431"/>
+      <c r="F70" s="431"/>
+      <c r="G70" s="431"/>
+      <c r="H70" s="431"/>
+      <c r="I70" s="431"/>
+      <c r="J70" s="432"/>
     </row>
     <row r="71" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C71" s="431"/>
-      <c r="D71" s="432"/>
-      <c r="E71" s="432"/>
-      <c r="F71" s="432"/>
-      <c r="G71" s="432"/>
-      <c r="H71" s="432"/>
-      <c r="I71" s="432"/>
-      <c r="J71" s="433"/>
+      <c r="C71" s="433"/>
+      <c r="D71" s="434"/>
+      <c r="E71" s="434"/>
+      <c r="F71" s="434"/>
+      <c r="G71" s="434"/>
+      <c r="H71" s="434"/>
+      <c r="I71" s="434"/>
+      <c r="J71" s="435"/>
     </row>
     <row r="72" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="434"/>
-      <c r="D72" s="435"/>
-      <c r="E72" s="435"/>
-      <c r="F72" s="435"/>
-      <c r="G72" s="435"/>
-      <c r="H72" s="435"/>
-      <c r="I72" s="435"/>
-      <c r="J72" s="436"/>
+      <c r="C72" s="436"/>
+      <c r="D72" s="437"/>
+      <c r="E72" s="437"/>
+      <c r="F72" s="437"/>
+      <c r="G72" s="437"/>
+      <c r="H72" s="437"/>
+      <c r="I72" s="437"/>
+      <c r="J72" s="438"/>
     </row>
     <row r="74" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="75" spans="3:10" x14ac:dyDescent="0.3">
@@ -18022,11 +18031,11 @@
       <c r="G77" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H77" s="437">
+      <c r="H77" s="428">
         <v>78</v>
       </c>
-      <c r="I77" s="437"/>
-      <c r="J77" s="438"/>
+      <c r="I77" s="428"/>
+      <c r="J77" s="429"/>
     </row>
     <row r="78" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C78" s="313" t="s">
@@ -18041,36 +18050,36 @@
       <c r="J78" s="69"/>
     </row>
     <row r="79" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C79" s="428" t="s">
+      <c r="C79" s="430" t="s">
         <v>435</v>
       </c>
-      <c r="D79" s="429"/>
-      <c r="E79" s="429"/>
-      <c r="F79" s="429"/>
-      <c r="G79" s="429"/>
-      <c r="H79" s="429"/>
-      <c r="I79" s="429"/>
-      <c r="J79" s="430"/>
+      <c r="D79" s="431"/>
+      <c r="E79" s="431"/>
+      <c r="F79" s="431"/>
+      <c r="G79" s="431"/>
+      <c r="H79" s="431"/>
+      <c r="I79" s="431"/>
+      <c r="J79" s="432"/>
     </row>
     <row r="80" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C80" s="431"/>
-      <c r="D80" s="432"/>
-      <c r="E80" s="432"/>
-      <c r="F80" s="432"/>
-      <c r="G80" s="432"/>
-      <c r="H80" s="432"/>
-      <c r="I80" s="432"/>
-      <c r="J80" s="433"/>
+      <c r="C80" s="433"/>
+      <c r="D80" s="434"/>
+      <c r="E80" s="434"/>
+      <c r="F80" s="434"/>
+      <c r="G80" s="434"/>
+      <c r="H80" s="434"/>
+      <c r="I80" s="434"/>
+      <c r="J80" s="435"/>
     </row>
     <row r="81" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C81" s="434"/>
-      <c r="D81" s="435"/>
-      <c r="E81" s="435"/>
-      <c r="F81" s="435"/>
-      <c r="G81" s="435"/>
-      <c r="H81" s="435"/>
-      <c r="I81" s="435"/>
-      <c r="J81" s="436"/>
+      <c r="C81" s="436"/>
+      <c r="D81" s="437"/>
+      <c r="E81" s="437"/>
+      <c r="F81" s="437"/>
+      <c r="G81" s="437"/>
+      <c r="H81" s="437"/>
+      <c r="I81" s="437"/>
+      <c r="J81" s="438"/>
     </row>
     <row r="83" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="84" spans="3:10" x14ac:dyDescent="0.3">
@@ -18118,11 +18127,11 @@
       <c r="G86" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H86" s="437">
+      <c r="H86" s="428">
         <v>59</v>
       </c>
-      <c r="I86" s="437"/>
-      <c r="J86" s="438"/>
+      <c r="I86" s="428"/>
+      <c r="J86" s="429"/>
     </row>
     <row r="87" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C87" s="318" t="s">
@@ -18137,36 +18146,36 @@
       <c r="J87" s="69"/>
     </row>
     <row r="88" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C88" s="428" t="s">
+      <c r="C88" s="430" t="s">
         <v>436</v>
       </c>
-      <c r="D88" s="429"/>
-      <c r="E88" s="429"/>
-      <c r="F88" s="429"/>
-      <c r="G88" s="429"/>
-      <c r="H88" s="429"/>
-      <c r="I88" s="429"/>
-      <c r="J88" s="430"/>
+      <c r="D88" s="431"/>
+      <c r="E88" s="431"/>
+      <c r="F88" s="431"/>
+      <c r="G88" s="431"/>
+      <c r="H88" s="431"/>
+      <c r="I88" s="431"/>
+      <c r="J88" s="432"/>
     </row>
     <row r="89" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C89" s="431"/>
-      <c r="D89" s="432"/>
-      <c r="E89" s="432"/>
-      <c r="F89" s="432"/>
-      <c r="G89" s="432"/>
-      <c r="H89" s="432"/>
-      <c r="I89" s="432"/>
-      <c r="J89" s="433"/>
+      <c r="C89" s="433"/>
+      <c r="D89" s="434"/>
+      <c r="E89" s="434"/>
+      <c r="F89" s="434"/>
+      <c r="G89" s="434"/>
+      <c r="H89" s="434"/>
+      <c r="I89" s="434"/>
+      <c r="J89" s="435"/>
     </row>
     <row r="90" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C90" s="434"/>
-      <c r="D90" s="435"/>
-      <c r="E90" s="435"/>
-      <c r="F90" s="435"/>
-      <c r="G90" s="435"/>
-      <c r="H90" s="435"/>
-      <c r="I90" s="435"/>
-      <c r="J90" s="436"/>
+      <c r="C90" s="436"/>
+      <c r="D90" s="437"/>
+      <c r="E90" s="437"/>
+      <c r="F90" s="437"/>
+      <c r="G90" s="437"/>
+      <c r="H90" s="437"/>
+      <c r="I90" s="437"/>
+      <c r="J90" s="438"/>
     </row>
     <row r="92" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="93" spans="3:10" x14ac:dyDescent="0.3">
@@ -18214,11 +18223,11 @@
       <c r="G95" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H95" s="437">
+      <c r="H95" s="428">
         <v>112</v>
       </c>
-      <c r="I95" s="437"/>
-      <c r="J95" s="438"/>
+      <c r="I95" s="428"/>
+      <c r="J95" s="429"/>
     </row>
     <row r="96" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C96" s="322" t="s">
@@ -18233,36 +18242,36 @@
       <c r="J96" s="69"/>
     </row>
     <row r="97" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C97" s="428" t="s">
+      <c r="C97" s="430" t="s">
         <v>437</v>
       </c>
-      <c r="D97" s="429"/>
-      <c r="E97" s="429"/>
-      <c r="F97" s="429"/>
-      <c r="G97" s="429"/>
-      <c r="H97" s="429"/>
-      <c r="I97" s="429"/>
-      <c r="J97" s="430"/>
+      <c r="D97" s="431"/>
+      <c r="E97" s="431"/>
+      <c r="F97" s="431"/>
+      <c r="G97" s="431"/>
+      <c r="H97" s="431"/>
+      <c r="I97" s="431"/>
+      <c r="J97" s="432"/>
     </row>
     <row r="98" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C98" s="431"/>
-      <c r="D98" s="432"/>
-      <c r="E98" s="432"/>
-      <c r="F98" s="432"/>
-      <c r="G98" s="432"/>
-      <c r="H98" s="432"/>
-      <c r="I98" s="432"/>
-      <c r="J98" s="433"/>
+      <c r="C98" s="433"/>
+      <c r="D98" s="434"/>
+      <c r="E98" s="434"/>
+      <c r="F98" s="434"/>
+      <c r="G98" s="434"/>
+      <c r="H98" s="434"/>
+      <c r="I98" s="434"/>
+      <c r="J98" s="435"/>
     </row>
     <row r="99" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="434"/>
-      <c r="D99" s="435"/>
-      <c r="E99" s="435"/>
-      <c r="F99" s="435"/>
-      <c r="G99" s="435"/>
-      <c r="H99" s="435"/>
-      <c r="I99" s="435"/>
-      <c r="J99" s="436"/>
+      <c r="C99" s="436"/>
+      <c r="D99" s="437"/>
+      <c r="E99" s="437"/>
+      <c r="F99" s="437"/>
+      <c r="G99" s="437"/>
+      <c r="H99" s="437"/>
+      <c r="I99" s="437"/>
+      <c r="J99" s="438"/>
     </row>
     <row r="101" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="102" spans="3:10" x14ac:dyDescent="0.3">
@@ -18310,11 +18319,11 @@
       <c r="G104" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H104" s="437">
+      <c r="H104" s="428">
         <v>102</v>
       </c>
-      <c r="I104" s="437"/>
-      <c r="J104" s="438"/>
+      <c r="I104" s="428"/>
+      <c r="J104" s="429"/>
     </row>
     <row r="105" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C105" s="326" t="s">
@@ -18329,36 +18338,36 @@
       <c r="J105" s="69"/>
     </row>
     <row r="106" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C106" s="428" t="s">
+      <c r="C106" s="430" t="s">
         <v>438</v>
       </c>
-      <c r="D106" s="429"/>
-      <c r="E106" s="429"/>
-      <c r="F106" s="429"/>
-      <c r="G106" s="429"/>
-      <c r="H106" s="429"/>
-      <c r="I106" s="429"/>
-      <c r="J106" s="430"/>
+      <c r="D106" s="431"/>
+      <c r="E106" s="431"/>
+      <c r="F106" s="431"/>
+      <c r="G106" s="431"/>
+      <c r="H106" s="431"/>
+      <c r="I106" s="431"/>
+      <c r="J106" s="432"/>
     </row>
     <row r="107" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C107" s="431"/>
-      <c r="D107" s="432"/>
-      <c r="E107" s="432"/>
-      <c r="F107" s="432"/>
-      <c r="G107" s="432"/>
-      <c r="H107" s="432"/>
-      <c r="I107" s="432"/>
-      <c r="J107" s="433"/>
+      <c r="C107" s="433"/>
+      <c r="D107" s="434"/>
+      <c r="E107" s="434"/>
+      <c r="F107" s="434"/>
+      <c r="G107" s="434"/>
+      <c r="H107" s="434"/>
+      <c r="I107" s="434"/>
+      <c r="J107" s="435"/>
     </row>
     <row r="108" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C108" s="434"/>
-      <c r="D108" s="435"/>
-      <c r="E108" s="435"/>
-      <c r="F108" s="435"/>
-      <c r="G108" s="435"/>
-      <c r="H108" s="435"/>
-      <c r="I108" s="435"/>
-      <c r="J108" s="436"/>
+      <c r="C108" s="436"/>
+      <c r="D108" s="437"/>
+      <c r="E108" s="437"/>
+      <c r="F108" s="437"/>
+      <c r="G108" s="437"/>
+      <c r="H108" s="437"/>
+      <c r="I108" s="437"/>
+      <c r="J108" s="438"/>
     </row>
     <row r="110" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="111" spans="3:10" x14ac:dyDescent="0.3">
@@ -18406,11 +18415,11 @@
       <c r="G113" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H113" s="437">
+      <c r="H113" s="428">
         <v>60</v>
       </c>
-      <c r="I113" s="437"/>
-      <c r="J113" s="438"/>
+      <c r="I113" s="428"/>
+      <c r="J113" s="429"/>
     </row>
     <row r="114" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C114" s="330" t="s">
@@ -18425,36 +18434,36 @@
       <c r="J114" s="69"/>
     </row>
     <row r="115" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C115" s="428" t="s">
+      <c r="C115" s="430" t="s">
         <v>439</v>
       </c>
-      <c r="D115" s="429"/>
-      <c r="E115" s="429"/>
-      <c r="F115" s="429"/>
-      <c r="G115" s="429"/>
-      <c r="H115" s="429"/>
-      <c r="I115" s="429"/>
-      <c r="J115" s="430"/>
+      <c r="D115" s="431"/>
+      <c r="E115" s="431"/>
+      <c r="F115" s="431"/>
+      <c r="G115" s="431"/>
+      <c r="H115" s="431"/>
+      <c r="I115" s="431"/>
+      <c r="J115" s="432"/>
     </row>
     <row r="116" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C116" s="431"/>
-      <c r="D116" s="432"/>
-      <c r="E116" s="432"/>
-      <c r="F116" s="432"/>
-      <c r="G116" s="432"/>
-      <c r="H116" s="432"/>
-      <c r="I116" s="432"/>
-      <c r="J116" s="433"/>
+      <c r="C116" s="433"/>
+      <c r="D116" s="434"/>
+      <c r="E116" s="434"/>
+      <c r="F116" s="434"/>
+      <c r="G116" s="434"/>
+      <c r="H116" s="434"/>
+      <c r="I116" s="434"/>
+      <c r="J116" s="435"/>
     </row>
     <row r="117" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C117" s="434"/>
-      <c r="D117" s="435"/>
-      <c r="E117" s="435"/>
-      <c r="F117" s="435"/>
-      <c r="G117" s="435"/>
-      <c r="H117" s="435"/>
-      <c r="I117" s="435"/>
-      <c r="J117" s="436"/>
+      <c r="C117" s="436"/>
+      <c r="D117" s="437"/>
+      <c r="E117" s="437"/>
+      <c r="F117" s="437"/>
+      <c r="G117" s="437"/>
+      <c r="H117" s="437"/>
+      <c r="I117" s="437"/>
+      <c r="J117" s="438"/>
     </row>
     <row r="119" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="120" spans="3:10" x14ac:dyDescent="0.3">
@@ -18502,11 +18511,11 @@
       <c r="G122" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H122" s="437">
+      <c r="H122" s="428">
         <v>97</v>
       </c>
-      <c r="I122" s="437"/>
-      <c r="J122" s="438"/>
+      <c r="I122" s="428"/>
+      <c r="J122" s="429"/>
     </row>
     <row r="123" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C123" s="334" t="s">
@@ -18521,36 +18530,36 @@
       <c r="J123" s="69"/>
     </row>
     <row r="124" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C124" s="428" t="s">
+      <c r="C124" s="430" t="s">
         <v>440</v>
       </c>
-      <c r="D124" s="429"/>
-      <c r="E124" s="429"/>
-      <c r="F124" s="429"/>
-      <c r="G124" s="429"/>
-      <c r="H124" s="429"/>
-      <c r="I124" s="429"/>
-      <c r="J124" s="430"/>
+      <c r="D124" s="431"/>
+      <c r="E124" s="431"/>
+      <c r="F124" s="431"/>
+      <c r="G124" s="431"/>
+      <c r="H124" s="431"/>
+      <c r="I124" s="431"/>
+      <c r="J124" s="432"/>
     </row>
     <row r="125" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C125" s="431"/>
-      <c r="D125" s="432"/>
-      <c r="E125" s="432"/>
-      <c r="F125" s="432"/>
-      <c r="G125" s="432"/>
-      <c r="H125" s="432"/>
-      <c r="I125" s="432"/>
-      <c r="J125" s="433"/>
+      <c r="C125" s="433"/>
+      <c r="D125" s="434"/>
+      <c r="E125" s="434"/>
+      <c r="F125" s="434"/>
+      <c r="G125" s="434"/>
+      <c r="H125" s="434"/>
+      <c r="I125" s="434"/>
+      <c r="J125" s="435"/>
     </row>
     <row r="126" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C126" s="434"/>
-      <c r="D126" s="435"/>
-      <c r="E126" s="435"/>
-      <c r="F126" s="435"/>
-      <c r="G126" s="435"/>
-      <c r="H126" s="435"/>
-      <c r="I126" s="435"/>
-      <c r="J126" s="436"/>
+      <c r="C126" s="436"/>
+      <c r="D126" s="437"/>
+      <c r="E126" s="437"/>
+      <c r="F126" s="437"/>
+      <c r="G126" s="437"/>
+      <c r="H126" s="437"/>
+      <c r="I126" s="437"/>
+      <c r="J126" s="438"/>
     </row>
     <row r="128" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="129" spans="3:10" x14ac:dyDescent="0.3">
@@ -18598,11 +18607,11 @@
       <c r="G131" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H131" s="437">
+      <c r="H131" s="428">
         <v>110</v>
       </c>
-      <c r="I131" s="437"/>
-      <c r="J131" s="438"/>
+      <c r="I131" s="428"/>
+      <c r="J131" s="429"/>
     </row>
     <row r="132" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C132" s="338" t="s">
@@ -18617,36 +18626,36 @@
       <c r="J132" s="69"/>
     </row>
     <row r="133" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C133" s="428" t="s">
+      <c r="C133" s="430" t="s">
         <v>441</v>
       </c>
-      <c r="D133" s="429"/>
-      <c r="E133" s="429"/>
-      <c r="F133" s="429"/>
-      <c r="G133" s="429"/>
-      <c r="H133" s="429"/>
-      <c r="I133" s="429"/>
-      <c r="J133" s="430"/>
+      <c r="D133" s="431"/>
+      <c r="E133" s="431"/>
+      <c r="F133" s="431"/>
+      <c r="G133" s="431"/>
+      <c r="H133" s="431"/>
+      <c r="I133" s="431"/>
+      <c r="J133" s="432"/>
     </row>
     <row r="134" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C134" s="431"/>
-      <c r="D134" s="432"/>
-      <c r="E134" s="432"/>
-      <c r="F134" s="432"/>
-      <c r="G134" s="432"/>
-      <c r="H134" s="432"/>
-      <c r="I134" s="432"/>
-      <c r="J134" s="433"/>
+      <c r="C134" s="433"/>
+      <c r="D134" s="434"/>
+      <c r="E134" s="434"/>
+      <c r="F134" s="434"/>
+      <c r="G134" s="434"/>
+      <c r="H134" s="434"/>
+      <c r="I134" s="434"/>
+      <c r="J134" s="435"/>
     </row>
     <row r="135" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C135" s="434"/>
-      <c r="D135" s="435"/>
-      <c r="E135" s="435"/>
-      <c r="F135" s="435"/>
-      <c r="G135" s="435"/>
-      <c r="H135" s="435"/>
-      <c r="I135" s="435"/>
-      <c r="J135" s="436"/>
+      <c r="C135" s="436"/>
+      <c r="D135" s="437"/>
+      <c r="E135" s="437"/>
+      <c r="F135" s="437"/>
+      <c r="G135" s="437"/>
+      <c r="H135" s="437"/>
+      <c r="I135" s="437"/>
+      <c r="J135" s="438"/>
     </row>
     <row r="137" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="138" spans="3:10" x14ac:dyDescent="0.3">
@@ -18694,11 +18703,11 @@
       <c r="G140" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H140" s="437">
+      <c r="H140" s="428">
         <v>61</v>
       </c>
-      <c r="I140" s="437"/>
-      <c r="J140" s="438"/>
+      <c r="I140" s="428"/>
+      <c r="J140" s="429"/>
     </row>
     <row r="141" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C141" s="342" t="s">
@@ -18713,36 +18722,36 @@
       <c r="J141" s="69"/>
     </row>
     <row r="142" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C142" s="428" t="s">
+      <c r="C142" s="430" t="s">
         <v>442</v>
       </c>
-      <c r="D142" s="429"/>
-      <c r="E142" s="429"/>
-      <c r="F142" s="429"/>
-      <c r="G142" s="429"/>
-      <c r="H142" s="429"/>
-      <c r="I142" s="429"/>
-      <c r="J142" s="430"/>
+      <c r="D142" s="431"/>
+      <c r="E142" s="431"/>
+      <c r="F142" s="431"/>
+      <c r="G142" s="431"/>
+      <c r="H142" s="431"/>
+      <c r="I142" s="431"/>
+      <c r="J142" s="432"/>
     </row>
     <row r="143" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C143" s="431"/>
-      <c r="D143" s="432"/>
-      <c r="E143" s="432"/>
-      <c r="F143" s="432"/>
-      <c r="G143" s="432"/>
-      <c r="H143" s="432"/>
-      <c r="I143" s="432"/>
-      <c r="J143" s="433"/>
+      <c r="C143" s="433"/>
+      <c r="D143" s="434"/>
+      <c r="E143" s="434"/>
+      <c r="F143" s="434"/>
+      <c r="G143" s="434"/>
+      <c r="H143" s="434"/>
+      <c r="I143" s="434"/>
+      <c r="J143" s="435"/>
     </row>
     <row r="144" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C144" s="434"/>
-      <c r="D144" s="435"/>
-      <c r="E144" s="435"/>
-      <c r="F144" s="435"/>
-      <c r="G144" s="435"/>
-      <c r="H144" s="435"/>
-      <c r="I144" s="435"/>
-      <c r="J144" s="436"/>
+      <c r="C144" s="436"/>
+      <c r="D144" s="437"/>
+      <c r="E144" s="437"/>
+      <c r="F144" s="437"/>
+      <c r="G144" s="437"/>
+      <c r="H144" s="437"/>
+      <c r="I144" s="437"/>
+      <c r="J144" s="438"/>
     </row>
     <row r="146" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="147" spans="3:10" x14ac:dyDescent="0.3">
@@ -18790,11 +18799,11 @@
       <c r="G149" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H149" s="437">
+      <c r="H149" s="428">
         <v>73</v>
       </c>
-      <c r="I149" s="437"/>
-      <c r="J149" s="438"/>
+      <c r="I149" s="428"/>
+      <c r="J149" s="429"/>
     </row>
     <row r="150" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C150" s="347" t="s">
@@ -18809,36 +18818,36 @@
       <c r="J150" s="69"/>
     </row>
     <row r="151" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C151" s="428" t="s">
+      <c r="C151" s="430" t="s">
         <v>443</v>
       </c>
-      <c r="D151" s="429"/>
-      <c r="E151" s="429"/>
-      <c r="F151" s="429"/>
-      <c r="G151" s="429"/>
-      <c r="H151" s="429"/>
-      <c r="I151" s="429"/>
-      <c r="J151" s="430"/>
+      <c r="D151" s="431"/>
+      <c r="E151" s="431"/>
+      <c r="F151" s="431"/>
+      <c r="G151" s="431"/>
+      <c r="H151" s="431"/>
+      <c r="I151" s="431"/>
+      <c r="J151" s="432"/>
     </row>
     <row r="152" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C152" s="431"/>
-      <c r="D152" s="432"/>
-      <c r="E152" s="432"/>
-      <c r="F152" s="432"/>
-      <c r="G152" s="432"/>
-      <c r="H152" s="432"/>
-      <c r="I152" s="432"/>
-      <c r="J152" s="433"/>
+      <c r="C152" s="433"/>
+      <c r="D152" s="434"/>
+      <c r="E152" s="434"/>
+      <c r="F152" s="434"/>
+      <c r="G152" s="434"/>
+      <c r="H152" s="434"/>
+      <c r="I152" s="434"/>
+      <c r="J152" s="435"/>
     </row>
     <row r="153" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C153" s="434"/>
-      <c r="D153" s="435"/>
-      <c r="E153" s="435"/>
-      <c r="F153" s="435"/>
-      <c r="G153" s="435"/>
-      <c r="H153" s="435"/>
-      <c r="I153" s="435"/>
-      <c r="J153" s="436"/>
+      <c r="C153" s="436"/>
+      <c r="D153" s="437"/>
+      <c r="E153" s="437"/>
+      <c r="F153" s="437"/>
+      <c r="G153" s="437"/>
+      <c r="H153" s="437"/>
+      <c r="I153" s="437"/>
+      <c r="J153" s="438"/>
     </row>
     <row r="155" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="156" spans="3:10" x14ac:dyDescent="0.3">
@@ -18886,11 +18895,11 @@
       <c r="G158" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H158" s="437">
+      <c r="H158" s="428">
         <v>119</v>
       </c>
-      <c r="I158" s="437"/>
-      <c r="J158" s="438"/>
+      <c r="I158" s="428"/>
+      <c r="J158" s="429"/>
     </row>
     <row r="159" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C159" s="352" t="s">
@@ -18905,36 +18914,36 @@
       <c r="J159" s="69"/>
     </row>
     <row r="160" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C160" s="428" t="s">
+      <c r="C160" s="430" t="s">
         <v>444</v>
       </c>
-      <c r="D160" s="429"/>
-      <c r="E160" s="429"/>
-      <c r="F160" s="429"/>
-      <c r="G160" s="429"/>
-      <c r="H160" s="429"/>
-      <c r="I160" s="429"/>
-      <c r="J160" s="430"/>
+      <c r="D160" s="431"/>
+      <c r="E160" s="431"/>
+      <c r="F160" s="431"/>
+      <c r="G160" s="431"/>
+      <c r="H160" s="431"/>
+      <c r="I160" s="431"/>
+      <c r="J160" s="432"/>
     </row>
     <row r="161" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C161" s="431"/>
-      <c r="D161" s="432"/>
-      <c r="E161" s="432"/>
-      <c r="F161" s="432"/>
-      <c r="G161" s="432"/>
-      <c r="H161" s="432"/>
-      <c r="I161" s="432"/>
-      <c r="J161" s="433"/>
+      <c r="C161" s="433"/>
+      <c r="D161" s="434"/>
+      <c r="E161" s="434"/>
+      <c r="F161" s="434"/>
+      <c r="G161" s="434"/>
+      <c r="H161" s="434"/>
+      <c r="I161" s="434"/>
+      <c r="J161" s="435"/>
     </row>
     <row r="162" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C162" s="434"/>
-      <c r="D162" s="435"/>
-      <c r="E162" s="435"/>
-      <c r="F162" s="435"/>
-      <c r="G162" s="435"/>
-      <c r="H162" s="435"/>
-      <c r="I162" s="435"/>
-      <c r="J162" s="436"/>
+      <c r="C162" s="436"/>
+      <c r="D162" s="437"/>
+      <c r="E162" s="437"/>
+      <c r="F162" s="437"/>
+      <c r="G162" s="437"/>
+      <c r="H162" s="437"/>
+      <c r="I162" s="437"/>
+      <c r="J162" s="438"/>
     </row>
     <row r="164" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="165" spans="3:10" x14ac:dyDescent="0.3">
@@ -18982,11 +18991,11 @@
       <c r="G167" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H167" s="437">
+      <c r="H167" s="428">
         <v>96</v>
       </c>
-      <c r="I167" s="437"/>
-      <c r="J167" s="438"/>
+      <c r="I167" s="428"/>
+      <c r="J167" s="429"/>
     </row>
     <row r="168" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C168" s="352" t="s">
@@ -19001,36 +19010,36 @@
       <c r="J168" s="69"/>
     </row>
     <row r="169" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C169" s="428" t="s">
+      <c r="C169" s="430" t="s">
         <v>445</v>
       </c>
-      <c r="D169" s="429"/>
-      <c r="E169" s="429"/>
-      <c r="F169" s="429"/>
-      <c r="G169" s="429"/>
-      <c r="H169" s="429"/>
-      <c r="I169" s="429"/>
-      <c r="J169" s="430"/>
+      <c r="D169" s="431"/>
+      <c r="E169" s="431"/>
+      <c r="F169" s="431"/>
+      <c r="G169" s="431"/>
+      <c r="H169" s="431"/>
+      <c r="I169" s="431"/>
+      <c r="J169" s="432"/>
     </row>
     <row r="170" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C170" s="431"/>
-      <c r="D170" s="432"/>
-      <c r="E170" s="432"/>
-      <c r="F170" s="432"/>
-      <c r="G170" s="432"/>
-      <c r="H170" s="432"/>
-      <c r="I170" s="432"/>
-      <c r="J170" s="433"/>
+      <c r="C170" s="433"/>
+      <c r="D170" s="434"/>
+      <c r="E170" s="434"/>
+      <c r="F170" s="434"/>
+      <c r="G170" s="434"/>
+      <c r="H170" s="434"/>
+      <c r="I170" s="434"/>
+      <c r="J170" s="435"/>
     </row>
     <row r="171" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C171" s="434"/>
-      <c r="D171" s="435"/>
-      <c r="E171" s="435"/>
-      <c r="F171" s="435"/>
-      <c r="G171" s="435"/>
-      <c r="H171" s="435"/>
-      <c r="I171" s="435"/>
-      <c r="J171" s="436"/>
+      <c r="C171" s="436"/>
+      <c r="D171" s="437"/>
+      <c r="E171" s="437"/>
+      <c r="F171" s="437"/>
+      <c r="G171" s="437"/>
+      <c r="H171" s="437"/>
+      <c r="I171" s="437"/>
+      <c r="J171" s="438"/>
     </row>
     <row r="173" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="174" spans="3:10" x14ac:dyDescent="0.3">
@@ -19078,11 +19087,11 @@
       <c r="G176" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H176" s="437">
+      <c r="H176" s="428">
         <v>130</v>
       </c>
-      <c r="I176" s="437"/>
-      <c r="J176" s="438"/>
+      <c r="I176" s="428"/>
+      <c r="J176" s="429"/>
     </row>
     <row r="177" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C177" s="352" t="s">
@@ -19097,36 +19106,36 @@
       <c r="J177" s="69"/>
     </row>
     <row r="178" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C178" s="428" t="s">
+      <c r="C178" s="430" t="s">
         <v>446</v>
       </c>
-      <c r="D178" s="429"/>
-      <c r="E178" s="429"/>
-      <c r="F178" s="429"/>
-      <c r="G178" s="429"/>
-      <c r="H178" s="429"/>
-      <c r="I178" s="429"/>
-      <c r="J178" s="430"/>
+      <c r="D178" s="431"/>
+      <c r="E178" s="431"/>
+      <c r="F178" s="431"/>
+      <c r="G178" s="431"/>
+      <c r="H178" s="431"/>
+      <c r="I178" s="431"/>
+      <c r="J178" s="432"/>
     </row>
     <row r="179" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C179" s="431"/>
-      <c r="D179" s="432"/>
-      <c r="E179" s="432"/>
-      <c r="F179" s="432"/>
-      <c r="G179" s="432"/>
-      <c r="H179" s="432"/>
-      <c r="I179" s="432"/>
-      <c r="J179" s="433"/>
+      <c r="C179" s="433"/>
+      <c r="D179" s="434"/>
+      <c r="E179" s="434"/>
+      <c r="F179" s="434"/>
+      <c r="G179" s="434"/>
+      <c r="H179" s="434"/>
+      <c r="I179" s="434"/>
+      <c r="J179" s="435"/>
     </row>
     <row r="180" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C180" s="434"/>
-      <c r="D180" s="435"/>
-      <c r="E180" s="435"/>
-      <c r="F180" s="435"/>
-      <c r="G180" s="435"/>
-      <c r="H180" s="435"/>
-      <c r="I180" s="435"/>
-      <c r="J180" s="436"/>
+      <c r="C180" s="436"/>
+      <c r="D180" s="437"/>
+      <c r="E180" s="437"/>
+      <c r="F180" s="437"/>
+      <c r="G180" s="437"/>
+      <c r="H180" s="437"/>
+      <c r="I180" s="437"/>
+      <c r="J180" s="438"/>
     </row>
     <row r="181" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="182" spans="3:10" x14ac:dyDescent="0.3">
@@ -19174,11 +19183,11 @@
       <c r="G184" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H184" s="437">
+      <c r="H184" s="428">
         <v>88</v>
       </c>
-      <c r="I184" s="437"/>
-      <c r="J184" s="438"/>
+      <c r="I184" s="428"/>
+      <c r="J184" s="429"/>
     </row>
     <row r="185" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C185" s="352" t="s">
@@ -19193,36 +19202,36 @@
       <c r="J185" s="69"/>
     </row>
     <row r="186" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C186" s="428" t="s">
+      <c r="C186" s="430" t="s">
         <v>447</v>
       </c>
-      <c r="D186" s="429"/>
-      <c r="E186" s="429"/>
-      <c r="F186" s="429"/>
-      <c r="G186" s="429"/>
-      <c r="H186" s="429"/>
-      <c r="I186" s="429"/>
-      <c r="J186" s="430"/>
+      <c r="D186" s="431"/>
+      <c r="E186" s="431"/>
+      <c r="F186" s="431"/>
+      <c r="G186" s="431"/>
+      <c r="H186" s="431"/>
+      <c r="I186" s="431"/>
+      <c r="J186" s="432"/>
     </row>
     <row r="187" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C187" s="431"/>
-      <c r="D187" s="432"/>
-      <c r="E187" s="432"/>
-      <c r="F187" s="432"/>
-      <c r="G187" s="432"/>
-      <c r="H187" s="432"/>
-      <c r="I187" s="432"/>
-      <c r="J187" s="433"/>
+      <c r="C187" s="433"/>
+      <c r="D187" s="434"/>
+      <c r="E187" s="434"/>
+      <c r="F187" s="434"/>
+      <c r="G187" s="434"/>
+      <c r="H187" s="434"/>
+      <c r="I187" s="434"/>
+      <c r="J187" s="435"/>
     </row>
     <row r="188" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C188" s="434"/>
-      <c r="D188" s="435"/>
-      <c r="E188" s="435"/>
-      <c r="F188" s="435"/>
-      <c r="G188" s="435"/>
-      <c r="H188" s="435"/>
-      <c r="I188" s="435"/>
-      <c r="J188" s="436"/>
+      <c r="C188" s="436"/>
+      <c r="D188" s="437"/>
+      <c r="E188" s="437"/>
+      <c r="F188" s="437"/>
+      <c r="G188" s="437"/>
+      <c r="H188" s="437"/>
+      <c r="I188" s="437"/>
+      <c r="J188" s="438"/>
     </row>
     <row r="190" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="191" spans="3:10" x14ac:dyDescent="0.3">
@@ -19270,11 +19279,11 @@
       <c r="G193" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H193" s="437">
+      <c r="H193" s="428">
         <v>88</v>
       </c>
-      <c r="I193" s="437"/>
-      <c r="J193" s="438"/>
+      <c r="I193" s="428"/>
+      <c r="J193" s="429"/>
     </row>
     <row r="194" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C194" s="352" t="s">
@@ -19289,36 +19298,36 @@
       <c r="J194" s="69"/>
     </row>
     <row r="195" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C195" s="428" t="s">
+      <c r="C195" s="430" t="s">
         <v>448</v>
       </c>
-      <c r="D195" s="429"/>
-      <c r="E195" s="429"/>
-      <c r="F195" s="429"/>
-      <c r="G195" s="429"/>
-      <c r="H195" s="429"/>
-      <c r="I195" s="429"/>
-      <c r="J195" s="430"/>
+      <c r="D195" s="431"/>
+      <c r="E195" s="431"/>
+      <c r="F195" s="431"/>
+      <c r="G195" s="431"/>
+      <c r="H195" s="431"/>
+      <c r="I195" s="431"/>
+      <c r="J195" s="432"/>
     </row>
     <row r="196" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C196" s="431"/>
-      <c r="D196" s="432"/>
-      <c r="E196" s="432"/>
-      <c r="F196" s="432"/>
-      <c r="G196" s="432"/>
-      <c r="H196" s="432"/>
-      <c r="I196" s="432"/>
-      <c r="J196" s="433"/>
+      <c r="C196" s="433"/>
+      <c r="D196" s="434"/>
+      <c r="E196" s="434"/>
+      <c r="F196" s="434"/>
+      <c r="G196" s="434"/>
+      <c r="H196" s="434"/>
+      <c r="I196" s="434"/>
+      <c r="J196" s="435"/>
     </row>
     <row r="197" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C197" s="434"/>
-      <c r="D197" s="435"/>
-      <c r="E197" s="435"/>
-      <c r="F197" s="435"/>
-      <c r="G197" s="435"/>
-      <c r="H197" s="435"/>
-      <c r="I197" s="435"/>
-      <c r="J197" s="436"/>
+      <c r="C197" s="436"/>
+      <c r="D197" s="437"/>
+      <c r="E197" s="437"/>
+      <c r="F197" s="437"/>
+      <c r="G197" s="437"/>
+      <c r="H197" s="437"/>
+      <c r="I197" s="437"/>
+      <c r="J197" s="438"/>
     </row>
     <row r="199" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="200" spans="3:13" x14ac:dyDescent="0.3">
@@ -19367,11 +19376,11 @@
       <c r="G202" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H202" s="437">
+      <c r="H202" s="428">
         <v>42</v>
       </c>
-      <c r="I202" s="437"/>
-      <c r="J202" s="438"/>
+      <c r="I202" s="428"/>
+      <c r="J202" s="429"/>
     </row>
     <row r="203" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C203" s="352" t="s">
@@ -19386,36 +19395,36 @@
       <c r="J203" s="69"/>
     </row>
     <row r="204" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C204" s="428" t="s">
+      <c r="C204" s="430" t="s">
         <v>449</v>
       </c>
-      <c r="D204" s="429"/>
-      <c r="E204" s="429"/>
-      <c r="F204" s="429"/>
-      <c r="G204" s="429"/>
-      <c r="H204" s="429"/>
-      <c r="I204" s="429"/>
-      <c r="J204" s="430"/>
+      <c r="D204" s="431"/>
+      <c r="E204" s="431"/>
+      <c r="F204" s="431"/>
+      <c r="G204" s="431"/>
+      <c r="H204" s="431"/>
+      <c r="I204" s="431"/>
+      <c r="J204" s="432"/>
     </row>
     <row r="205" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C205" s="431"/>
-      <c r="D205" s="432"/>
-      <c r="E205" s="432"/>
-      <c r="F205" s="432"/>
-      <c r="G205" s="432"/>
-      <c r="H205" s="432"/>
-      <c r="I205" s="432"/>
-      <c r="J205" s="433"/>
+      <c r="C205" s="433"/>
+      <c r="D205" s="434"/>
+      <c r="E205" s="434"/>
+      <c r="F205" s="434"/>
+      <c r="G205" s="434"/>
+      <c r="H205" s="434"/>
+      <c r="I205" s="434"/>
+      <c r="J205" s="435"/>
     </row>
     <row r="206" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C206" s="434"/>
-      <c r="D206" s="435"/>
-      <c r="E206" s="435"/>
-      <c r="F206" s="435"/>
-      <c r="G206" s="435"/>
-      <c r="H206" s="435"/>
-      <c r="I206" s="435"/>
-      <c r="J206" s="436"/>
+      <c r="C206" s="436"/>
+      <c r="D206" s="437"/>
+      <c r="E206" s="437"/>
+      <c r="F206" s="437"/>
+      <c r="G206" s="437"/>
+      <c r="H206" s="437"/>
+      <c r="I206" s="437"/>
+      <c r="J206" s="438"/>
     </row>
     <row r="209" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="210" spans="3:10" x14ac:dyDescent="0.3">
@@ -19465,11 +19474,11 @@
       <c r="G212" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H212" s="437">
+      <c r="H212" s="428">
         <v>139</v>
       </c>
-      <c r="I212" s="437"/>
-      <c r="J212" s="438"/>
+      <c r="I212" s="428"/>
+      <c r="J212" s="429"/>
     </row>
     <row r="213" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C213" s="352" t="s">
@@ -19484,36 +19493,36 @@
       <c r="J213" s="69"/>
     </row>
     <row r="214" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C214" s="428" t="s">
+      <c r="C214" s="430" t="s">
         <v>452</v>
       </c>
-      <c r="D214" s="429"/>
-      <c r="E214" s="429"/>
-      <c r="F214" s="429"/>
-      <c r="G214" s="429"/>
-      <c r="H214" s="429"/>
-      <c r="I214" s="429"/>
-      <c r="J214" s="430"/>
+      <c r="D214" s="431"/>
+      <c r="E214" s="431"/>
+      <c r="F214" s="431"/>
+      <c r="G214" s="431"/>
+      <c r="H214" s="431"/>
+      <c r="I214" s="431"/>
+      <c r="J214" s="432"/>
     </row>
     <row r="215" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C215" s="431"/>
-      <c r="D215" s="432"/>
-      <c r="E215" s="432"/>
-      <c r="F215" s="432"/>
-      <c r="G215" s="432"/>
-      <c r="H215" s="432"/>
-      <c r="I215" s="432"/>
-      <c r="J215" s="433"/>
+      <c r="C215" s="433"/>
+      <c r="D215" s="434"/>
+      <c r="E215" s="434"/>
+      <c r="F215" s="434"/>
+      <c r="G215" s="434"/>
+      <c r="H215" s="434"/>
+      <c r="I215" s="434"/>
+      <c r="J215" s="435"/>
     </row>
     <row r="216" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C216" s="434"/>
-      <c r="D216" s="435"/>
-      <c r="E216" s="435"/>
-      <c r="F216" s="435"/>
-      <c r="G216" s="435"/>
-      <c r="H216" s="435"/>
-      <c r="I216" s="435"/>
-      <c r="J216" s="436"/>
+      <c r="C216" s="436"/>
+      <c r="D216" s="437"/>
+      <c r="E216" s="437"/>
+      <c r="F216" s="437"/>
+      <c r="G216" s="437"/>
+      <c r="H216" s="437"/>
+      <c r="I216" s="437"/>
+      <c r="J216" s="438"/>
     </row>
     <row r="218" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="219" spans="3:10" x14ac:dyDescent="0.3">
@@ -19563,11 +19572,11 @@
       <c r="G221" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H221" s="437">
+      <c r="H221" s="428">
         <v>105</v>
       </c>
-      <c r="I221" s="437"/>
-      <c r="J221" s="438"/>
+      <c r="I221" s="428"/>
+      <c r="J221" s="429"/>
     </row>
     <row r="222" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C222" s="352" t="s">
@@ -19582,36 +19591,36 @@
       <c r="J222" s="69"/>
     </row>
     <row r="223" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C223" s="428" t="s">
+      <c r="C223" s="430" t="s">
         <v>454</v>
       </c>
-      <c r="D223" s="429"/>
-      <c r="E223" s="429"/>
-      <c r="F223" s="429"/>
-      <c r="G223" s="429"/>
-      <c r="H223" s="429"/>
-      <c r="I223" s="429"/>
-      <c r="J223" s="430"/>
+      <c r="D223" s="431"/>
+      <c r="E223" s="431"/>
+      <c r="F223" s="431"/>
+      <c r="G223" s="431"/>
+      <c r="H223" s="431"/>
+      <c r="I223" s="431"/>
+      <c r="J223" s="432"/>
     </row>
     <row r="224" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C224" s="431"/>
-      <c r="D224" s="432"/>
-      <c r="E224" s="432"/>
-      <c r="F224" s="432"/>
-      <c r="G224" s="432"/>
-      <c r="H224" s="432"/>
-      <c r="I224" s="432"/>
-      <c r="J224" s="433"/>
+      <c r="C224" s="433"/>
+      <c r="D224" s="434"/>
+      <c r="E224" s="434"/>
+      <c r="F224" s="434"/>
+      <c r="G224" s="434"/>
+      <c r="H224" s="434"/>
+      <c r="I224" s="434"/>
+      <c r="J224" s="435"/>
     </row>
     <row r="225" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C225" s="434"/>
-      <c r="D225" s="435"/>
-      <c r="E225" s="435"/>
-      <c r="F225" s="435"/>
-      <c r="G225" s="435"/>
-      <c r="H225" s="435"/>
-      <c r="I225" s="435"/>
-      <c r="J225" s="436"/>
+      <c r="C225" s="436"/>
+      <c r="D225" s="437"/>
+      <c r="E225" s="437"/>
+      <c r="F225" s="437"/>
+      <c r="G225" s="437"/>
+      <c r="H225" s="437"/>
+      <c r="I225" s="437"/>
+      <c r="J225" s="438"/>
     </row>
     <row r="227" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="228" spans="3:10" x14ac:dyDescent="0.3">
@@ -19659,11 +19668,11 @@
       <c r="G230" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="H230" s="437">
+      <c r="H230" s="428">
         <v>28</v>
       </c>
-      <c r="I230" s="437"/>
-      <c r="J230" s="438"/>
+      <c r="I230" s="428"/>
+      <c r="J230" s="429"/>
     </row>
     <row r="231" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C231" s="352" t="s">
@@ -19678,39 +19687,333 @@
       <c r="J231" s="69"/>
     </row>
     <row r="232" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C232" s="428" t="s">
+      <c r="C232" s="430" t="s">
         <v>456</v>
       </c>
-      <c r="D232" s="429"/>
-      <c r="E232" s="429"/>
-      <c r="F232" s="429"/>
-      <c r="G232" s="429"/>
-      <c r="H232" s="429"/>
-      <c r="I232" s="429"/>
-      <c r="J232" s="430"/>
+      <c r="D232" s="431"/>
+      <c r="E232" s="431"/>
+      <c r="F232" s="431"/>
+      <c r="G232" s="431"/>
+      <c r="H232" s="431"/>
+      <c r="I232" s="431"/>
+      <c r="J232" s="432"/>
     </row>
     <row r="233" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C233" s="431"/>
-      <c r="D233" s="432"/>
-      <c r="E233" s="432"/>
-      <c r="F233" s="432"/>
-      <c r="G233" s="432"/>
-      <c r="H233" s="432"/>
-      <c r="I233" s="432"/>
-      <c r="J233" s="433"/>
+      <c r="C233" s="433"/>
+      <c r="D233" s="434"/>
+      <c r="E233" s="434"/>
+      <c r="F233" s="434"/>
+      <c r="G233" s="434"/>
+      <c r="H233" s="434"/>
+      <c r="I233" s="434"/>
+      <c r="J233" s="435"/>
     </row>
     <row r="234" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C234" s="434"/>
-      <c r="D234" s="435"/>
-      <c r="E234" s="435"/>
-      <c r="F234" s="435"/>
-      <c r="G234" s="435"/>
-      <c r="H234" s="435"/>
-      <c r="I234" s="435"/>
-      <c r="J234" s="436"/>
+      <c r="C234" s="436"/>
+      <c r="D234" s="437"/>
+      <c r="E234" s="437"/>
+      <c r="F234" s="437"/>
+      <c r="G234" s="437"/>
+      <c r="H234" s="437"/>
+      <c r="I234" s="437"/>
+      <c r="J234" s="438"/>
+    </row>
+    <row r="236" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="237" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C237" s="350" t="s">
+        <v>159</v>
+      </c>
+      <c r="D237" s="351">
+        <f>D228+1</f>
+        <v>27</v>
+      </c>
+      <c r="E237" s="64"/>
+      <c r="F237" s="64"/>
+      <c r="G237" s="64"/>
+      <c r="H237" s="64"/>
+      <c r="I237" s="64"/>
+      <c r="J237" s="66"/>
+    </row>
+    <row r="238" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C238" s="352" t="s">
+        <v>160</v>
+      </c>
+      <c r="D238" s="353"/>
+      <c r="E238" s="220">
+        <v>45945</v>
+      </c>
+      <c r="F238" s="36"/>
+      <c r="G238" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H238" s="90"/>
+      <c r="I238" s="67"/>
+      <c r="J238" s="68"/>
+    </row>
+    <row r="239" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C239" s="352" t="s">
+        <v>161</v>
+      </c>
+      <c r="D239" s="353" t="s">
+        <v>162</v>
+      </c>
+      <c r="E239" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F239" s="36"/>
+      <c r="G239" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H239" s="428">
+        <v>71</v>
+      </c>
+      <c r="I239" s="428"/>
+      <c r="J239" s="429"/>
+    </row>
+    <row r="240" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C240" s="352" t="s">
+        <v>164</v>
+      </c>
+      <c r="D240" s="353"/>
+      <c r="E240" s="36"/>
+      <c r="F240" s="36"/>
+      <c r="G240" s="36"/>
+      <c r="H240" s="36"/>
+      <c r="I240" s="36"/>
+      <c r="J240" s="69"/>
+    </row>
+    <row r="241" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C241" s="430" t="s">
+        <v>515</v>
+      </c>
+      <c r="D241" s="431"/>
+      <c r="E241" s="431"/>
+      <c r="F241" s="431"/>
+      <c r="G241" s="431"/>
+      <c r="H241" s="431"/>
+      <c r="I241" s="431"/>
+      <c r="J241" s="432"/>
+    </row>
+    <row r="242" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C242" s="433"/>
+      <c r="D242" s="434"/>
+      <c r="E242" s="434"/>
+      <c r="F242" s="434"/>
+      <c r="G242" s="434"/>
+      <c r="H242" s="434"/>
+      <c r="I242" s="434"/>
+      <c r="J242" s="435"/>
+    </row>
+    <row r="243" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C243" s="436"/>
+      <c r="D243" s="437"/>
+      <c r="E243" s="437"/>
+      <c r="F243" s="437"/>
+      <c r="G243" s="437"/>
+      <c r="H243" s="437"/>
+      <c r="I243" s="437"/>
+      <c r="J243" s="438"/>
+    </row>
+    <row r="245" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="246" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C246" s="350" t="s">
+        <v>159</v>
+      </c>
+      <c r="D246" s="351">
+        <f>D237+1</f>
+        <v>28</v>
+      </c>
+      <c r="E246" s="64"/>
+      <c r="F246" s="64"/>
+      <c r="G246" s="64"/>
+      <c r="H246" s="64"/>
+      <c r="I246" s="64"/>
+      <c r="J246" s="66"/>
+    </row>
+    <row r="247" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C247" s="352" t="s">
+        <v>160</v>
+      </c>
+      <c r="D247" s="353"/>
+      <c r="E247" s="220">
+        <v>45945</v>
+      </c>
+      <c r="F247" s="36"/>
+      <c r="G247" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H247" s="90"/>
+      <c r="I247" s="67"/>
+      <c r="J247" s="68"/>
+    </row>
+    <row r="248" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C248" s="352" t="s">
+        <v>161</v>
+      </c>
+      <c r="D248" s="353" t="s">
+        <v>162</v>
+      </c>
+      <c r="E248" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F248" s="36"/>
+      <c r="G248" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H248" s="428">
+        <v>109</v>
+      </c>
+      <c r="I248" s="428"/>
+      <c r="J248" s="429"/>
+    </row>
+    <row r="249" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C249" s="352" t="s">
+        <v>164</v>
+      </c>
+      <c r="D249" s="353"/>
+      <c r="E249" s="36"/>
+      <c r="F249" s="36"/>
+      <c r="G249" s="36"/>
+      <c r="H249" s="36"/>
+      <c r="I249" s="36"/>
+      <c r="J249" s="69"/>
+    </row>
+    <row r="250" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C250" s="430" t="s">
+        <v>516</v>
+      </c>
+      <c r="D250" s="431"/>
+      <c r="E250" s="431"/>
+      <c r="F250" s="431"/>
+      <c r="G250" s="431"/>
+      <c r="H250" s="431"/>
+      <c r="I250" s="431"/>
+      <c r="J250" s="432"/>
+    </row>
+    <row r="251" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C251" s="433"/>
+      <c r="D251" s="434"/>
+      <c r="E251" s="434"/>
+      <c r="F251" s="434"/>
+      <c r="G251" s="434"/>
+      <c r="H251" s="434"/>
+      <c r="I251" s="434"/>
+      <c r="J251" s="435"/>
+    </row>
+    <row r="252" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C252" s="436"/>
+      <c r="D252" s="437"/>
+      <c r="E252" s="437"/>
+      <c r="F252" s="437"/>
+      <c r="G252" s="437"/>
+      <c r="H252" s="437"/>
+      <c r="I252" s="437"/>
+      <c r="J252" s="438"/>
+    </row>
+    <row r="254" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="255" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C255" s="350" t="s">
+        <v>159</v>
+      </c>
+      <c r="D255" s="351">
+        <f>D246+1</f>
+        <v>29</v>
+      </c>
+      <c r="E255" s="64"/>
+      <c r="F255" s="64"/>
+      <c r="G255" s="64"/>
+      <c r="H255" s="64"/>
+      <c r="I255" s="64"/>
+      <c r="J255" s="66"/>
+    </row>
+    <row r="256" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C256" s="352" t="s">
+        <v>160</v>
+      </c>
+      <c r="D256" s="353"/>
+      <c r="E256" s="220">
+        <v>45945</v>
+      </c>
+      <c r="F256" s="36"/>
+      <c r="G256" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H256" s="90"/>
+      <c r="I256" s="67"/>
+      <c r="J256" s="68"/>
+    </row>
+    <row r="257" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C257" s="352" t="s">
+        <v>161</v>
+      </c>
+      <c r="D257" s="353" t="s">
+        <v>162</v>
+      </c>
+      <c r="E257" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F257" s="36"/>
+      <c r="G257" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H257" s="428">
+        <v>95</v>
+      </c>
+      <c r="I257" s="428"/>
+      <c r="J257" s="429"/>
+    </row>
+    <row r="258" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C258" s="352" t="s">
+        <v>164</v>
+      </c>
+      <c r="D258" s="353"/>
+      <c r="E258" s="36"/>
+      <c r="F258" s="36"/>
+      <c r="G258" s="36"/>
+      <c r="H258" s="36"/>
+      <c r="I258" s="36"/>
+      <c r="J258" s="69"/>
+    </row>
+    <row r="259" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C259" s="430" t="s">
+        <v>517</v>
+      </c>
+      <c r="D259" s="431"/>
+      <c r="E259" s="431"/>
+      <c r="F259" s="431"/>
+      <c r="G259" s="431"/>
+      <c r="H259" s="431"/>
+      <c r="I259" s="431"/>
+      <c r="J259" s="432"/>
+    </row>
+    <row r="260" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C260" s="433"/>
+      <c r="D260" s="434"/>
+      <c r="E260" s="434"/>
+      <c r="F260" s="434"/>
+      <c r="G260" s="434"/>
+      <c r="H260" s="434"/>
+      <c r="I260" s="434"/>
+      <c r="J260" s="435"/>
+    </row>
+    <row r="261" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C261" s="436"/>
+      <c r="D261" s="437"/>
+      <c r="E261" s="437"/>
+      <c r="F261" s="437"/>
+      <c r="G261" s="437"/>
+      <c r="H261" s="437"/>
+      <c r="I261" s="437"/>
+      <c r="J261" s="438"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="57">
+    <mergeCell ref="H248:J248"/>
+    <mergeCell ref="C250:J252"/>
+    <mergeCell ref="H257:J257"/>
+    <mergeCell ref="C259:J261"/>
+    <mergeCell ref="H184:J184"/>
+    <mergeCell ref="C186:J188"/>
     <mergeCell ref="H230:J230"/>
     <mergeCell ref="C232:J234"/>
     <mergeCell ref="H193:J193"/>
@@ -19721,16 +20024,6 @@
     <mergeCell ref="C214:J216"/>
     <mergeCell ref="H202:J202"/>
     <mergeCell ref="C204:J206"/>
-    <mergeCell ref="C169:J171"/>
-    <mergeCell ref="H176:J176"/>
-    <mergeCell ref="C178:J180"/>
-    <mergeCell ref="H184:J184"/>
-    <mergeCell ref="C186:J188"/>
-    <mergeCell ref="H149:J149"/>
-    <mergeCell ref="C151:J153"/>
-    <mergeCell ref="H158:J158"/>
-    <mergeCell ref="C160:J162"/>
-    <mergeCell ref="H167:J167"/>
     <mergeCell ref="H59:J59"/>
     <mergeCell ref="C61:J63"/>
     <mergeCell ref="C52:J54"/>
@@ -19756,12 +20049,22 @@
     <mergeCell ref="H104:J104"/>
     <mergeCell ref="C106:J108"/>
     <mergeCell ref="H113:J113"/>
+    <mergeCell ref="H239:J239"/>
+    <mergeCell ref="C241:J243"/>
     <mergeCell ref="C142:J144"/>
     <mergeCell ref="H122:J122"/>
     <mergeCell ref="C124:J126"/>
     <mergeCell ref="H131:J131"/>
     <mergeCell ref="C133:J135"/>
     <mergeCell ref="H140:J140"/>
+    <mergeCell ref="H149:J149"/>
+    <mergeCell ref="C151:J153"/>
+    <mergeCell ref="H158:J158"/>
+    <mergeCell ref="C160:J162"/>
+    <mergeCell ref="H167:J167"/>
+    <mergeCell ref="C169:J171"/>
+    <mergeCell ref="H176:J176"/>
+    <mergeCell ref="C178:J180"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BRISAS/EXPENSAS/2026/MARZO/BRISAS-MARZO.xlsx
+++ b/BRISAS/EXPENSAS/2026/MARZO/BRISAS-MARZO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\MARZO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6815EA7-4CE5-477B-B6E9-DEF4657F849D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CBFF74-0728-4484-A915-91F857FD4DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="519">
   <si>
     <t>Dpto.</t>
   </si>
@@ -1624,6 +1624,9 @@
   </si>
   <si>
     <t>Transfirio $700.000 el dia 30/03</t>
+  </si>
+  <si>
+    <t>Lote 92 transfririo 1.736.196,00 el 31/03 - HABLAR CON RO COMO DIVIDIR ESO, YA QUE PARTE VA PARA SU PLAN DE PAGO Y PARTE PARA SUS EXPENSAS</t>
   </si>
 </sst>
 </file>
@@ -3000,19 +3003,16 @@
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3021,33 +3021,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3081,50 +3065,52 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3183,7 +3169,24 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3652,34 +3655,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="388"/>
-      <c r="B1" s="383" t="s">
+      <c r="A1" s="383"/>
+      <c r="B1" s="378" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="384"/>
-      <c r="D1" s="384"/>
-      <c r="E1" s="385"/>
+      <c r="C1" s="379"/>
+      <c r="D1" s="379"/>
+      <c r="E1" s="380"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="389"/>
-      <c r="B2" s="383" t="s">
+      <c r="A2" s="384"/>
+      <c r="B2" s="378" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="384"/>
-      <c r="D2" s="384"/>
-      <c r="E2" s="385"/>
+      <c r="C2" s="379"/>
+      <c r="D2" s="379"/>
+      <c r="E2" s="380"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="389"/>
-      <c r="B3" s="380" t="s">
+      <c r="A3" s="384"/>
+      <c r="B3" s="375" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="381"/>
-      <c r="D3" s="381"/>
-      <c r="E3" s="382"/>
+      <c r="C3" s="376"/>
+      <c r="D3" s="376"/>
+      <c r="E3" s="377"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="389"/>
+      <c r="A4" s="384"/>
       <c r="B4" s="47" t="s">
         <v>155</v>
       </c>
@@ -3688,7 +3691,7 @@
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="389"/>
+      <c r="A5" s="384"/>
       <c r="B5" s="50" t="s">
         <v>458</v>
       </c>
@@ -3697,7 +3700,7 @@
       <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="389"/>
+      <c r="A6" s="384"/>
       <c r="B6" s="51" t="s">
         <v>285</v>
       </c>
@@ -3706,7 +3709,7 @@
       <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="389"/>
+      <c r="A7" s="384"/>
       <c r="B7" s="51" t="s">
         <v>284</v>
       </c>
@@ -3715,36 +3718,36 @@
       <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="390"/>
-      <c r="B8" s="386" t="s">
+      <c r="A8" s="385"/>
+      <c r="B8" s="381" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="386"/>
-      <c r="D8" s="386"/>
-      <c r="E8" s="387"/>
+      <c r="C8" s="381"/>
+      <c r="D8" s="381"/>
+      <c r="E8" s="382"/>
     </row>
     <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="391" t="s">
+      <c r="A10" s="370" t="s">
         <v>457</v>
       </c>
-      <c r="B10" s="391"/>
-      <c r="C10" s="391"/>
-      <c r="D10" s="391"/>
-      <c r="E10" s="391"/>
+      <c r="B10" s="370"/>
+      <c r="C10" s="370"/>
+      <c r="D10" s="370"/>
+      <c r="E10" s="370"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="391"/>
-      <c r="B11" s="391"/>
-      <c r="C11" s="391"/>
-      <c r="D11" s="391"/>
-      <c r="E11" s="391"/>
+      <c r="A11" s="370"/>
+      <c r="B11" s="370"/>
+      <c r="C11" s="370"/>
+      <c r="D11" s="370"/>
+      <c r="E11" s="370"/>
     </row>
     <row r="12" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="391"/>
-      <c r="B12" s="391"/>
-      <c r="C12" s="391"/>
-      <c r="D12" s="391"/>
-      <c r="E12" s="391"/>
+      <c r="A12" s="370"/>
+      <c r="B12" s="370"/>
+      <c r="C12" s="370"/>
+      <c r="D12" s="370"/>
+      <c r="E12" s="370"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="32"/>
@@ -3761,34 +3764,34 @@
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="392" t="s">
+      <c r="A15" s="371" t="s">
         <v>243</v>
       </c>
-      <c r="B15" s="392"/>
-      <c r="C15" s="392"/>
-      <c r="D15" s="392"/>
-      <c r="E15" s="392"/>
+      <c r="B15" s="371"/>
+      <c r="C15" s="371"/>
+      <c r="D15" s="371"/>
+      <c r="E15" s="371"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="392"/>
-      <c r="B16" s="392"/>
-      <c r="C16" s="392"/>
-      <c r="D16" s="392"/>
-      <c r="E16" s="392"/>
+      <c r="A16" s="371"/>
+      <c r="B16" s="371"/>
+      <c r="C16" s="371"/>
+      <c r="D16" s="371"/>
+      <c r="E16" s="371"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="392"/>
-      <c r="B17" s="392"/>
-      <c r="C17" s="392"/>
-      <c r="D17" s="392"/>
-      <c r="E17" s="392"/>
+      <c r="A17" s="371"/>
+      <c r="B17" s="371"/>
+      <c r="C17" s="371"/>
+      <c r="D17" s="371"/>
+      <c r="E17" s="371"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="392"/>
-      <c r="B18" s="392"/>
-      <c r="C18" s="392"/>
-      <c r="D18" s="392"/>
-      <c r="E18" s="392"/>
+      <c r="A18" s="371"/>
+      <c r="B18" s="371"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="32"/>
@@ -3844,10 +3847,10 @@
       <c r="G24" s="79"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="394" t="s">
+      <c r="A25" s="373" t="s">
         <v>460</v>
       </c>
-      <c r="B25" s="395"/>
+      <c r="B25" s="374"/>
       <c r="C25" s="24"/>
       <c r="D25" s="291">
         <v>-435318.34</v>
@@ -3856,10 +3859,10 @@
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="396" t="s">
+      <c r="A26" s="364" t="s">
         <v>461</v>
       </c>
-      <c r="B26" s="397"/>
+      <c r="B26" s="365"/>
       <c r="C26" s="24"/>
       <c r="D26" s="291">
         <v>0.81</v>
@@ -3887,10 +3890,10 @@
       <c r="H27" s="79"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="369" t="s">
+      <c r="A28" s="368" t="s">
         <v>313</v>
       </c>
-      <c r="B28" s="370"/>
+      <c r="B28" s="369"/>
       <c r="C28" s="24"/>
       <c r="D28" s="363">
         <v>1520000</v>
@@ -4095,7 +4098,7 @@
       <c r="A44" s="366" t="s">
         <v>466</v>
       </c>
-      <c r="B44" s="393"/>
+      <c r="B44" s="372"/>
       <c r="C44" s="112"/>
       <c r="D44" s="360">
         <v>42932619.280000001</v>
@@ -4110,7 +4113,7 @@
       <c r="A45" s="366" t="s">
         <v>498</v>
       </c>
-      <c r="B45" s="393"/>
+      <c r="B45" s="372"/>
       <c r="C45" s="112"/>
       <c r="D45" s="230">
         <v>4440609.5999999996</v>
@@ -4147,7 +4150,7 @@
       <c r="A48" s="366" t="s">
         <v>326</v>
       </c>
-      <c r="B48" s="393"/>
+      <c r="B48" s="372"/>
       <c r="C48" s="112"/>
       <c r="D48" s="360">
         <v>1212341.6499999999</v>
@@ -4160,7 +4163,7 @@
       <c r="A49" s="366" t="s">
         <v>341</v>
       </c>
-      <c r="B49" s="393"/>
+      <c r="B49" s="372"/>
       <c r="C49" s="112"/>
       <c r="D49" s="230">
         <v>1512500</v>
@@ -4173,7 +4176,7 @@
       <c r="A50" s="366" t="s">
         <v>351</v>
       </c>
-      <c r="B50" s="393"/>
+      <c r="B50" s="372"/>
       <c r="C50" s="112"/>
       <c r="D50" s="230">
         <v>5445000</v>
@@ -4383,10 +4386,10 @@
       <c r="E65" s="29"/>
     </row>
     <row r="66" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="369" t="s">
+      <c r="A66" s="368" t="s">
         <v>494</v>
       </c>
-      <c r="B66" s="370"/>
+      <c r="B66" s="369"/>
       <c r="C66" s="24"/>
       <c r="D66" s="359">
         <v>500000</v>
@@ -4394,10 +4397,10 @@
       <c r="E66" s="86"/>
     </row>
     <row r="67" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="369" t="s">
+      <c r="A67" s="368" t="s">
         <v>480</v>
       </c>
-      <c r="B67" s="370"/>
+      <c r="B67" s="369"/>
       <c r="C67" s="24"/>
       <c r="D67" s="359">
         <v>5138870</v>
@@ -4407,10 +4410,10 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="369" t="s">
+      <c r="A68" s="368" t="s">
         <v>340</v>
       </c>
-      <c r="B68" s="370"/>
+      <c r="B68" s="369"/>
       <c r="C68" s="24"/>
       <c r="D68" s="149">
         <v>150000</v>
@@ -4570,10 +4573,10 @@
       </c>
     </row>
     <row r="80" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="364" t="s">
+      <c r="A80" s="396" t="s">
         <v>510</v>
       </c>
-      <c r="B80" s="365"/>
+      <c r="B80" s="397"/>
       <c r="C80" s="109"/>
       <c r="D80" s="359">
         <v>2138870</v>
@@ -4657,10 +4660,10 @@
       </c>
     </row>
     <row r="87" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="364" t="s">
+      <c r="A87" s="396" t="s">
         <v>478</v>
       </c>
-      <c r="B87" s="365"/>
+      <c r="B87" s="397"/>
       <c r="C87" s="109"/>
       <c r="D87" s="359">
         <v>2138000</v>
@@ -4668,10 +4671,10 @@
       <c r="E87" s="156"/>
     </row>
     <row r="88" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="364" t="s">
+      <c r="A88" s="396" t="s">
         <v>479</v>
       </c>
-      <c r="B88" s="365"/>
+      <c r="B88" s="397"/>
       <c r="C88" s="109"/>
       <c r="D88" s="359">
         <v>2445000</v>
@@ -4732,10 +4735,10 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="364" t="s">
+      <c r="A93" s="396" t="s">
         <v>491</v>
       </c>
-      <c r="B93" s="365"/>
+      <c r="B93" s="397"/>
       <c r="C93" s="109"/>
       <c r="D93" s="359">
         <v>318165.87</v>
@@ -4996,10 +4999,10 @@
       </c>
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="369" t="s">
+      <c r="A117" s="368" t="s">
         <v>502</v>
       </c>
-      <c r="B117" s="370"/>
+      <c r="B117" s="369"/>
       <c r="C117" s="24"/>
       <c r="D117" s="360">
         <v>1114493.6200000001</v>
@@ -5009,10 +5012,10 @@
       </c>
     </row>
     <row r="118" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="369" t="s">
+      <c r="A118" s="368" t="s">
         <v>191</v>
       </c>
-      <c r="B118" s="370"/>
+      <c r="B118" s="369"/>
       <c r="C118" s="24"/>
       <c r="D118" s="230">
         <v>6056.84</v>
@@ -5023,10 +5026,10 @@
       </c>
     </row>
     <row r="119" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="369" t="s">
+      <c r="A119" s="368" t="s">
         <v>304</v>
       </c>
-      <c r="B119" s="370"/>
+      <c r="B119" s="369"/>
       <c r="C119" s="24"/>
       <c r="D119" s="230"/>
       <c r="E119" s="24" t="s">
@@ -5065,10 +5068,10 @@
       <c r="E122" s="52"/>
     </row>
     <row r="123" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="369" t="s">
+      <c r="A123" s="368" t="s">
         <v>463</v>
       </c>
-      <c r="B123" s="370"/>
+      <c r="B123" s="369"/>
       <c r="C123" s="24"/>
       <c r="D123" s="292">
         <v>5816279.9100000001</v>
@@ -5078,8 +5081,8 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="369"/>
-      <c r="B124" s="370"/>
+      <c r="A124" s="368"/>
+      <c r="B124" s="369"/>
       <c r="C124" s="24"/>
       <c r="D124" s="149"/>
       <c r="E124" s="86"/>
@@ -5146,10 +5149,10 @@
       <c r="E131" s="59"/>
     </row>
     <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="368" t="s">
+      <c r="A132" s="393" t="s">
         <v>469</v>
       </c>
-      <c r="B132" s="368"/>
+      <c r="B132" s="393"/>
       <c r="C132" s="24"/>
       <c r="D132" s="360">
         <f>2112165-920000</f>
@@ -5161,10 +5164,10 @@
       </c>
     </row>
     <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="368" t="s">
+      <c r="A133" s="393" t="s">
         <v>506</v>
       </c>
-      <c r="B133" s="368"/>
+      <c r="B133" s="393"/>
       <c r="C133" s="24"/>
       <c r="D133" s="360">
         <v>79063</v>
@@ -5335,24 +5338,24 @@
       <c r="E148" s="32"/>
     </row>
     <row r="149" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="371" t="s">
+      <c r="A149" s="386" t="s">
         <v>470</v>
       </c>
-      <c r="B149" s="372"/>
+      <c r="B149" s="387"/>
       <c r="C149" s="32"/>
       <c r="D149" s="32"/>
       <c r="E149" s="32"/>
     </row>
     <row r="150" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="373"/>
-      <c r="B150" s="374"/>
+      <c r="A150" s="388"/>
+      <c r="B150" s="389"/>
       <c r="C150" s="32"/>
       <c r="D150" s="32"/>
       <c r="E150" s="32"/>
     </row>
     <row r="151" spans="1:5" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="375"/>
-      <c r="B151" s="376"/>
+      <c r="A151" s="390"/>
+      <c r="B151" s="391"/>
       <c r="C151" s="32"/>
       <c r="D151" s="32"/>
       <c r="E151" s="32"/>
@@ -5627,10 +5630,10 @@
       <c r="F177" s="83"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="378" t="s">
+      <c r="A178" s="394" t="s">
         <v>296</v>
       </c>
-      <c r="B178" s="379"/>
+      <c r="B178" s="395"/>
       <c r="C178" s="6"/>
       <c r="D178" s="13"/>
       <c r="E178" s="37"/>
@@ -5902,16 +5905,16 @@
       <c r="F200" s="38"/>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A201" s="377" t="s">
+      <c r="A201" s="392" t="s">
         <v>17</v>
       </c>
-      <c r="B201" s="377"/>
-      <c r="C201" s="377"/>
+      <c r="B201" s="392"/>
+      <c r="C201" s="392"/>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A202" s="377"/>
-      <c r="B202" s="377"/>
-      <c r="C202" s="377"/>
+      <c r="A202" s="392"/>
+      <c r="B202" s="392"/>
+      <c r="C202" s="392"/>
     </row>
     <row r="203" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="71"/>
@@ -5938,6 +5941,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A149:B151"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A201:C202"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A178:B178"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A57:B57"/>
@@ -5954,68 +6019,6 @@
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A149:B151"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A201:C202"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A178:B178"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A118:B118"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A89:B89"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6055,27 +6058,27 @@
     <row r="1" spans="1:24" ht="182.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="411" t="s">
+      <c r="C1" s="406" t="s">
         <v>389</v>
       </c>
-      <c r="D1" s="412"/>
-      <c r="E1" s="412"/>
-      <c r="F1" s="412"/>
-      <c r="G1" s="412"/>
-      <c r="H1" s="412"/>
-      <c r="I1" s="412"/>
-      <c r="J1" s="412"/>
-      <c r="K1" s="412"/>
-      <c r="L1" s="412"/>
+      <c r="D1" s="407"/>
+      <c r="E1" s="407"/>
+      <c r="F1" s="407"/>
+      <c r="G1" s="407"/>
+      <c r="H1" s="407"/>
+      <c r="I1" s="407"/>
+      <c r="J1" s="407"/>
+      <c r="K1" s="407"/>
+      <c r="L1" s="407"/>
       <c r="M1" s="155"/>
-      <c r="N1" s="413" t="s">
+      <c r="N1" s="408" t="s">
         <v>318</v>
       </c>
-      <c r="O1" s="413"/>
-      <c r="P1" s="408">
+      <c r="O1" s="408"/>
+      <c r="P1" s="403">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="408"/>
+      <c r="Q1" s="403"/>
       <c r="R1" s="184"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -6089,35 +6092,35 @@
     <row r="2" spans="1:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="410" t="s">
+      <c r="C2" s="405" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="410"/>
-      <c r="E2" s="410"/>
+      <c r="D2" s="405"/>
+      <c r="E2" s="405"/>
       <c r="F2" s="155"/>
-      <c r="G2" s="405">
+      <c r="G2" s="402">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="405"/>
+      <c r="H2" s="402"/>
       <c r="I2" s="155" t="s">
         <v>277</v>
       </c>
       <c r="J2" s="155"/>
-      <c r="K2" s="405">
+      <c r="K2" s="402">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="405"/>
+      <c r="L2" s="402"/>
       <c r="M2" s="270"/>
       <c r="N2" s="271" t="s">
         <v>263</v>
       </c>
       <c r="O2" s="270"/>
-      <c r="P2" s="409">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="409"/>
+      <c r="P2" s="404">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="404"/>
       <c r="R2" s="185"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -6129,112 +6132,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="76.650000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="418" t="str">
+      <c r="A3" s="413" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  17/04, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="419"/>
-      <c r="C3" s="419"/>
-      <c r="D3" s="419"/>
-      <c r="E3" s="419"/>
-      <c r="F3" s="419"/>
-      <c r="G3" s="419"/>
-      <c r="H3" s="419"/>
-      <c r="I3" s="419"/>
-      <c r="J3" s="419"/>
-      <c r="K3" s="419"/>
-      <c r="L3" s="419"/>
-      <c r="M3" s="419"/>
-      <c r="N3" s="419"/>
-      <c r="O3" s="419"/>
-      <c r="P3" s="419"/>
-      <c r="Q3" s="419"/>
-      <c r="R3" s="419"/>
-      <c r="S3" s="419"/>
-      <c r="T3" s="420"/>
+      <c r="B3" s="414"/>
+      <c r="C3" s="414"/>
+      <c r="D3" s="414"/>
+      <c r="E3" s="414"/>
+      <c r="F3" s="414"/>
+      <c r="G3" s="414"/>
+      <c r="H3" s="414"/>
+      <c r="I3" s="414"/>
+      <c r="J3" s="414"/>
+      <c r="K3" s="414"/>
+      <c r="L3" s="414"/>
+      <c r="M3" s="414"/>
+      <c r="N3" s="414"/>
+      <c r="O3" s="414"/>
+      <c r="P3" s="414"/>
+      <c r="Q3" s="414"/>
+      <c r="R3" s="414"/>
+      <c r="S3" s="414"/>
+      <c r="T3" s="415"/>
       <c r="X3" s="40"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="421" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="423" t="s">
+      <c r="A4" s="416" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="418" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="423" t="s">
+      <c r="C4" s="418" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="423" t="s">
+      <c r="D4" s="418" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="406" t="s">
+      <c r="E4" s="398" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="423" t="s">
+      <c r="F4" s="418" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="425" t="s">
+      <c r="G4" s="420" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="406" t="s">
+      <c r="H4" s="398" t="s">
         <v>234</v>
       </c>
-      <c r="I4" s="406" t="s">
+      <c r="I4" s="398" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="406"/>
-      <c r="K4" s="406" t="s">
+      <c r="J4" s="398"/>
+      <c r="K4" s="398" t="s">
         <v>184</v>
       </c>
-      <c r="L4" s="406" t="s">
+      <c r="L4" s="398" t="s">
         <v>147</v>
       </c>
-      <c r="M4" s="406" t="s">
+      <c r="M4" s="398" t="s">
         <v>186</v>
       </c>
-      <c r="N4" s="406" t="s">
+      <c r="N4" s="398" t="s">
         <v>185</v>
       </c>
-      <c r="O4" s="406" t="s">
+      <c r="O4" s="398" t="s">
         <v>420</v>
       </c>
-      <c r="P4" s="414" t="s">
+      <c r="P4" s="409" t="s">
         <v>335</v>
       </c>
-      <c r="Q4" s="415"/>
-      <c r="R4" s="414" t="s">
+      <c r="Q4" s="410"/>
+      <c r="R4" s="409" t="s">
         <v>323</v>
       </c>
-      <c r="S4" s="415"/>
-      <c r="T4" s="406" t="s">
+      <c r="S4" s="410"/>
+      <c r="T4" s="398" t="s">
         <v>261</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="422"/>
-      <c r="B5" s="424"/>
-      <c r="C5" s="424"/>
-      <c r="D5" s="424"/>
-      <c r="E5" s="407"/>
-      <c r="F5" s="424"/>
-      <c r="G5" s="426"/>
-      <c r="H5" s="407"/>
-      <c r="I5" s="407"/>
-      <c r="J5" s="407"/>
-      <c r="K5" s="407"/>
-      <c r="L5" s="407"/>
-      <c r="M5" s="407"/>
-      <c r="N5" s="407"/>
-      <c r="O5" s="407"/>
-      <c r="P5" s="416" t="str">
+      <c r="A5" s="417"/>
+      <c r="B5" s="419"/>
+      <c r="C5" s="419"/>
+      <c r="D5" s="419"/>
+      <c r="E5" s="399"/>
+      <c r="F5" s="419"/>
+      <c r="G5" s="421"/>
+      <c r="H5" s="399"/>
+      <c r="I5" s="399"/>
+      <c r="J5" s="399"/>
+      <c r="K5" s="399"/>
+      <c r="L5" s="399"/>
+      <c r="M5" s="399"/>
+      <c r="N5" s="399"/>
+      <c r="O5" s="399"/>
+      <c r="P5" s="411" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  17/04</v>
       </c>
-      <c r="Q5" s="417"/>
-      <c r="R5" s="416"/>
-      <c r="S5" s="417"/>
-      <c r="T5" s="407"/>
+      <c r="Q5" s="412"/>
+      <c r="R5" s="411"/>
+      <c r="S5" s="412"/>
+      <c r="T5" s="399"/>
     </row>
     <row r="6" spans="1:24" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="204"/>
@@ -6283,11 +6286,11 @@
         <v>0</v>
       </c>
       <c r="O6" s="209"/>
-      <c r="P6" s="427">
+      <c r="P6" s="400">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>1518529.01</v>
       </c>
-      <c r="Q6" s="427"/>
+      <c r="Q6" s="400"/>
       <c r="R6" s="272">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>1564586.01</v>
@@ -6352,11 +6355,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="74"/>
-      <c r="P7" s="398">
+      <c r="P7" s="401">
         <f t="shared" si="2"/>
         <v>1542558.02</v>
       </c>
-      <c r="Q7" s="398"/>
+      <c r="Q7" s="401"/>
       <c r="R7" s="272">
         <f t="shared" si="3"/>
         <v>1589344.02</v>
@@ -6420,11 +6423,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="74"/>
-      <c r="P8" s="398">
+      <c r="P8" s="401">
         <f t="shared" si="2"/>
         <v>736705.03</v>
       </c>
-      <c r="Q8" s="398"/>
+      <c r="Q8" s="401"/>
       <c r="R8" s="272">
         <f t="shared" si="3"/>
         <v>759049.03</v>
@@ -6489,11 +6492,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="74"/>
-      <c r="P9" s="398">
+      <c r="P9" s="401">
         <f t="shared" si="2"/>
         <v>3222835.04</v>
       </c>
-      <c r="Q9" s="398"/>
+      <c r="Q9" s="401"/>
       <c r="R9" s="272">
         <f t="shared" si="3"/>
         <v>3320584.04</v>
@@ -6561,11 +6564,11 @@
         <v>0</v>
       </c>
       <c r="O10" s="74"/>
-      <c r="P10" s="398">
+      <c r="P10" s="401">
         <f t="shared" si="2"/>
         <v>744528.05</v>
       </c>
-      <c r="Q10" s="398"/>
+      <c r="Q10" s="401"/>
       <c r="R10" s="272">
         <f t="shared" si="3"/>
         <v>767110.05</v>
@@ -6631,11 +6634,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="74"/>
-      <c r="P11" s="398">
+      <c r="P11" s="401">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="398"/>
+      <c r="Q11" s="401"/>
       <c r="R11" s="272">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6702,11 +6705,11 @@
         <v>0</v>
       </c>
       <c r="O12" s="74"/>
-      <c r="P12" s="398">
+      <c r="P12" s="401">
         <f t="shared" si="2"/>
         <v>744299.07</v>
       </c>
-      <c r="Q12" s="398"/>
+      <c r="Q12" s="401"/>
       <c r="R12" s="272">
         <f t="shared" si="3"/>
         <v>766874.07</v>
@@ -6773,11 +6776,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="74"/>
-      <c r="P13" s="398">
+      <c r="P13" s="401">
         <f t="shared" si="2"/>
         <v>744514.08</v>
       </c>
-      <c r="Q13" s="398"/>
+      <c r="Q13" s="401"/>
       <c r="R13" s="272">
         <f t="shared" si="3"/>
         <v>767095.08</v>
@@ -6842,11 +6845,11 @@
         <v>379177.030424</v>
       </c>
       <c r="O14" s="74"/>
-      <c r="P14" s="398">
+      <c r="P14" s="401">
         <f t="shared" si="2"/>
         <v>3585790.09</v>
       </c>
-      <c r="Q14" s="398"/>
+      <c r="Q14" s="401"/>
       <c r="R14" s="272">
         <f t="shared" si="3"/>
         <v>3694547.09</v>
@@ -6910,11 +6913,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="74"/>
-      <c r="P15" s="398">
+      <c r="P15" s="401">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="398"/>
+      <c r="Q15" s="401"/>
       <c r="R15" s="272">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -6980,11 +6983,11 @@
         <v>0</v>
       </c>
       <c r="O16" s="36"/>
-      <c r="P16" s="398">
+      <c r="P16" s="401">
         <f t="shared" si="2"/>
         <v>744528.11</v>
       </c>
-      <c r="Q16" s="398"/>
+      <c r="Q16" s="401"/>
       <c r="R16" s="272">
         <f t="shared" si="3"/>
         <v>767110.11</v>
@@ -7048,11 +7051,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="74"/>
-      <c r="P17" s="398">
+      <c r="P17" s="401">
         <f t="shared" si="2"/>
         <v>4420303.12</v>
       </c>
-      <c r="Q17" s="398"/>
+      <c r="Q17" s="401"/>
       <c r="R17" s="272">
         <f t="shared" si="3"/>
         <v>4554371.12</v>
@@ -7119,11 +7122,11 @@
       <c r="O18" s="74">
         <v>91169.89</v>
       </c>
-      <c r="P18" s="398">
+      <c r="P18" s="401">
         <f t="shared" si="2"/>
         <v>850918.13</v>
       </c>
-      <c r="Q18" s="398"/>
+      <c r="Q18" s="401"/>
       <c r="R18" s="272">
         <f t="shared" si="3"/>
         <v>876726.13</v>
@@ -7187,11 +7190,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="74"/>
-      <c r="P19" s="398">
+      <c r="P19" s="401">
         <f t="shared" si="2"/>
         <v>720435.14</v>
       </c>
-      <c r="Q19" s="398"/>
+      <c r="Q19" s="401"/>
       <c r="R19" s="272">
         <f t="shared" si="3"/>
         <v>742286.14</v>
@@ -7258,11 +7261,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="74"/>
-      <c r="P20" s="398">
+      <c r="P20" s="401">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="398"/>
+      <c r="Q20" s="401"/>
       <c r="R20" s="272">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7327,11 +7330,11 @@
       </c>
       <c r="N21" s="74"/>
       <c r="O21" s="74"/>
-      <c r="P21" s="398">
+      <c r="P21" s="401">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="398"/>
+      <c r="Q21" s="401"/>
       <c r="R21" s="272">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7392,11 +7395,11 @@
         <v>0</v>
       </c>
       <c r="O22" s="74"/>
-      <c r="P22" s="398">
+      <c r="P22" s="401">
         <f t="shared" si="2"/>
         <v>2350329.17</v>
       </c>
-      <c r="Q22" s="398"/>
+      <c r="Q22" s="401"/>
       <c r="R22" s="272">
         <f t="shared" si="3"/>
         <v>2421615.17</v>
@@ -7462,11 +7465,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="88"/>
-      <c r="P23" s="398">
+      <c r="P23" s="401">
         <f t="shared" si="2"/>
         <v>736705.18</v>
       </c>
-      <c r="Q23" s="398"/>
+      <c r="Q23" s="401"/>
       <c r="R23" s="272">
         <f t="shared" si="3"/>
         <v>759049.18</v>
@@ -7532,11 +7535,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="88"/>
-      <c r="P24" s="398">
+      <c r="P24" s="401">
         <f t="shared" si="2"/>
         <v>744528.19</v>
       </c>
-      <c r="Q24" s="398"/>
+      <c r="Q24" s="401"/>
       <c r="R24" s="272">
         <f t="shared" si="3"/>
         <v>767110.19</v>
@@ -7599,11 +7602,11 @@
         <v>0</v>
       </c>
       <c r="O25" s="88"/>
-      <c r="P25" s="398">
+      <c r="P25" s="401">
         <f t="shared" si="2"/>
         <v>744528.2</v>
       </c>
-      <c r="Q25" s="398"/>
+      <c r="Q25" s="401"/>
       <c r="R25" s="272">
         <f t="shared" si="3"/>
         <v>767110.2</v>
@@ -7664,11 +7667,11 @@
         <v>0</v>
       </c>
       <c r="O26" s="88"/>
-      <c r="P26" s="398">
+      <c r="P26" s="401">
         <f t="shared" si="2"/>
         <v>1559335.21</v>
       </c>
-      <c r="Q26" s="398"/>
+      <c r="Q26" s="401"/>
       <c r="R26" s="272">
         <f t="shared" si="3"/>
         <v>1606630.21</v>
@@ -7737,11 +7740,11 @@
         <v>0</v>
       </c>
       <c r="O27" s="88"/>
-      <c r="P27" s="398">
+      <c r="P27" s="401">
         <f t="shared" si="2"/>
         <v>744528.22</v>
       </c>
-      <c r="Q27" s="398"/>
+      <c r="Q27" s="401"/>
       <c r="R27" s="272">
         <f t="shared" si="3"/>
         <v>767110.22</v>
@@ -7807,11 +7810,11 @@
         <v>0</v>
       </c>
       <c r="O28" s="88"/>
-      <c r="P28" s="398">
+      <c r="P28" s="401">
         <f t="shared" si="2"/>
         <v>767815.23</v>
       </c>
-      <c r="Q28" s="398"/>
+      <c r="Q28" s="401"/>
       <c r="R28" s="272">
         <f t="shared" si="3"/>
         <v>791103.23</v>
@@ -7877,11 +7880,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="88"/>
-      <c r="P29" s="398">
+      <c r="P29" s="401">
         <f t="shared" si="2"/>
         <v>744528.24</v>
       </c>
-      <c r="Q29" s="398"/>
+      <c r="Q29" s="401"/>
       <c r="R29" s="272">
         <f t="shared" si="3"/>
         <v>767110.24</v>
@@ -7948,11 +7951,11 @@
         <v>0</v>
       </c>
       <c r="O30" s="88"/>
-      <c r="P30" s="398">
+      <c r="P30" s="401">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="398"/>
+      <c r="Q30" s="401"/>
       <c r="R30" s="272">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8018,11 +8021,11 @@
         <v>0</v>
       </c>
       <c r="O31" s="88"/>
-      <c r="P31" s="398">
+      <c r="P31" s="401">
         <f t="shared" si="2"/>
         <v>752356.26</v>
       </c>
-      <c r="Q31" s="398"/>
+      <c r="Q31" s="401"/>
       <c r="R31" s="272">
         <f t="shared" si="3"/>
         <v>775175.26</v>
@@ -8089,11 +8092,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="88"/>
-      <c r="P32" s="398">
+      <c r="P32" s="401">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="398"/>
+      <c r="Q32" s="401"/>
       <c r="R32" s="272">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8159,11 +8162,11 @@
         <f>I33/2</f>
         <v>181520.91881999999</v>
       </c>
-      <c r="P33" s="398">
+      <c r="P33" s="401">
         <f t="shared" si="2"/>
         <v>923797.28</v>
       </c>
-      <c r="Q33" s="398"/>
+      <c r="Q33" s="401"/>
       <c r="R33" s="272">
         <f t="shared" si="3"/>
         <v>951816.28</v>
@@ -8229,11 +8232,11 @@
         <v>0</v>
       </c>
       <c r="O34" s="88"/>
-      <c r="P34" s="398">
+      <c r="P34" s="401">
         <f t="shared" si="2"/>
         <v>752351.29</v>
       </c>
-      <c r="Q34" s="398"/>
+      <c r="Q34" s="401"/>
       <c r="R34" s="272">
         <f t="shared" si="3"/>
         <v>775170.29</v>
@@ -8300,11 +8303,11 @@
         <v>0</v>
       </c>
       <c r="O35" s="88"/>
-      <c r="P35" s="398">
+      <c r="P35" s="401">
         <f t="shared" si="2"/>
         <v>751681.3</v>
       </c>
-      <c r="Q35" s="398"/>
+      <c r="Q35" s="401"/>
       <c r="R35" s="272">
         <f t="shared" si="3"/>
         <v>774480.3</v>
@@ -8368,11 +8371,11 @@
         <v>0</v>
       </c>
       <c r="O36" s="88"/>
-      <c r="P36" s="398">
+      <c r="P36" s="401">
         <f t="shared" si="2"/>
         <v>2643433.31</v>
       </c>
-      <c r="Q36" s="398"/>
+      <c r="Q36" s="401"/>
       <c r="R36" s="272">
         <f t="shared" si="3"/>
         <v>2723609.31</v>
@@ -8439,11 +8442,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="88"/>
-      <c r="P37" s="398">
+      <c r="P37" s="401">
         <f t="shared" si="2"/>
         <v>573720.31999999995</v>
       </c>
-      <c r="Q37" s="398"/>
+      <c r="Q37" s="401"/>
       <c r="R37" s="272">
         <f t="shared" si="3"/>
         <v>591121.31999999995</v>
@@ -8506,11 +8509,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="88"/>
-      <c r="P38" s="398">
+      <c r="P38" s="401">
         <f t="shared" ref="P38:P69" si="14">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="398"/>
+      <c r="Q38" s="401"/>
       <c r="R38" s="272">
         <f t="shared" ref="R38:R69" si="15">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8570,11 +8573,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="88"/>
-      <c r="P39" s="398">
+      <c r="P39" s="401">
         <f t="shared" si="14"/>
         <v>2473411.34</v>
       </c>
-      <c r="Q39" s="398"/>
+      <c r="Q39" s="401"/>
       <c r="R39" s="272">
         <f t="shared" si="15"/>
         <v>2548430.34</v>
@@ -8641,11 +8644,11 @@
         <v>0</v>
       </c>
       <c r="O40" s="88"/>
-      <c r="P40" s="398">
+      <c r="P40" s="401">
         <f t="shared" si="14"/>
         <v>736704.35</v>
       </c>
-      <c r="Q40" s="398"/>
+      <c r="Q40" s="401"/>
       <c r="R40" s="272">
         <f t="shared" si="15"/>
         <v>759049.35</v>
@@ -8713,11 +8716,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="88"/>
-      <c r="P41" s="398">
+      <c r="P41" s="401">
         <f t="shared" si="14"/>
         <v>748020.36</v>
       </c>
-      <c r="Q41" s="398"/>
+      <c r="Q41" s="401"/>
       <c r="R41" s="272">
         <f t="shared" si="15"/>
         <v>770708.36</v>
@@ -8780,11 +8783,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="88"/>
-      <c r="P42" s="398">
+      <c r="P42" s="401">
         <f t="shared" si="14"/>
         <v>1526106.37</v>
       </c>
-      <c r="Q42" s="398"/>
+      <c r="Q42" s="401"/>
       <c r="R42" s="272">
         <f t="shared" si="15"/>
         <v>1572393.37</v>
@@ -8850,11 +8853,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="88"/>
-      <c r="P43" s="398">
+      <c r="P43" s="401">
         <f t="shared" si="14"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="398"/>
+      <c r="Q43" s="401"/>
       <c r="R43" s="272">
         <f t="shared" si="15"/>
         <v>774480.38</v>
@@ -8922,11 +8925,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="88"/>
-      <c r="P44" s="398">
+      <c r="P44" s="401">
         <f t="shared" si="14"/>
         <v>872758.39</v>
       </c>
-      <c r="Q44" s="398"/>
+      <c r="Q44" s="401"/>
       <c r="R44" s="272">
         <f t="shared" si="15"/>
         <v>899229.39</v>
@@ -8993,11 +8996,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="88"/>
-      <c r="P45" s="398">
+      <c r="P45" s="401">
         <f t="shared" si="14"/>
         <v>728593.4</v>
       </c>
-      <c r="Q45" s="398"/>
+      <c r="Q45" s="401"/>
       <c r="R45" s="272">
         <f t="shared" si="15"/>
         <v>750692.4</v>
@@ -9061,11 +9064,11 @@
         <v>0</v>
       </c>
       <c r="O46" s="88"/>
-      <c r="P46" s="398">
+      <c r="P46" s="401">
         <f t="shared" si="14"/>
         <v>728882.41</v>
       </c>
-      <c r="Q46" s="398"/>
+      <c r="Q46" s="401"/>
       <c r="R46" s="272">
         <f t="shared" si="15"/>
         <v>750989.41</v>
@@ -9132,11 +9135,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="88"/>
-      <c r="P47" s="398">
+      <c r="P47" s="401">
         <f t="shared" si="14"/>
         <v>728882.42</v>
       </c>
-      <c r="Q47" s="398"/>
+      <c r="Q47" s="401"/>
       <c r="R47" s="272">
         <f t="shared" si="15"/>
         <v>750989.42</v>
@@ -9204,11 +9207,11 @@
         <v>0</v>
       </c>
       <c r="O48" s="88"/>
-      <c r="P48" s="398">
+      <c r="P48" s="401">
         <f t="shared" si="14"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="398"/>
+      <c r="Q48" s="401"/>
       <c r="R48" s="272">
         <f t="shared" si="15"/>
         <v>699669.43</v>
@@ -9272,11 +9275,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="88"/>
-      <c r="P49" s="398">
+      <c r="P49" s="401">
         <f t="shared" si="14"/>
         <v>895905.44</v>
       </c>
-      <c r="Q49" s="398"/>
+      <c r="Q49" s="401"/>
       <c r="R49" s="272">
         <f t="shared" si="15"/>
         <v>923078.44</v>
@@ -9342,11 +9345,11 @@
         <v>395312.22320800001</v>
       </c>
       <c r="O50" s="88"/>
-      <c r="P50" s="398">
+      <c r="P50" s="401">
         <f t="shared" si="14"/>
         <v>1987415.45</v>
       </c>
-      <c r="Q50" s="398"/>
+      <c r="Q50" s="401"/>
       <c r="R50" s="272">
         <f t="shared" si="15"/>
         <v>2047694.45</v>
@@ -9410,11 +9413,11 @@
         <v>0</v>
       </c>
       <c r="O51" s="88"/>
-      <c r="P51" s="398">
+      <c r="P51" s="401">
         <f t="shared" si="14"/>
         <v>1451367.46</v>
       </c>
-      <c r="Q51" s="398"/>
+      <c r="Q51" s="401"/>
       <c r="R51" s="272">
         <f t="shared" si="15"/>
         <v>1495387.46</v>
@@ -9479,11 +9482,11 @@
         <v>0</v>
       </c>
       <c r="O52" s="88"/>
-      <c r="P52" s="398">
+      <c r="P52" s="401">
         <f t="shared" si="14"/>
         <v>3158183.47</v>
       </c>
-      <c r="Q52" s="398"/>
+      <c r="Q52" s="401"/>
       <c r="R52" s="272">
         <f t="shared" si="15"/>
         <v>3253971.47</v>
@@ -9554,11 +9557,11 @@
         <f>I53*0.1</f>
         <v>36304.183764000001</v>
       </c>
-      <c r="P53" s="398">
+      <c r="P53" s="401">
         <f t="shared" si="14"/>
         <v>1125839.48</v>
       </c>
-      <c r="Q53" s="398"/>
+      <c r="Q53" s="401"/>
       <c r="R53" s="272">
         <f t="shared" si="15"/>
         <v>1159986.48</v>
@@ -9623,11 +9626,11 @@
         <v>0</v>
       </c>
       <c r="O54" s="88"/>
-      <c r="P54" s="398">
+      <c r="P54" s="401">
         <f t="shared" si="14"/>
         <v>728882.49</v>
       </c>
-      <c r="Q54" s="398"/>
+      <c r="Q54" s="401"/>
       <c r="R54" s="272">
         <f t="shared" si="15"/>
         <v>750989.49</v>
@@ -9694,11 +9697,11 @@
         <v>0</v>
       </c>
       <c r="O55" s="88"/>
-      <c r="P55" s="398">
+      <c r="P55" s="401">
         <f t="shared" si="14"/>
         <v>728882.5</v>
       </c>
-      <c r="Q55" s="398"/>
+      <c r="Q55" s="401"/>
       <c r="R55" s="272">
         <f t="shared" si="15"/>
         <v>750990.5</v>
@@ -9764,11 +9767,11 @@
         <v>363041.83763999998</v>
       </c>
       <c r="O56" s="88"/>
-      <c r="P56" s="398">
+      <c r="P56" s="401">
         <f t="shared" si="14"/>
         <v>2245180.5099999998</v>
       </c>
-      <c r="Q56" s="398"/>
+      <c r="Q56" s="401"/>
       <c r="R56" s="272">
         <f t="shared" si="15"/>
         <v>2313277.5099999998</v>
@@ -9836,11 +9839,11 @@
         <v>0</v>
       </c>
       <c r="O57" s="88"/>
-      <c r="P57" s="398">
+      <c r="P57" s="401">
         <f t="shared" si="14"/>
         <v>712950.52</v>
       </c>
-      <c r="Q57" s="398"/>
+      <c r="Q57" s="401"/>
       <c r="R57" s="272">
         <f t="shared" si="15"/>
         <v>734574.52</v>
@@ -9905,11 +9908,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="88"/>
-      <c r="P58" s="398">
+      <c r="P58" s="401">
         <f t="shared" si="14"/>
         <v>3399941.53</v>
       </c>
-      <c r="Q58" s="398"/>
+      <c r="Q58" s="401"/>
       <c r="R58" s="272">
         <f t="shared" si="15"/>
         <v>3503062.53</v>
@@ -9974,11 +9977,11 @@
         <v>0</v>
       </c>
       <c r="O59" s="88"/>
-      <c r="P59" s="398">
+      <c r="P59" s="401">
         <f t="shared" si="14"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="398"/>
+      <c r="Q59" s="401"/>
       <c r="R59" s="272">
         <f t="shared" si="15"/>
         <v>774480.54</v>
@@ -10045,11 +10048,11 @@
         <v>0</v>
       </c>
       <c r="O60" s="88"/>
-      <c r="P60" s="398">
+      <c r="P60" s="401">
         <f t="shared" si="14"/>
         <v>728882.55</v>
       </c>
-      <c r="Q60" s="398"/>
+      <c r="Q60" s="401"/>
       <c r="R60" s="272">
         <f t="shared" si="15"/>
         <v>750990.55</v>
@@ -10120,11 +10123,11 @@
         <f>(I61*0.1)*2</f>
         <v>72608.367528000002</v>
       </c>
-      <c r="P61" s="398">
+      <c r="P61" s="401">
         <f t="shared" si="14"/>
         <v>1225512.56</v>
       </c>
-      <c r="Q61" s="398"/>
+      <c r="Q61" s="401"/>
       <c r="R61" s="272">
         <f t="shared" si="15"/>
         <v>1262682.56</v>
@@ -10189,11 +10192,11 @@
         <v>0</v>
       </c>
       <c r="O62" s="88"/>
-      <c r="P62" s="398">
+      <c r="P62" s="401">
         <f t="shared" si="14"/>
         <v>1526567.57</v>
       </c>
-      <c r="Q62" s="398"/>
+      <c r="Q62" s="401"/>
       <c r="R62" s="272">
         <f t="shared" si="15"/>
         <v>1572868.57</v>
@@ -10257,11 +10260,11 @@
         <v>0</v>
       </c>
       <c r="O63" s="88"/>
-      <c r="P63" s="398">
+      <c r="P63" s="401">
         <f t="shared" si="14"/>
         <v>728882.58</v>
       </c>
-      <c r="Q63" s="398"/>
+      <c r="Q63" s="401"/>
       <c r="R63" s="272">
         <f t="shared" si="15"/>
         <v>750990.58</v>
@@ -10325,11 +10328,11 @@
         <v>0</v>
       </c>
       <c r="O64" s="88"/>
-      <c r="P64" s="398">
+      <c r="P64" s="401">
         <f t="shared" si="14"/>
         <v>691468.59</v>
       </c>
-      <c r="Q64" s="398"/>
+      <c r="Q64" s="401"/>
       <c r="R64" s="272">
         <f t="shared" si="15"/>
         <v>712441.59</v>
@@ -10396,11 +10399,11 @@
         <v>0</v>
       </c>
       <c r="O65" s="88"/>
-      <c r="P65" s="398">
+      <c r="P65" s="401">
         <f t="shared" si="14"/>
         <v>750827.6</v>
       </c>
-      <c r="Q65" s="398"/>
+      <c r="Q65" s="401"/>
       <c r="R65" s="272">
         <f t="shared" si="15"/>
         <v>773600.6</v>
@@ -10468,11 +10471,11 @@
         <v>0</v>
       </c>
       <c r="O66" s="88"/>
-      <c r="P66" s="398">
+      <c r="P66" s="401">
         <f t="shared" si="14"/>
         <v>751038.61</v>
       </c>
-      <c r="Q66" s="398"/>
+      <c r="Q66" s="401"/>
       <c r="R66" s="272">
         <f t="shared" si="15"/>
         <v>773818.61</v>
@@ -10543,11 +10546,11 @@
         <f>I67/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P67" s="398">
+      <c r="P67" s="401">
         <f t="shared" si="14"/>
         <v>921295.62</v>
       </c>
-      <c r="Q67" s="398"/>
+      <c r="Q67" s="401"/>
       <c r="R67" s="272">
         <f t="shared" si="15"/>
         <v>949239.62</v>
@@ -10612,11 +10615,11 @@
         <v>0</v>
       </c>
       <c r="O68" s="88"/>
-      <c r="P68" s="398">
+      <c r="P68" s="401">
         <f t="shared" si="14"/>
         <v>751681.63</v>
       </c>
-      <c r="Q68" s="398"/>
+      <c r="Q68" s="401"/>
       <c r="R68" s="272">
         <f t="shared" si="15"/>
         <v>774480.63</v>
@@ -10684,11 +10687,11 @@
         <v>0</v>
       </c>
       <c r="O69" s="88"/>
-      <c r="P69" s="398">
+      <c r="P69" s="401">
         <f t="shared" si="14"/>
         <v>706943.64</v>
       </c>
-      <c r="Q69" s="398"/>
+      <c r="Q69" s="401"/>
       <c r="R69" s="272">
         <f t="shared" si="15"/>
         <v>728385.64</v>
@@ -10756,11 +10759,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="88"/>
-      <c r="P70" s="398">
+      <c r="P70" s="401">
         <f t="shared" ref="P70:P101" si="22">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="398"/>
+      <c r="Q70" s="401"/>
       <c r="R70" s="272">
         <f t="shared" ref="R70:R101" si="23">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10824,11 +10827,11 @@
         <v>0</v>
       </c>
       <c r="O71" s="88"/>
-      <c r="P71" s="398">
+      <c r="P71" s="401">
         <f t="shared" si="22"/>
         <v>728882.66</v>
       </c>
-      <c r="Q71" s="398"/>
+      <c r="Q71" s="401"/>
       <c r="R71" s="272">
         <f t="shared" si="23"/>
         <v>750990.66</v>
@@ -10893,11 +10896,11 @@
         <v>0</v>
       </c>
       <c r="O72" s="88"/>
-      <c r="P72" s="398">
+      <c r="P72" s="401">
         <f t="shared" si="22"/>
         <v>1518273.67</v>
       </c>
-      <c r="Q72" s="398"/>
+      <c r="Q72" s="401"/>
       <c r="R72" s="272">
         <f t="shared" si="23"/>
         <v>1564323.67</v>
@@ -10962,11 +10965,11 @@
         <v>363041.83763999998</v>
       </c>
       <c r="O73" s="88"/>
-      <c r="P73" s="398">
+      <c r="P73" s="401">
         <f t="shared" si="22"/>
         <v>4559265.68</v>
       </c>
-      <c r="Q73" s="398"/>
+      <c r="Q73" s="401"/>
       <c r="R73" s="272">
         <f t="shared" si="23"/>
         <v>4697548.68</v>
@@ -11029,11 +11032,11 @@
         <v>0</v>
       </c>
       <c r="O74" s="36"/>
-      <c r="P74" s="398">
+      <c r="P74" s="401">
         <f t="shared" si="22"/>
         <v>658475.68999999994</v>
       </c>
-      <c r="Q74" s="398"/>
+      <c r="Q74" s="401"/>
       <c r="R74" s="272">
         <f t="shared" si="23"/>
         <v>678447.69</v>
@@ -11099,11 +11102,11 @@
         <v>0</v>
       </c>
       <c r="O75" s="88"/>
-      <c r="P75" s="398">
+      <c r="P75" s="401">
         <f t="shared" si="22"/>
         <v>1372860.7</v>
       </c>
-      <c r="Q75" s="398"/>
+      <c r="Q75" s="401"/>
       <c r="R75" s="272">
         <f t="shared" si="23"/>
         <v>1414500.7</v>
@@ -11167,11 +11170,11 @@
         <v>0</v>
       </c>
       <c r="O76" s="88"/>
-      <c r="P76" s="398">
+      <c r="P76" s="401">
         <f t="shared" si="22"/>
         <v>4028209.71</v>
       </c>
-      <c r="Q76" s="398"/>
+      <c r="Q76" s="401"/>
       <c r="R76" s="272">
         <f t="shared" si="23"/>
         <v>4150385.71</v>
@@ -11237,11 +11240,11 @@
         <v>0</v>
       </c>
       <c r="O77" s="88"/>
-      <c r="P77" s="398">
+      <c r="P77" s="401">
         <f t="shared" si="22"/>
         <v>690051.72</v>
       </c>
-      <c r="Q77" s="398"/>
+      <c r="Q77" s="401"/>
       <c r="R77" s="272">
         <f t="shared" si="23"/>
         <v>710981.72</v>
@@ -11308,11 +11311,11 @@
         <v>0</v>
       </c>
       <c r="O78" s="88"/>
-      <c r="P78" s="398">
+      <c r="P78" s="401">
         <f t="shared" si="22"/>
         <v>711343.73</v>
       </c>
-      <c r="Q78" s="398"/>
+      <c r="Q78" s="401"/>
       <c r="R78" s="272">
         <f t="shared" si="23"/>
         <v>732919.73</v>
@@ -11376,11 +11379,11 @@
         <v>0</v>
       </c>
       <c r="O79" s="88"/>
-      <c r="P79" s="398">
+      <c r="P79" s="401">
         <f t="shared" si="22"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="398"/>
+      <c r="Q79" s="401"/>
       <c r="R79" s="272">
         <f t="shared" si="23"/>
         <v>766168.74</v>
@@ -11447,11 +11450,11 @@
         <f>I80/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P80" s="398">
+      <c r="P80" s="401">
         <f t="shared" si="22"/>
         <v>884796.75</v>
       </c>
-      <c r="Q80" s="398"/>
+      <c r="Q80" s="401"/>
       <c r="R80" s="272">
         <f t="shared" si="23"/>
         <v>911633.75</v>
@@ -11518,11 +11521,11 @@
         <v>0</v>
       </c>
       <c r="O81" s="88"/>
-      <c r="P81" s="398">
+      <c r="P81" s="401">
         <f t="shared" si="22"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="398"/>
+      <c r="Q81" s="401"/>
       <c r="R81" s="272">
         <f t="shared" si="23"/>
         <v>774480.76</v>
@@ -11585,11 +11588,11 @@
         <v>0</v>
       </c>
       <c r="O82" s="88"/>
-      <c r="P82" s="398">
+      <c r="P82" s="401">
         <f t="shared" si="22"/>
         <v>854048.77</v>
       </c>
-      <c r="Q82" s="398"/>
+      <c r="Q82" s="401"/>
       <c r="R82" s="272">
         <f t="shared" si="23"/>
         <v>879952.77</v>
@@ -11655,11 +11658,11 @@
         <v>0</v>
       </c>
       <c r="O83" s="88"/>
-      <c r="P83" s="398">
+      <c r="P83" s="401">
         <f t="shared" si="22"/>
         <v>751480.78</v>
       </c>
-      <c r="Q83" s="398"/>
+      <c r="Q83" s="401"/>
       <c r="R83" s="272">
         <f t="shared" si="23"/>
         <v>774273.78</v>
@@ -11726,11 +11729,11 @@
         <v>0</v>
       </c>
       <c r="O84" s="88"/>
-      <c r="P84" s="398">
+      <c r="P84" s="401">
         <f t="shared" si="22"/>
         <v>1089017.79</v>
       </c>
-      <c r="Q84" s="398"/>
+      <c r="Q84" s="401"/>
       <c r="R84" s="272">
         <f t="shared" si="23"/>
         <v>1122048.79</v>
@@ -11799,11 +11802,11 @@
         <v>0</v>
       </c>
       <c r="O85" s="88"/>
-      <c r="P85" s="398">
+      <c r="P85" s="401">
         <f t="shared" si="22"/>
         <v>728063.8</v>
       </c>
-      <c r="Q85" s="398"/>
+      <c r="Q85" s="401"/>
       <c r="R85" s="272">
         <f t="shared" si="23"/>
         <v>750146.8</v>
@@ -11870,11 +11873,11 @@
         <v>0</v>
       </c>
       <c r="O86" s="88"/>
-      <c r="P86" s="398">
+      <c r="P86" s="401">
         <f t="shared" si="22"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="398"/>
+      <c r="Q86" s="401"/>
       <c r="R86" s="272">
         <f t="shared" si="23"/>
         <v>774480.81</v>
@@ -11940,11 +11943,11 @@
         <v>0</v>
       </c>
       <c r="O87" s="74"/>
-      <c r="P87" s="398">
+      <c r="P87" s="401">
         <f t="shared" si="22"/>
         <v>682667.82</v>
       </c>
-      <c r="Q87" s="398"/>
+      <c r="Q87" s="401"/>
       <c r="R87" s="272">
         <f t="shared" si="23"/>
         <v>703373.82</v>
@@ -12011,11 +12014,11 @@
         <v>0</v>
       </c>
       <c r="O88" s="88"/>
-      <c r="P88" s="398">
+      <c r="P88" s="401">
         <f t="shared" si="22"/>
         <v>752351.83</v>
       </c>
-      <c r="Q88" s="398"/>
+      <c r="Q88" s="401"/>
       <c r="R88" s="272">
         <f t="shared" si="23"/>
         <v>775171.83</v>
@@ -12078,11 +12081,11 @@
         <v>0</v>
       </c>
       <c r="O89" s="88"/>
-      <c r="P89" s="398">
+      <c r="P89" s="401">
         <f t="shared" si="22"/>
         <v>752351.84</v>
       </c>
-      <c r="Q89" s="398"/>
+      <c r="Q89" s="401"/>
       <c r="R89" s="272">
         <f t="shared" si="23"/>
         <v>775171.84</v>
@@ -12146,11 +12149,11 @@
         <v>0</v>
       </c>
       <c r="O90" s="88"/>
-      <c r="P90" s="398">
+      <c r="P90" s="401">
         <f t="shared" si="22"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="398"/>
+      <c r="Q90" s="401"/>
       <c r="R90" s="272">
         <f t="shared" si="23"/>
         <v>799417.85</v>
@@ -12218,11 +12221,11 @@
         <v>387244.62681599997</v>
       </c>
       <c r="O91" s="88"/>
-      <c r="P91" s="398">
+      <c r="P91" s="401">
         <f t="shared" si="22"/>
         <v>1240577.8600000001</v>
       </c>
-      <c r="Q91" s="398"/>
+      <c r="Q91" s="401"/>
       <c r="R91" s="272">
         <f t="shared" si="23"/>
         <v>1278205.8600000001</v>
@@ -12288,11 +12291,11 @@
         <v>0</v>
       </c>
       <c r="O92" s="88"/>
-      <c r="P92" s="398">
+      <c r="P92" s="401">
         <f t="shared" si="22"/>
         <v>752351.87</v>
       </c>
-      <c r="Q92" s="398"/>
+      <c r="Q92" s="401"/>
       <c r="R92" s="272">
         <f t="shared" si="23"/>
         <v>775171.87</v>
@@ -12356,11 +12359,11 @@
         <v>0</v>
       </c>
       <c r="O93" s="88"/>
-      <c r="P93" s="398">
+      <c r="P93" s="401">
         <f t="shared" si="22"/>
         <v>775884.88</v>
       </c>
-      <c r="Q93" s="398"/>
+      <c r="Q93" s="401"/>
       <c r="R93" s="272">
         <f t="shared" si="23"/>
         <v>799417.88</v>
@@ -12423,11 +12426,11 @@
         <v>0</v>
       </c>
       <c r="O94" s="88"/>
-      <c r="P94" s="398">
+      <c r="P94" s="401">
         <f t="shared" si="22"/>
         <v>752351.89</v>
       </c>
-      <c r="Q94" s="398"/>
+      <c r="Q94" s="401"/>
       <c r="R94" s="272">
         <f t="shared" si="23"/>
         <v>775171.89</v>
@@ -12493,11 +12496,11 @@
         <v>0</v>
       </c>
       <c r="O95" s="88"/>
-      <c r="P95" s="398">
+      <c r="P95" s="401">
         <f t="shared" si="22"/>
         <v>743876.9</v>
       </c>
-      <c r="Q95" s="398"/>
+      <c r="Q95" s="401"/>
       <c r="R95" s="272">
         <f t="shared" si="23"/>
         <v>766439.9</v>
@@ -12563,11 +12566,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="88"/>
-      <c r="P96" s="398">
+      <c r="P96" s="401">
         <f t="shared" si="22"/>
         <v>752351.91</v>
       </c>
-      <c r="Q96" s="398"/>
+      <c r="Q96" s="401"/>
       <c r="R96" s="272">
         <f t="shared" si="23"/>
         <v>775171.91</v>
@@ -12636,11 +12639,11 @@
         <f>1780*100</f>
         <v>178000</v>
       </c>
-      <c r="P97" s="398">
+      <c r="P97" s="401">
         <f t="shared" si="22"/>
         <v>1840080.92</v>
       </c>
-      <c r="Q97" s="398"/>
+      <c r="Q97" s="401"/>
       <c r="R97" s="272">
         <f t="shared" si="23"/>
         <v>1895891.92</v>
@@ -12706,11 +12709,11 @@
         <v>0</v>
       </c>
       <c r="O98" s="60"/>
-      <c r="P98" s="398">
+      <c r="P98" s="401">
         <f t="shared" si="22"/>
         <v>238871.93</v>
       </c>
-      <c r="Q98" s="398"/>
+      <c r="Q98" s="401"/>
       <c r="R98" s="272">
         <f t="shared" si="23"/>
         <v>246117.93</v>
@@ -12777,11 +12780,11 @@
         <v>0</v>
       </c>
       <c r="O99" s="60"/>
-      <c r="P99" s="398">
+      <c r="P99" s="401">
         <f t="shared" si="22"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="398"/>
+      <c r="Q99" s="401"/>
       <c r="R99" s="272">
         <f t="shared" si="23"/>
         <v>799418.94</v>
@@ -12847,11 +12850,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="88"/>
-      <c r="P100" s="398">
+      <c r="P100" s="401">
         <f t="shared" si="22"/>
         <v>4049080.95</v>
       </c>
-      <c r="Q100" s="398"/>
+      <c r="Q100" s="401"/>
       <c r="R100" s="272">
         <f t="shared" si="23"/>
         <v>4171890.95</v>
@@ -12914,11 +12917,11 @@
         <v>0</v>
       </c>
       <c r="O101" s="88"/>
-      <c r="P101" s="398">
+      <c r="P101" s="401">
         <f t="shared" si="22"/>
         <v>752388.96</v>
       </c>
-      <c r="Q101" s="398"/>
+      <c r="Q101" s="401"/>
       <c r="R101" s="272">
         <f t="shared" si="23"/>
         <v>775209.96</v>
@@ -12984,11 +12987,11 @@
         <v>0</v>
       </c>
       <c r="O102" s="88"/>
-      <c r="P102" s="398">
+      <c r="P102" s="401">
         <f t="shared" ref="P102:P133" si="32">ROUND(SUM(G102:O102),0) + S102</f>
         <v>752269.97</v>
       </c>
-      <c r="Q102" s="398"/>
+      <c r="Q102" s="401"/>
       <c r="R102" s="272">
         <f t="shared" ref="R102:R133" si="33">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>775086.97</v>
@@ -13054,11 +13057,11 @@
         <v>0</v>
       </c>
       <c r="O103" s="88"/>
-      <c r="P103" s="398">
+      <c r="P103" s="401">
         <f t="shared" si="32"/>
         <v>752350.98</v>
       </c>
-      <c r="Q103" s="398"/>
+      <c r="Q103" s="401"/>
       <c r="R103" s="272">
         <f t="shared" si="33"/>
         <v>775170.98</v>
@@ -13122,11 +13125,11 @@
         <v>0</v>
       </c>
       <c r="O104" s="88"/>
-      <c r="P104" s="398">
+      <c r="P104" s="401">
         <f t="shared" si="32"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="398"/>
+      <c r="Q104" s="401"/>
       <c r="R104" s="272">
         <f t="shared" si="33"/>
         <v>799418.99</v>
@@ -13192,11 +13195,11 @@
         <v>0</v>
       </c>
       <c r="O105" s="88"/>
-      <c r="P105" s="398">
+      <c r="P105" s="401">
         <f t="shared" si="32"/>
         <v>752351</v>
       </c>
-      <c r="Q105" s="398"/>
+      <c r="Q105" s="401"/>
       <c r="R105" s="272">
         <f t="shared" si="33"/>
         <v>775171</v>
@@ -13259,11 +13262,11 @@
         <v>0</v>
       </c>
       <c r="O106" s="88"/>
-      <c r="P106" s="398">
+      <c r="P106" s="401">
         <f t="shared" si="32"/>
         <v>752351.01</v>
       </c>
-      <c r="Q106" s="398"/>
+      <c r="Q106" s="401"/>
       <c r="R106" s="272">
         <f t="shared" si="33"/>
         <v>775171.01</v>
@@ -13326,11 +13329,11 @@
         <v>0</v>
       </c>
       <c r="O107" s="88"/>
-      <c r="P107" s="398">
+      <c r="P107" s="401">
         <f t="shared" si="32"/>
         <v>775118.02</v>
       </c>
-      <c r="Q107" s="398"/>
+      <c r="Q107" s="401"/>
       <c r="R107" s="272">
         <f t="shared" si="33"/>
         <v>798628.02</v>
@@ -13396,11 +13399,11 @@
         <v>0</v>
       </c>
       <c r="O108" s="88"/>
-      <c r="P108" s="398">
+      <c r="P108" s="401">
         <f t="shared" si="32"/>
         <v>728092.03</v>
       </c>
-      <c r="Q108" s="398"/>
+      <c r="Q108" s="401"/>
       <c r="R108" s="272">
         <f t="shared" si="33"/>
         <v>750176.03</v>
@@ -13464,11 +13467,11 @@
         <v>0</v>
       </c>
       <c r="O109" s="88"/>
-      <c r="P109" s="398">
+      <c r="P109" s="401">
         <f t="shared" si="32"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="398"/>
+      <c r="Q109" s="401"/>
       <c r="R109" s="272">
         <f t="shared" si="33"/>
         <v>791106.04</v>
@@ -13534,11 +13537,11 @@
         <v>0</v>
       </c>
       <c r="O110" s="88"/>
-      <c r="P110" s="398">
+      <c r="P110" s="401">
         <f t="shared" si="32"/>
         <v>705414.05</v>
       </c>
-      <c r="Q110" s="398"/>
+      <c r="Q110" s="401"/>
       <c r="R110" s="272">
         <f t="shared" si="33"/>
         <v>726810.05</v>
@@ -13607,11 +13610,11 @@
         <v>270455.26692913822</v>
       </c>
       <c r="O111" s="88"/>
-      <c r="P111" s="398">
+      <c r="P111" s="401">
         <f t="shared" si="32"/>
         <v>1769526.06</v>
       </c>
-      <c r="Q111" s="398"/>
+      <c r="Q111" s="401"/>
       <c r="R111" s="272">
         <f t="shared" si="33"/>
         <v>1823197.06</v>
@@ -13677,11 +13680,11 @@
         <v>0</v>
       </c>
       <c r="O112" s="88"/>
-      <c r="P112" s="398">
+      <c r="P112" s="401">
         <f t="shared" si="32"/>
         <v>766866.07</v>
       </c>
-      <c r="Q112" s="398"/>
+      <c r="Q112" s="401"/>
       <c r="R112" s="272">
         <f t="shared" si="33"/>
         <v>790126.07</v>
@@ -13747,11 +13750,11 @@
         <v>0</v>
       </c>
       <c r="O113" s="88"/>
-      <c r="P113" s="398">
+      <c r="P113" s="401">
         <f t="shared" si="32"/>
         <v>721059.08</v>
       </c>
-      <c r="Q113" s="398"/>
+      <c r="Q113" s="401"/>
       <c r="R113" s="272">
         <f t="shared" si="33"/>
         <v>742930.08</v>
@@ -13814,11 +13817,11 @@
         <v>0</v>
       </c>
       <c r="O114" s="88"/>
-      <c r="P114" s="398">
+      <c r="P114" s="401">
         <f t="shared" si="32"/>
         <v>1511441.09</v>
       </c>
-      <c r="Q114" s="398"/>
+      <c r="Q114" s="401"/>
       <c r="R114" s="272">
         <f t="shared" si="33"/>
         <v>1557284.09</v>
@@ -13884,11 +13887,11 @@
         <v>0</v>
       </c>
       <c r="O115" s="88"/>
-      <c r="P115" s="398">
+      <c r="P115" s="401">
         <f t="shared" si="32"/>
         <v>1524957.1</v>
       </c>
-      <c r="Q115" s="398"/>
+      <c r="Q115" s="401"/>
       <c r="R115" s="272">
         <f t="shared" si="33"/>
         <v>1571210.1</v>
@@ -13956,11 +13959,11 @@
         <v>0</v>
       </c>
       <c r="O116" s="88"/>
-      <c r="P116" s="398">
+      <c r="P116" s="401">
         <f t="shared" si="32"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="398"/>
+      <c r="Q116" s="401"/>
       <c r="R116" s="272">
         <f t="shared" si="33"/>
         <v>774482.11</v>
@@ -14023,11 +14026,11 @@
         <v>0</v>
       </c>
       <c r="O117" s="88"/>
-      <c r="P117" s="398">
+      <c r="P117" s="401">
         <f t="shared" si="32"/>
         <v>725114.12</v>
       </c>
-      <c r="Q117" s="398"/>
+      <c r="Q117" s="401"/>
       <c r="R117" s="272">
         <f t="shared" si="33"/>
         <v>747108.12</v>
@@ -14093,11 +14096,11 @@
         <v>0</v>
       </c>
       <c r="O118" s="88"/>
-      <c r="P118" s="398">
+      <c r="P118" s="401">
         <f t="shared" si="32"/>
         <v>744528.13</v>
       </c>
-      <c r="Q118" s="398"/>
+      <c r="Q118" s="401"/>
       <c r="R118" s="272">
         <f t="shared" si="33"/>
         <v>767111.13</v>
@@ -14160,11 +14163,11 @@
         <v>0</v>
       </c>
       <c r="O119" s="88"/>
-      <c r="P119" s="398">
+      <c r="P119" s="401">
         <f t="shared" si="32"/>
         <v>728882.14</v>
       </c>
-      <c r="Q119" s="398"/>
+      <c r="Q119" s="401"/>
       <c r="R119" s="272">
         <f t="shared" si="33"/>
         <v>750990.14</v>
@@ -14228,11 +14231,11 @@
         <v>0</v>
       </c>
       <c r="O120" s="88"/>
-      <c r="P120" s="398">
+      <c r="P120" s="401">
         <f t="shared" si="32"/>
         <v>849222.15</v>
       </c>
-      <c r="Q120" s="398"/>
+      <c r="Q120" s="401"/>
       <c r="R120" s="272">
         <f t="shared" si="33"/>
         <v>874980.15</v>
@@ -14299,11 +14302,11 @@
         <v>0</v>
       </c>
       <c r="O121" s="88"/>
-      <c r="P121" s="398">
+      <c r="P121" s="401">
         <f t="shared" si="32"/>
         <v>803799.16</v>
       </c>
-      <c r="Q121" s="398"/>
+      <c r="Q121" s="401"/>
       <c r="R121" s="272">
         <f t="shared" si="33"/>
         <v>828179.16</v>
@@ -14366,11 +14369,11 @@
         <v>0</v>
       </c>
       <c r="O122" s="88"/>
-      <c r="P122" s="398">
+      <c r="P122" s="401">
         <f t="shared" si="32"/>
         <v>854048.17</v>
       </c>
-      <c r="Q122" s="398"/>
+      <c r="Q122" s="401"/>
       <c r="R122" s="272">
         <f t="shared" si="33"/>
         <v>879952.17</v>
@@ -14437,11 +14440,11 @@
         <v>0</v>
       </c>
       <c r="O123" s="88"/>
-      <c r="P123" s="398">
+      <c r="P123" s="401">
         <f t="shared" si="32"/>
         <v>856559.18</v>
       </c>
-      <c r="Q123" s="398"/>
+      <c r="Q123" s="401"/>
       <c r="R123" s="272">
         <f t="shared" si="33"/>
         <v>882540.18</v>
@@ -14507,11 +14510,11 @@
         <v>0</v>
       </c>
       <c r="O124" s="88"/>
-      <c r="P124" s="398">
+      <c r="P124" s="401">
         <f t="shared" si="32"/>
         <v>827956.19</v>
       </c>
-      <c r="Q124" s="398"/>
+      <c r="Q124" s="401"/>
       <c r="R124" s="272">
         <f t="shared" si="33"/>
         <v>853069.19</v>
@@ -14578,11 +14581,11 @@
         <v>0</v>
       </c>
       <c r="O125" s="88"/>
-      <c r="P125" s="398">
+      <c r="P125" s="401">
         <f t="shared" si="32"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="398"/>
+      <c r="Q125" s="401"/>
       <c r="R125" s="272">
         <f t="shared" si="33"/>
         <v>782793.2</v>
@@ -14649,11 +14652,11 @@
         <v>0</v>
       </c>
       <c r="O126" s="88"/>
-      <c r="P126" s="398">
+      <c r="P126" s="401">
         <f t="shared" si="32"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="398"/>
+      <c r="Q126" s="401"/>
       <c r="R126" s="272">
         <f t="shared" si="33"/>
         <v>782793.21</v>
@@ -14719,11 +14722,11 @@
         <v>0</v>
       </c>
       <c r="O127" s="74"/>
-      <c r="P127" s="398">
+      <c r="P127" s="401">
         <f t="shared" si="32"/>
         <v>736705.22</v>
       </c>
-      <c r="Q127" s="398"/>
+      <c r="Q127" s="401"/>
       <c r="R127" s="272">
         <f t="shared" si="33"/>
         <v>759050.22</v>
@@ -14787,11 +14790,11 @@
         <v>0</v>
       </c>
       <c r="O128" s="88"/>
-      <c r="P128" s="398">
+      <c r="P128" s="401">
         <f t="shared" si="32"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="398"/>
+      <c r="Q128" s="401"/>
       <c r="R128" s="272">
         <f t="shared" si="33"/>
         <v>782793.23</v>
@@ -14857,11 +14860,11 @@
         <v>0</v>
       </c>
       <c r="O129" s="88"/>
-      <c r="P129" s="398">
+      <c r="P129" s="401">
         <f t="shared" si="32"/>
         <v>736705.24</v>
       </c>
-      <c r="Q129" s="398"/>
+      <c r="Q129" s="401"/>
       <c r="R129" s="272">
         <f t="shared" si="33"/>
         <v>759051.24</v>
@@ -14925,11 +14928,11 @@
         <v>0</v>
       </c>
       <c r="O130" s="88"/>
-      <c r="P130" s="398">
+      <c r="P130" s="401">
         <f t="shared" si="32"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="398"/>
+      <c r="Q130" s="401"/>
       <c r="R130" s="272">
         <f t="shared" si="33"/>
         <v>782793.25</v>
@@ -14996,11 +14999,11 @@
         <v>0</v>
       </c>
       <c r="O131" s="88"/>
-      <c r="P131" s="398">
+      <c r="P131" s="401">
         <f t="shared" si="32"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="398"/>
+      <c r="Q131" s="401"/>
       <c r="R131" s="272">
         <f t="shared" si="33"/>
         <v>782793.26</v>
@@ -15061,11 +15064,11 @@
         <v>0</v>
       </c>
       <c r="O132" s="88"/>
-      <c r="P132" s="398">
+      <c r="P132" s="401">
         <f t="shared" si="32"/>
         <v>1680082.27</v>
       </c>
-      <c r="Q132" s="398"/>
+      <c r="Q132" s="401"/>
       <c r="R132" s="272">
         <f t="shared" si="33"/>
         <v>1731040.27</v>
@@ -15132,11 +15135,11 @@
         <v>339029.8362611382</v>
       </c>
       <c r="O133" s="88"/>
-      <c r="P133" s="398">
+      <c r="P133" s="401">
         <f t="shared" si="32"/>
         <v>9465986.2799999993</v>
       </c>
-      <c r="Q133" s="398"/>
+      <c r="Q133" s="401"/>
       <c r="R133" s="272">
         <f t="shared" si="33"/>
         <v>9753091.2799999993</v>
@@ -15199,11 +15202,11 @@
         <v>0</v>
       </c>
       <c r="O134" s="88"/>
-      <c r="P134" s="398">
+      <c r="P134" s="401">
         <f t="shared" ref="P134:P144" si="39">ROUND(SUM(G134:O134),0) + S134</f>
         <v>854048.29</v>
       </c>
-      <c r="Q134" s="398"/>
+      <c r="Q134" s="401"/>
       <c r="R134" s="272">
         <f t="shared" ref="R134:R144" si="40">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>879953.29</v>
@@ -15269,11 +15272,11 @@
         <v>0</v>
       </c>
       <c r="O135" s="88"/>
-      <c r="P135" s="398">
+      <c r="P135" s="401">
         <f t="shared" si="39"/>
         <v>847809.3</v>
       </c>
-      <c r="Q135" s="398"/>
+      <c r="Q135" s="401"/>
       <c r="R135" s="272">
         <f t="shared" si="40"/>
         <v>873524.3</v>
@@ -15340,11 +15343,11 @@
         <v>0</v>
       </c>
       <c r="O136" s="88"/>
-      <c r="P136" s="398">
+      <c r="P136" s="401">
         <f t="shared" si="39"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="398"/>
+      <c r="Q136" s="401"/>
       <c r="R136" s="272">
         <f t="shared" si="40"/>
         <v>907478.31</v>
@@ -15410,11 +15413,11 @@
         <v>0</v>
       </c>
       <c r="O137" s="88"/>
-      <c r="P137" s="398">
+      <c r="P137" s="401">
         <f t="shared" si="39"/>
         <v>846226.32</v>
       </c>
-      <c r="Q137" s="398"/>
+      <c r="Q137" s="401"/>
       <c r="R137" s="272">
         <f t="shared" si="40"/>
         <v>871893.32</v>
@@ -15481,11 +15484,11 @@
         <v>0</v>
       </c>
       <c r="O138" s="88"/>
-      <c r="P138" s="398">
+      <c r="P138" s="401">
         <f t="shared" si="39"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="398"/>
+      <c r="Q138" s="401"/>
       <c r="R138" s="272">
         <f t="shared" si="40"/>
         <v>932415.33</v>
@@ -15551,11 +15554,11 @@
         <v>0</v>
       </c>
       <c r="O139" s="88"/>
-      <c r="P139" s="398">
+      <c r="P139" s="401">
         <f t="shared" si="39"/>
         <v>791466.34</v>
       </c>
-      <c r="Q139" s="398"/>
+      <c r="Q139" s="401"/>
       <c r="R139" s="272">
         <f t="shared" si="40"/>
         <v>815473.34</v>
@@ -15621,11 +15624,11 @@
         <v>0</v>
       </c>
       <c r="O140" s="88"/>
-      <c r="P140" s="398">
+      <c r="P140" s="401">
         <f t="shared" si="39"/>
         <v>854048.35</v>
       </c>
-      <c r="Q140" s="398"/>
+      <c r="Q140" s="401"/>
       <c r="R140" s="272">
         <f t="shared" si="40"/>
         <v>879953.35</v>
@@ -15689,11 +15692,11 @@
         <v>0</v>
       </c>
       <c r="O141" s="88"/>
-      <c r="P141" s="398">
+      <c r="P141" s="401">
         <f t="shared" si="39"/>
         <v>3751757.36</v>
       </c>
-      <c r="Q141" s="398"/>
+      <c r="Q141" s="401"/>
       <c r="R141" s="272">
         <f t="shared" si="40"/>
         <v>3865549.36</v>
@@ -15759,11 +15762,11 @@
         <v>0</v>
       </c>
       <c r="O142" s="88"/>
-      <c r="P142" s="398">
+      <c r="P142" s="401">
         <f t="shared" si="39"/>
         <v>799288.37</v>
       </c>
-      <c r="Q142" s="398"/>
+      <c r="Q142" s="401"/>
       <c r="R142" s="272">
         <f t="shared" si="40"/>
         <v>823532.37</v>
@@ -15826,11 +15829,11 @@
         <v>0</v>
       </c>
       <c r="O143" s="88"/>
-      <c r="P143" s="398">
+      <c r="P143" s="401">
         <f t="shared" si="39"/>
         <v>885340.38</v>
       </c>
-      <c r="Q143" s="398"/>
+      <c r="Q143" s="401"/>
       <c r="R143" s="272">
         <f t="shared" si="40"/>
         <v>912194.38</v>
@@ -15896,11 +15899,11 @@
         <v>0</v>
       </c>
       <c r="O144" s="88"/>
-      <c r="P144" s="398">
+      <c r="P144" s="401">
         <f t="shared" si="39"/>
         <v>880691.39</v>
       </c>
-      <c r="Q144" s="398"/>
+      <c r="Q144" s="401"/>
       <c r="R144" s="272">
         <f t="shared" si="40"/>
         <v>907404.39</v>
@@ -15940,8 +15943,8 @@
       <c r="M145" s="74"/>
       <c r="N145" s="74"/>
       <c r="O145" s="88"/>
-      <c r="P145" s="398"/>
-      <c r="Q145" s="398"/>
+      <c r="P145" s="401"/>
+      <c r="Q145" s="401"/>
       <c r="R145" s="273"/>
       <c r="S145" s="13">
         <f t="shared" si="41"/>
@@ -15975,8 +15978,8 @@
       <c r="M146" s="74"/>
       <c r="N146" s="74"/>
       <c r="O146" s="88"/>
-      <c r="P146" s="398"/>
-      <c r="Q146" s="398"/>
+      <c r="P146" s="401"/>
+      <c r="Q146" s="401"/>
       <c r="R146" s="273"/>
       <c r="S146" s="13">
         <f t="shared" si="41"/>
@@ -16003,8 +16006,8 @@
       <c r="M147" s="74"/>
       <c r="N147" s="74"/>
       <c r="O147" s="88"/>
-      <c r="P147" s="398"/>
-      <c r="Q147" s="398"/>
+      <c r="P147" s="401"/>
+      <c r="Q147" s="401"/>
       <c r="R147" s="273"/>
       <c r="S147" s="13">
         <f t="shared" si="41"/>
@@ -16031,8 +16034,8 @@
       <c r="M148" s="74"/>
       <c r="N148" s="74"/>
       <c r="O148" s="88"/>
-      <c r="P148" s="398"/>
-      <c r="Q148" s="398"/>
+      <c r="P148" s="401"/>
+      <c r="Q148" s="401"/>
       <c r="R148" s="273"/>
       <c r="S148" s="13">
         <f t="shared" si="41"/>
@@ -16092,11 +16095,11 @@
         <v>246252.47775313823</v>
       </c>
       <c r="O149" s="88"/>
-      <c r="P149" s="398">
+      <c r="P149" s="401">
         <f t="shared" ref="P149:P158" si="49">ROUND(SUM(G149:O149),0) + S149</f>
         <v>882923.46</v>
       </c>
-      <c r="Q149" s="398"/>
+      <c r="Q149" s="401"/>
       <c r="R149" s="272">
         <f t="shared" ref="R149:R158" si="50">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>909704.46</v>
@@ -16157,11 +16160,11 @@
         <v>0</v>
       </c>
       <c r="O150" s="88"/>
-      <c r="P150" s="398">
+      <c r="P150" s="401">
         <f t="shared" si="49"/>
         <v>707760.55</v>
       </c>
-      <c r="Q150" s="398"/>
+      <c r="Q150" s="401"/>
       <c r="R150" s="272">
         <f t="shared" si="50"/>
         <v>729228.55</v>
@@ -16228,11 +16231,11 @@
         <v>0</v>
       </c>
       <c r="O151" s="74"/>
-      <c r="P151" s="398">
+      <c r="P151" s="401">
         <f t="shared" si="49"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="398"/>
+      <c r="Q151" s="401"/>
       <c r="R151" s="272">
         <f t="shared" si="50"/>
         <v>782794.58</v>
@@ -16296,11 +16299,11 @@
         <v>0</v>
       </c>
       <c r="O152" s="74"/>
-      <c r="P152" s="398">
+      <c r="P152" s="401">
         <f t="shared" si="49"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="398"/>
+      <c r="Q152" s="401"/>
       <c r="R152" s="272">
         <f t="shared" si="50"/>
         <v>782794.59</v>
@@ -16364,11 +16367,11 @@
         <v>0</v>
       </c>
       <c r="O153" s="74"/>
-      <c r="P153" s="398">
+      <c r="P153" s="401">
         <f t="shared" si="49"/>
         <v>759750.63</v>
       </c>
-      <c r="Q153" s="398"/>
+      <c r="Q153" s="401"/>
       <c r="R153" s="272">
         <f t="shared" si="50"/>
         <v>782795.63</v>
@@ -16432,11 +16435,11 @@
         <v>0</v>
       </c>
       <c r="O154" s="74"/>
-      <c r="P154" s="398">
+      <c r="P154" s="401">
         <f t="shared" si="49"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="398"/>
+      <c r="Q154" s="401"/>
       <c r="R154" s="272">
         <f t="shared" si="50"/>
         <v>766170.68</v>
@@ -16499,11 +16502,11 @@
         <v>0</v>
       </c>
       <c r="O155" s="74"/>
-      <c r="P155" s="398">
+      <c r="P155" s="401">
         <f t="shared" si="49"/>
         <v>736704.73</v>
       </c>
-      <c r="Q155" s="398"/>
+      <c r="Q155" s="401"/>
       <c r="R155" s="272">
         <f t="shared" si="50"/>
         <v>759050.73</v>
@@ -16569,11 +16572,11 @@
         <v>0</v>
       </c>
       <c r="O156" s="74"/>
-      <c r="P156" s="398">
+      <c r="P156" s="401">
         <f t="shared" si="49"/>
         <v>736704.75</v>
       </c>
-      <c r="Q156" s="398"/>
+      <c r="Q156" s="401"/>
       <c r="R156" s="272">
         <f t="shared" si="50"/>
         <v>759050.75</v>
@@ -16640,11 +16643,11 @@
         <v>0</v>
       </c>
       <c r="O157" s="74"/>
-      <c r="P157" s="398">
+      <c r="P157" s="401">
         <f t="shared" si="49"/>
         <v>759750.76</v>
       </c>
-      <c r="Q157" s="398"/>
+      <c r="Q157" s="401"/>
       <c r="R157" s="272">
         <f t="shared" si="50"/>
         <v>782795.76</v>
@@ -16708,11 +16711,11 @@
         <v>0</v>
       </c>
       <c r="O158" s="74"/>
-      <c r="P158" s="398">
+      <c r="P158" s="401">
         <f t="shared" si="49"/>
         <v>783953.04</v>
       </c>
-      <c r="Q158" s="398"/>
+      <c r="Q158" s="401"/>
       <c r="R158" s="272">
         <f t="shared" si="50"/>
         <v>807732.04</v>
@@ -16745,8 +16748,8 @@
       <c r="M159" s="22"/>
       <c r="N159" s="22"/>
       <c r="O159" s="74"/>
-      <c r="P159" s="403"/>
-      <c r="Q159" s="403"/>
+      <c r="P159" s="426"/>
+      <c r="Q159" s="426"/>
       <c r="R159" s="183"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -16767,8 +16770,8 @@
       <c r="M160" s="194"/>
       <c r="N160" s="194"/>
       <c r="O160" s="269"/>
-      <c r="P160" s="404"/>
-      <c r="Q160" s="404"/>
+      <c r="P160" s="427"/>
+      <c r="Q160" s="427"/>
       <c r="R160" s="186"/>
       <c r="S160" s="13"/>
       <c r="T160" s="195"/>
@@ -16822,150 +16825,312 @@
         <f t="shared" si="54"/>
         <v>890374.81218400015</v>
       </c>
-      <c r="P161" s="401">
+      <c r="P161" s="424">
         <f>SUM(P6:P160)</f>
         <v>169388305.07000002</v>
       </c>
-      <c r="Q161" s="402"/>
+      <c r="Q161" s="425"/>
       <c r="R161" s="187">
         <f>SUM(R6:R160)</f>
         <v>174525973.07000002</v>
       </c>
-      <c r="S161" s="401"/>
-      <c r="T161" s="402"/>
+      <c r="S161" s="424"/>
+      <c r="T161" s="425"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B162" s="399" t="s">
+      <c r="B162" s="422" t="s">
         <v>324</v>
       </c>
-      <c r="C162" s="399"/>
-      <c r="D162" s="399"/>
-      <c r="E162" s="399"/>
-      <c r="F162" s="399"/>
-      <c r="G162" s="399"/>
-      <c r="H162" s="399"/>
-      <c r="I162" s="399"/>
-      <c r="J162" s="399"/>
-      <c r="K162" s="399"/>
-      <c r="L162" s="399"/>
-      <c r="M162" s="399"/>
-      <c r="N162" s="399"/>
-      <c r="O162" s="399"/>
-      <c r="P162" s="399"/>
-      <c r="Q162" s="399"/>
-      <c r="R162" s="399"/>
-      <c r="S162" s="399"/>
-      <c r="T162" s="399"/>
+      <c r="C162" s="422"/>
+      <c r="D162" s="422"/>
+      <c r="E162" s="422"/>
+      <c r="F162" s="422"/>
+      <c r="G162" s="422"/>
+      <c r="H162" s="422"/>
+      <c r="I162" s="422"/>
+      <c r="J162" s="422"/>
+      <c r="K162" s="422"/>
+      <c r="L162" s="422"/>
+      <c r="M162" s="422"/>
+      <c r="N162" s="422"/>
+      <c r="O162" s="422"/>
+      <c r="P162" s="422"/>
+      <c r="Q162" s="422"/>
+      <c r="R162" s="422"/>
+      <c r="S162" s="422"/>
+      <c r="T162" s="422"/>
     </row>
     <row r="163" spans="1:20" ht="49.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="400"/>
-      <c r="C163" s="400"/>
-      <c r="D163" s="400"/>
-      <c r="E163" s="400"/>
-      <c r="F163" s="400"/>
-      <c r="G163" s="400"/>
-      <c r="H163" s="400"/>
-      <c r="I163" s="400"/>
-      <c r="J163" s="400"/>
-      <c r="K163" s="400"/>
-      <c r="L163" s="400"/>
-      <c r="M163" s="400"/>
-      <c r="N163" s="400"/>
-      <c r="O163" s="400"/>
-      <c r="P163" s="400"/>
-      <c r="Q163" s="400"/>
-      <c r="R163" s="400"/>
-      <c r="S163" s="400"/>
-      <c r="T163" s="400"/>
+      <c r="B163" s="423"/>
+      <c r="C163" s="423"/>
+      <c r="D163" s="423"/>
+      <c r="E163" s="423"/>
+      <c r="F163" s="423"/>
+      <c r="G163" s="423"/>
+      <c r="H163" s="423"/>
+      <c r="I163" s="423"/>
+      <c r="J163" s="423"/>
+      <c r="K163" s="423"/>
+      <c r="L163" s="423"/>
+      <c r="M163" s="423"/>
+      <c r="N163" s="423"/>
+      <c r="O163" s="423"/>
+      <c r="P163" s="423"/>
+      <c r="Q163" s="423"/>
+      <c r="R163" s="423"/>
+      <c r="S163" s="423"/>
+      <c r="T163" s="423"/>
     </row>
     <row r="164" spans="1:20" ht="13.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B164" s="400" t="s">
+      <c r="B164" s="423" t="s">
         <v>262</v>
       </c>
-      <c r="C164" s="400"/>
-      <c r="D164" s="400"/>
-      <c r="E164" s="400"/>
-      <c r="F164" s="400"/>
-      <c r="G164" s="400"/>
-      <c r="H164" s="400"/>
-      <c r="I164" s="400"/>
-      <c r="J164" s="400"/>
-      <c r="K164" s="400"/>
-      <c r="L164" s="400"/>
-      <c r="M164" s="400"/>
-      <c r="N164" s="400"/>
-      <c r="O164" s="400"/>
-      <c r="P164" s="400"/>
-      <c r="Q164" s="400"/>
-      <c r="R164" s="400"/>
-      <c r="S164" s="400"/>
-      <c r="T164" s="400"/>
+      <c r="C164" s="423"/>
+      <c r="D164" s="423"/>
+      <c r="E164" s="423"/>
+      <c r="F164" s="423"/>
+      <c r="G164" s="423"/>
+      <c r="H164" s="423"/>
+      <c r="I164" s="423"/>
+      <c r="J164" s="423"/>
+      <c r="K164" s="423"/>
+      <c r="L164" s="423"/>
+      <c r="M164" s="423"/>
+      <c r="N164" s="423"/>
+      <c r="O164" s="423"/>
+      <c r="P164" s="423"/>
+      <c r="Q164" s="423"/>
+      <c r="R164" s="423"/>
+      <c r="S164" s="423"/>
+      <c r="T164" s="423"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="400"/>
-      <c r="C165" s="400"/>
-      <c r="D165" s="400"/>
-      <c r="E165" s="400"/>
-      <c r="F165" s="400"/>
-      <c r="G165" s="400"/>
-      <c r="H165" s="400"/>
-      <c r="I165" s="400"/>
-      <c r="J165" s="400"/>
-      <c r="K165" s="400"/>
-      <c r="L165" s="400"/>
-      <c r="M165" s="400"/>
-      <c r="N165" s="400"/>
-      <c r="O165" s="400"/>
-      <c r="P165" s="400"/>
-      <c r="Q165" s="400"/>
-      <c r="R165" s="400"/>
-      <c r="S165" s="400"/>
-      <c r="T165" s="400"/>
+      <c r="B165" s="423"/>
+      <c r="C165" s="423"/>
+      <c r="D165" s="423"/>
+      <c r="E165" s="423"/>
+      <c r="F165" s="423"/>
+      <c r="G165" s="423"/>
+      <c r="H165" s="423"/>
+      <c r="I165" s="423"/>
+      <c r="J165" s="423"/>
+      <c r="K165" s="423"/>
+      <c r="L165" s="423"/>
+      <c r="M165" s="423"/>
+      <c r="N165" s="423"/>
+      <c r="O165" s="423"/>
+      <c r="P165" s="423"/>
+      <c r="Q165" s="423"/>
+      <c r="R165" s="423"/>
+      <c r="S165" s="423"/>
+      <c r="T165" s="423"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B166" s="400"/>
-      <c r="C166" s="400"/>
-      <c r="D166" s="400"/>
-      <c r="E166" s="400"/>
-      <c r="F166" s="400"/>
-      <c r="G166" s="400"/>
-      <c r="H166" s="400"/>
-      <c r="I166" s="400"/>
-      <c r="J166" s="400"/>
-      <c r="K166" s="400"/>
-      <c r="L166" s="400"/>
-      <c r="M166" s="400"/>
-      <c r="N166" s="400"/>
-      <c r="O166" s="400"/>
-      <c r="P166" s="400"/>
-      <c r="Q166" s="400"/>
-      <c r="R166" s="400"/>
-      <c r="S166" s="400"/>
-      <c r="T166" s="400"/>
+      <c r="B166" s="423"/>
+      <c r="C166" s="423"/>
+      <c r="D166" s="423"/>
+      <c r="E166" s="423"/>
+      <c r="F166" s="423"/>
+      <c r="G166" s="423"/>
+      <c r="H166" s="423"/>
+      <c r="I166" s="423"/>
+      <c r="J166" s="423"/>
+      <c r="K166" s="423"/>
+      <c r="L166" s="423"/>
+      <c r="M166" s="423"/>
+      <c r="N166" s="423"/>
+      <c r="O166" s="423"/>
+      <c r="P166" s="423"/>
+      <c r="Q166" s="423"/>
+      <c r="R166" s="423"/>
+      <c r="S166" s="423"/>
+      <c r="T166" s="423"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="400"/>
-      <c r="C167" s="400"/>
-      <c r="D167" s="400"/>
-      <c r="E167" s="400"/>
-      <c r="F167" s="400"/>
-      <c r="G167" s="400"/>
-      <c r="H167" s="400"/>
-      <c r="I167" s="400"/>
-      <c r="J167" s="400"/>
-      <c r="K167" s="400"/>
-      <c r="L167" s="400"/>
-      <c r="M167" s="400"/>
-      <c r="N167" s="400"/>
-      <c r="O167" s="400"/>
-      <c r="P167" s="400"/>
-      <c r="Q167" s="400"/>
-      <c r="R167" s="400"/>
-      <c r="S167" s="400"/>
-      <c r="T167" s="400"/>
+      <c r="B167" s="423"/>
+      <c r="C167" s="423"/>
+      <c r="D167" s="423"/>
+      <c r="E167" s="423"/>
+      <c r="F167" s="423"/>
+      <c r="G167" s="423"/>
+      <c r="H167" s="423"/>
+      <c r="I167" s="423"/>
+      <c r="J167" s="423"/>
+      <c r="K167" s="423"/>
+      <c r="L167" s="423"/>
+      <c r="M167" s="423"/>
+      <c r="N167" s="423"/>
+      <c r="O167" s="423"/>
+      <c r="P167" s="423"/>
+      <c r="Q167" s="423"/>
+      <c r="R167" s="423"/>
+      <c r="S167" s="423"/>
+      <c r="T167" s="423"/>
     </row>
   </sheetData>
   <mergeCells count="186">
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="P6:Q6"/>
@@ -16990,168 +17155,6 @@
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -17166,7 +17169,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D69DBA-AA88-413A-80A7-A9BAAE7F2C32}">
-  <dimension ref="C2:N261"/>
+  <dimension ref="C2:N270"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="10.88671875" customWidth="1"/>
@@ -20006,8 +20009,147 @@
       <c r="I261" s="437"/>
       <c r="J261" s="438"/>
     </row>
+    <row r="263" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="264" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C264" s="350" t="s">
+        <v>159</v>
+      </c>
+      <c r="D264" s="351">
+        <f>D255+1</f>
+        <v>30</v>
+      </c>
+      <c r="E264" s="64"/>
+      <c r="F264" s="64"/>
+      <c r="G264" s="64"/>
+      <c r="H264" s="64"/>
+      <c r="I264" s="64"/>
+      <c r="J264" s="66"/>
+    </row>
+    <row r="265" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C265" s="352" t="s">
+        <v>160</v>
+      </c>
+      <c r="D265" s="353"/>
+      <c r="E265" s="220">
+        <v>45945</v>
+      </c>
+      <c r="F265" s="36"/>
+      <c r="G265" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H265" s="90"/>
+      <c r="I265" s="67"/>
+      <c r="J265" s="68"/>
+    </row>
+    <row r="266" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C266" s="352" t="s">
+        <v>161</v>
+      </c>
+      <c r="D266" s="353" t="s">
+        <v>162</v>
+      </c>
+      <c r="E266" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F266" s="36"/>
+      <c r="G266" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H266" s="428">
+        <v>102</v>
+      </c>
+      <c r="I266" s="428"/>
+      <c r="J266" s="429"/>
+    </row>
+    <row r="267" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C267" s="352" t="s">
+        <v>164</v>
+      </c>
+      <c r="D267" s="353"/>
+      <c r="E267" s="36"/>
+      <c r="F267" s="36"/>
+      <c r="G267" s="36"/>
+      <c r="H267" s="36"/>
+      <c r="I267" s="36"/>
+      <c r="J267" s="69"/>
+    </row>
+    <row r="268" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C268" s="430" t="s">
+        <v>518</v>
+      </c>
+      <c r="D268" s="431"/>
+      <c r="E268" s="431"/>
+      <c r="F268" s="431"/>
+      <c r="G268" s="431"/>
+      <c r="H268" s="431"/>
+      <c r="I268" s="431"/>
+      <c r="J268" s="432"/>
+    </row>
+    <row r="269" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C269" s="433"/>
+      <c r="D269" s="434"/>
+      <c r="E269" s="434"/>
+      <c r="F269" s="434"/>
+      <c r="G269" s="434"/>
+      <c r="H269" s="434"/>
+      <c r="I269" s="434"/>
+      <c r="J269" s="435"/>
+    </row>
+    <row r="270" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C270" s="436"/>
+      <c r="D270" s="437"/>
+      <c r="E270" s="437"/>
+      <c r="F270" s="437"/>
+      <c r="G270" s="437"/>
+      <c r="H270" s="437"/>
+      <c r="I270" s="437"/>
+      <c r="J270" s="438"/>
+    </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="59">
+    <mergeCell ref="H266:J266"/>
+    <mergeCell ref="C268:J270"/>
+    <mergeCell ref="H239:J239"/>
+    <mergeCell ref="C241:J243"/>
+    <mergeCell ref="C142:J144"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="C124:J126"/>
+    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="C133:J135"/>
+    <mergeCell ref="H140:J140"/>
+    <mergeCell ref="H149:J149"/>
+    <mergeCell ref="C151:J153"/>
+    <mergeCell ref="H158:J158"/>
+    <mergeCell ref="C160:J162"/>
+    <mergeCell ref="H167:J167"/>
+    <mergeCell ref="C169:J171"/>
+    <mergeCell ref="H176:J176"/>
+    <mergeCell ref="C178:J180"/>
+    <mergeCell ref="C115:J117"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="C97:J99"/>
+    <mergeCell ref="H104:J104"/>
+    <mergeCell ref="C106:J108"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="C88:J90"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="C70:J72"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="C79:J81"/>
+    <mergeCell ref="H86:J86"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="C61:J63"/>
+    <mergeCell ref="C52:J54"/>
+    <mergeCell ref="K3:N6"/>
+    <mergeCell ref="C7:J9"/>
+    <mergeCell ref="C16:J18"/>
+    <mergeCell ref="C25:J27"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="C34:J36"/>
+    <mergeCell ref="K7:N9"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C43:J45"/>
+    <mergeCell ref="H32:J32"/>
     <mergeCell ref="H248:J248"/>
     <mergeCell ref="C250:J252"/>
     <mergeCell ref="H257:J257"/>
@@ -20024,47 +20166,6 @@
     <mergeCell ref="C214:J216"/>
     <mergeCell ref="H202:J202"/>
     <mergeCell ref="C204:J206"/>
-    <mergeCell ref="H59:J59"/>
-    <mergeCell ref="C61:J63"/>
-    <mergeCell ref="C52:J54"/>
-    <mergeCell ref="K3:N6"/>
-    <mergeCell ref="C7:J9"/>
-    <mergeCell ref="C16:J18"/>
-    <mergeCell ref="C25:J27"/>
-    <mergeCell ref="H50:J50"/>
-    <mergeCell ref="C34:J36"/>
-    <mergeCell ref="K7:N9"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="C43:J45"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="C88:J90"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="C70:J72"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="C79:J81"/>
-    <mergeCell ref="H86:J86"/>
-    <mergeCell ref="C115:J117"/>
-    <mergeCell ref="H95:J95"/>
-    <mergeCell ref="C97:J99"/>
-    <mergeCell ref="H104:J104"/>
-    <mergeCell ref="C106:J108"/>
-    <mergeCell ref="H113:J113"/>
-    <mergeCell ref="H239:J239"/>
-    <mergeCell ref="C241:J243"/>
-    <mergeCell ref="C142:J144"/>
-    <mergeCell ref="H122:J122"/>
-    <mergeCell ref="C124:J126"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="C133:J135"/>
-    <mergeCell ref="H140:J140"/>
-    <mergeCell ref="H149:J149"/>
-    <mergeCell ref="C151:J153"/>
-    <mergeCell ref="H158:J158"/>
-    <mergeCell ref="C160:J162"/>
-    <mergeCell ref="H167:J167"/>
-    <mergeCell ref="C169:J171"/>
-    <mergeCell ref="H176:J176"/>
-    <mergeCell ref="C178:J180"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BRISAS/EXPENSAS/2026/MARZO/BRISAS-MARZO.xlsx
+++ b/BRISAS/EXPENSAS/2026/MARZO/BRISAS-MARZO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\MARZO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CBFF74-0728-4484-A915-91F857FD4DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3E4C87-D0DB-4F96-A88D-3C61728003EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="523">
   <si>
     <t>Dpto.</t>
   </si>
@@ -1627,6 +1627,18 @@
   </si>
   <si>
     <t>Lote 92 transfririo 1.736.196,00 el 31/03 - HABLAR CON RO COMO DIVIDIR ESO, YA QUE PARTE VA PARA SU PLAN DE PAGO Y PARTE PARA SUS EXPENSAS</t>
+  </si>
+  <si>
+    <t>Deposito el 31/03 $1.518.300</t>
+  </si>
+  <si>
+    <t>Transfririo $311.000 y $689.000,17</t>
+  </si>
+  <si>
+    <t>PENDIENTE PARA ABRIL</t>
+  </si>
+  <si>
+    <t>Transfirio $1.250.000 el dia 31/03</t>
   </si>
 </sst>
 </file>
@@ -1885,7 +1897,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2117,6 +2129,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2516,7 +2534,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="453">
+  <cellXfs count="456">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -3003,16 +3021,19 @@
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3021,17 +3042,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3065,52 +3102,50 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="23" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3169,24 +3204,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3261,6 +3279,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3655,34 +3682,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="383"/>
-      <c r="B1" s="378" t="s">
+      <c r="A1" s="388"/>
+      <c r="B1" s="383" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="379"/>
-      <c r="D1" s="379"/>
-      <c r="E1" s="380"/>
+      <c r="C1" s="384"/>
+      <c r="D1" s="384"/>
+      <c r="E1" s="385"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="384"/>
-      <c r="B2" s="378" t="s">
+      <c r="A2" s="389"/>
+      <c r="B2" s="383" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="379"/>
-      <c r="D2" s="379"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="384"/>
+      <c r="D2" s="384"/>
+      <c r="E2" s="385"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="384"/>
-      <c r="B3" s="375" t="s">
+      <c r="A3" s="389"/>
+      <c r="B3" s="380" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="376"/>
-      <c r="D3" s="376"/>
-      <c r="E3" s="377"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="381"/>
+      <c r="E3" s="382"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="384"/>
+      <c r="A4" s="389"/>
       <c r="B4" s="47" t="s">
         <v>155</v>
       </c>
@@ -3691,7 +3718,7 @@
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="384"/>
+      <c r="A5" s="389"/>
       <c r="B5" s="50" t="s">
         <v>458</v>
       </c>
@@ -3700,7 +3727,7 @@
       <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="384"/>
+      <c r="A6" s="389"/>
       <c r="B6" s="51" t="s">
         <v>285</v>
       </c>
@@ -3709,7 +3736,7 @@
       <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="384"/>
+      <c r="A7" s="389"/>
       <c r="B7" s="51" t="s">
         <v>284</v>
       </c>
@@ -3718,36 +3745,36 @@
       <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="385"/>
-      <c r="B8" s="381" t="s">
+      <c r="A8" s="390"/>
+      <c r="B8" s="386" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="381"/>
-      <c r="D8" s="381"/>
-      <c r="E8" s="382"/>
+      <c r="C8" s="386"/>
+      <c r="D8" s="386"/>
+      <c r="E8" s="387"/>
     </row>
     <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="370" t="s">
+      <c r="A10" s="391" t="s">
         <v>457</v>
       </c>
-      <c r="B10" s="370"/>
-      <c r="C10" s="370"/>
-      <c r="D10" s="370"/>
-      <c r="E10" s="370"/>
+      <c r="B10" s="391"/>
+      <c r="C10" s="391"/>
+      <c r="D10" s="391"/>
+      <c r="E10" s="391"/>
     </row>
     <row r="11" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="370"/>
-      <c r="B11" s="370"/>
-      <c r="C11" s="370"/>
-      <c r="D11" s="370"/>
-      <c r="E11" s="370"/>
+      <c r="A11" s="391"/>
+      <c r="B11" s="391"/>
+      <c r="C11" s="391"/>
+      <c r="D11" s="391"/>
+      <c r="E11" s="391"/>
     </row>
     <row r="12" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="370"/>
-      <c r="B12" s="370"/>
-      <c r="C12" s="370"/>
-      <c r="D12" s="370"/>
-      <c r="E12" s="370"/>
+      <c r="A12" s="391"/>
+      <c r="B12" s="391"/>
+      <c r="C12" s="391"/>
+      <c r="D12" s="391"/>
+      <c r="E12" s="391"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="32"/>
@@ -3764,34 +3791,34 @@
       <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="371" t="s">
+      <c r="A15" s="392" t="s">
         <v>243</v>
       </c>
-      <c r="B15" s="371"/>
-      <c r="C15" s="371"/>
-      <c r="D15" s="371"/>
-      <c r="E15" s="371"/>
+      <c r="B15" s="392"/>
+      <c r="C15" s="392"/>
+      <c r="D15" s="392"/>
+      <c r="E15" s="392"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="371"/>
-      <c r="B16" s="371"/>
-      <c r="C16" s="371"/>
-      <c r="D16" s="371"/>
-      <c r="E16" s="371"/>
+      <c r="A16" s="392"/>
+      <c r="B16" s="392"/>
+      <c r="C16" s="392"/>
+      <c r="D16" s="392"/>
+      <c r="E16" s="392"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="371"/>
-      <c r="B17" s="371"/>
-      <c r="C17" s="371"/>
-      <c r="D17" s="371"/>
-      <c r="E17" s="371"/>
+      <c r="A17" s="392"/>
+      <c r="B17" s="392"/>
+      <c r="C17" s="392"/>
+      <c r="D17" s="392"/>
+      <c r="E17" s="392"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="371"/>
-      <c r="B18" s="371"/>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
+      <c r="A18" s="392"/>
+      <c r="B18" s="392"/>
+      <c r="C18" s="392"/>
+      <c r="D18" s="392"/>
+      <c r="E18" s="392"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="32"/>
@@ -3847,10 +3874,10 @@
       <c r="G24" s="79"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="373" t="s">
+      <c r="A25" s="394" t="s">
         <v>460</v>
       </c>
-      <c r="B25" s="374"/>
+      <c r="B25" s="395"/>
       <c r="C25" s="24"/>
       <c r="D25" s="291">
         <v>-435318.34</v>
@@ -3859,10 +3886,10 @@
       <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="364" t="s">
+      <c r="A26" s="396" t="s">
         <v>461</v>
       </c>
-      <c r="B26" s="365"/>
+      <c r="B26" s="397"/>
       <c r="C26" s="24"/>
       <c r="D26" s="291">
         <v>0.81</v>
@@ -3890,10 +3917,10 @@
       <c r="H27" s="79"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="368" t="s">
+      <c r="A28" s="369" t="s">
         <v>313</v>
       </c>
-      <c r="B28" s="369"/>
+      <c r="B28" s="370"/>
       <c r="C28" s="24"/>
       <c r="D28" s="363">
         <v>1520000</v>
@@ -4098,7 +4125,7 @@
       <c r="A44" s="366" t="s">
         <v>466</v>
       </c>
-      <c r="B44" s="372"/>
+      <c r="B44" s="393"/>
       <c r="C44" s="112"/>
       <c r="D44" s="360">
         <v>42932619.280000001</v>
@@ -4113,7 +4140,7 @@
       <c r="A45" s="366" t="s">
         <v>498</v>
       </c>
-      <c r="B45" s="372"/>
+      <c r="B45" s="393"/>
       <c r="C45" s="112"/>
       <c r="D45" s="230">
         <v>4440609.5999999996</v>
@@ -4150,7 +4177,7 @@
       <c r="A48" s="366" t="s">
         <v>326</v>
       </c>
-      <c r="B48" s="372"/>
+      <c r="B48" s="393"/>
       <c r="C48" s="112"/>
       <c r="D48" s="360">
         <v>1212341.6499999999</v>
@@ -4163,7 +4190,7 @@
       <c r="A49" s="366" t="s">
         <v>341</v>
       </c>
-      <c r="B49" s="372"/>
+      <c r="B49" s="393"/>
       <c r="C49" s="112"/>
       <c r="D49" s="230">
         <v>1512500</v>
@@ -4176,7 +4203,7 @@
       <c r="A50" s="366" t="s">
         <v>351</v>
       </c>
-      <c r="B50" s="372"/>
+      <c r="B50" s="393"/>
       <c r="C50" s="112"/>
       <c r="D50" s="230">
         <v>5445000</v>
@@ -4386,10 +4413,10 @@
       <c r="E65" s="29"/>
     </row>
     <row r="66" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="368" t="s">
+      <c r="A66" s="369" t="s">
         <v>494</v>
       </c>
-      <c r="B66" s="369"/>
+      <c r="B66" s="370"/>
       <c r="C66" s="24"/>
       <c r="D66" s="359">
         <v>500000</v>
@@ -4397,10 +4424,10 @@
       <c r="E66" s="86"/>
     </row>
     <row r="67" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="368" t="s">
+      <c r="A67" s="369" t="s">
         <v>480</v>
       </c>
-      <c r="B67" s="369"/>
+      <c r="B67" s="370"/>
       <c r="C67" s="24"/>
       <c r="D67" s="359">
         <v>5138870</v>
@@ -4410,10 +4437,10 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="368" t="s">
+      <c r="A68" s="369" t="s">
         <v>340</v>
       </c>
-      <c r="B68" s="369"/>
+      <c r="B68" s="370"/>
       <c r="C68" s="24"/>
       <c r="D68" s="149">
         <v>150000</v>
@@ -4573,10 +4600,10 @@
       </c>
     </row>
     <row r="80" spans="1:7" ht="31.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="396" t="s">
+      <c r="A80" s="364" t="s">
         <v>510</v>
       </c>
-      <c r="B80" s="397"/>
+      <c r="B80" s="365"/>
       <c r="C80" s="109"/>
       <c r="D80" s="359">
         <v>2138870</v>
@@ -4660,10 +4687,10 @@
       </c>
     </row>
     <row r="87" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="396" t="s">
+      <c r="A87" s="364" t="s">
         <v>478</v>
       </c>
-      <c r="B87" s="397"/>
+      <c r="B87" s="365"/>
       <c r="C87" s="109"/>
       <c r="D87" s="359">
         <v>2138000</v>
@@ -4671,10 +4698,10 @@
       <c r="E87" s="156"/>
     </row>
     <row r="88" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="396" t="s">
+      <c r="A88" s="364" t="s">
         <v>479</v>
       </c>
-      <c r="B88" s="397"/>
+      <c r="B88" s="365"/>
       <c r="C88" s="109"/>
       <c r="D88" s="359">
         <v>2445000</v>
@@ -4735,10 +4762,10 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="396" t="s">
+      <c r="A93" s="364" t="s">
         <v>491</v>
       </c>
-      <c r="B93" s="397"/>
+      <c r="B93" s="365"/>
       <c r="C93" s="109"/>
       <c r="D93" s="359">
         <v>318165.87</v>
@@ -4999,10 +5026,10 @@
       </c>
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="368" t="s">
+      <c r="A117" s="369" t="s">
         <v>502</v>
       </c>
-      <c r="B117" s="369"/>
+      <c r="B117" s="370"/>
       <c r="C117" s="24"/>
       <c r="D117" s="360">
         <v>1114493.6200000001</v>
@@ -5012,10 +5039,10 @@
       </c>
     </row>
     <row r="118" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="368" t="s">
+      <c r="A118" s="369" t="s">
         <v>191</v>
       </c>
-      <c r="B118" s="369"/>
+      <c r="B118" s="370"/>
       <c r="C118" s="24"/>
       <c r="D118" s="230">
         <v>6056.84</v>
@@ -5026,10 +5053,10 @@
       </c>
     </row>
     <row r="119" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="368" t="s">
+      <c r="A119" s="369" t="s">
         <v>304</v>
       </c>
-      <c r="B119" s="369"/>
+      <c r="B119" s="370"/>
       <c r="C119" s="24"/>
       <c r="D119" s="230"/>
       <c r="E119" s="24" t="s">
@@ -5068,10 +5095,10 @@
       <c r="E122" s="52"/>
     </row>
     <row r="123" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="368" t="s">
+      <c r="A123" s="369" t="s">
         <v>463</v>
       </c>
-      <c r="B123" s="369"/>
+      <c r="B123" s="370"/>
       <c r="C123" s="24"/>
       <c r="D123" s="292">
         <v>5816279.9100000001</v>
@@ -5081,8 +5108,8 @@
       </c>
     </row>
     <row r="124" spans="1:7" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="368"/>
-      <c r="B124" s="369"/>
+      <c r="A124" s="369"/>
+      <c r="B124" s="370"/>
       <c r="C124" s="24"/>
       <c r="D124" s="149"/>
       <c r="E124" s="86"/>
@@ -5149,10 +5176,10 @@
       <c r="E131" s="59"/>
     </row>
     <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="393" t="s">
+      <c r="A132" s="368" t="s">
         <v>469</v>
       </c>
-      <c r="B132" s="393"/>
+      <c r="B132" s="368"/>
       <c r="C132" s="24"/>
       <c r="D132" s="360">
         <f>2112165-920000</f>
@@ -5164,10 +5191,10 @@
       </c>
     </row>
     <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="393" t="s">
+      <c r="A133" s="368" t="s">
         <v>506</v>
       </c>
-      <c r="B133" s="393"/>
+      <c r="B133" s="368"/>
       <c r="C133" s="24"/>
       <c r="D133" s="360">
         <v>79063</v>
@@ -5338,24 +5365,24 @@
       <c r="E148" s="32"/>
     </row>
     <row r="149" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="386" t="s">
+      <c r="A149" s="371" t="s">
         <v>470</v>
       </c>
-      <c r="B149" s="387"/>
+      <c r="B149" s="372"/>
       <c r="C149" s="32"/>
       <c r="D149" s="32"/>
       <c r="E149" s="32"/>
     </row>
     <row r="150" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="388"/>
-      <c r="B150" s="389"/>
+      <c r="A150" s="373"/>
+      <c r="B150" s="374"/>
       <c r="C150" s="32"/>
       <c r="D150" s="32"/>
       <c r="E150" s="32"/>
     </row>
     <row r="151" spans="1:5" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="390"/>
-      <c r="B151" s="391"/>
+      <c r="A151" s="375"/>
+      <c r="B151" s="376"/>
       <c r="C151" s="32"/>
       <c r="D151" s="32"/>
       <c r="E151" s="32"/>
@@ -5630,10 +5657,10 @@
       <c r="F177" s="83"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="394" t="s">
+      <c r="A178" s="378" t="s">
         <v>296</v>
       </c>
-      <c r="B178" s="395"/>
+      <c r="B178" s="379"/>
       <c r="C178" s="6"/>
       <c r="D178" s="13"/>
       <c r="E178" s="37"/>
@@ -5905,16 +5932,16 @@
       <c r="F200" s="38"/>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A201" s="392" t="s">
+      <c r="A201" s="377" t="s">
         <v>17</v>
       </c>
-      <c r="B201" s="392"/>
-      <c r="C201" s="392"/>
+      <c r="B201" s="377"/>
+      <c r="C201" s="377"/>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A202" s="392"/>
-      <c r="B202" s="392"/>
-      <c r="C202" s="392"/>
+      <c r="A202" s="377"/>
+      <c r="B202" s="377"/>
+      <c r="C202" s="377"/>
     </row>
     <row r="203" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="71"/>
@@ -5941,31 +5968,43 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
     <mergeCell ref="A149:B151"/>
     <mergeCell ref="A97:B97"/>
     <mergeCell ref="A201:C202"/>
@@ -5982,43 +6021,31 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A114:B114"/>
     <mergeCell ref="A115:B115"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A89:B89"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6058,27 +6085,27 @@
     <row r="1" spans="1:24" ht="182.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="406" t="s">
+      <c r="C1" s="411" t="s">
         <v>389</v>
       </c>
-      <c r="D1" s="407"/>
-      <c r="E1" s="407"/>
-      <c r="F1" s="407"/>
-      <c r="G1" s="407"/>
-      <c r="H1" s="407"/>
-      <c r="I1" s="407"/>
-      <c r="J1" s="407"/>
-      <c r="K1" s="407"/>
-      <c r="L1" s="407"/>
+      <c r="D1" s="412"/>
+      <c r="E1" s="412"/>
+      <c r="F1" s="412"/>
+      <c r="G1" s="412"/>
+      <c r="H1" s="412"/>
+      <c r="I1" s="412"/>
+      <c r="J1" s="412"/>
+      <c r="K1" s="412"/>
+      <c r="L1" s="412"/>
       <c r="M1" s="155"/>
-      <c r="N1" s="408" t="s">
+      <c r="N1" s="413" t="s">
         <v>318</v>
       </c>
-      <c r="O1" s="408"/>
-      <c r="P1" s="403">
+      <c r="O1" s="413"/>
+      <c r="P1" s="408">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="403"/>
+      <c r="Q1" s="408"/>
       <c r="R1" s="184"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -6092,35 +6119,35 @@
     <row r="2" spans="1:24" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="405" t="s">
+      <c r="C2" s="410" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="405"/>
-      <c r="E2" s="405"/>
+      <c r="D2" s="410"/>
+      <c r="E2" s="410"/>
       <c r="F2" s="155"/>
-      <c r="G2" s="402">
+      <c r="G2" s="405">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="402"/>
+      <c r="H2" s="405"/>
       <c r="I2" s="155" t="s">
         <v>277</v>
       </c>
       <c r="J2" s="155"/>
-      <c r="K2" s="402">
+      <c r="K2" s="405">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="402"/>
+      <c r="L2" s="405"/>
       <c r="M2" s="270"/>
       <c r="N2" s="271" t="s">
         <v>263</v>
       </c>
       <c r="O2" s="270"/>
-      <c r="P2" s="404">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="404"/>
+      <c r="P2" s="409">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="409"/>
       <c r="R2" s="185"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -6132,112 +6159,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="76.650000000000006" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="413" t="str">
+      <c r="A3" s="418" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  17/04, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="414"/>
-      <c r="C3" s="414"/>
-      <c r="D3" s="414"/>
-      <c r="E3" s="414"/>
-      <c r="F3" s="414"/>
-      <c r="G3" s="414"/>
-      <c r="H3" s="414"/>
-      <c r="I3" s="414"/>
-      <c r="J3" s="414"/>
-      <c r="K3" s="414"/>
-      <c r="L3" s="414"/>
-      <c r="M3" s="414"/>
-      <c r="N3" s="414"/>
-      <c r="O3" s="414"/>
-      <c r="P3" s="414"/>
-      <c r="Q3" s="414"/>
-      <c r="R3" s="414"/>
-      <c r="S3" s="414"/>
-      <c r="T3" s="415"/>
+      <c r="B3" s="419"/>
+      <c r="C3" s="419"/>
+      <c r="D3" s="419"/>
+      <c r="E3" s="419"/>
+      <c r="F3" s="419"/>
+      <c r="G3" s="419"/>
+      <c r="H3" s="419"/>
+      <c r="I3" s="419"/>
+      <c r="J3" s="419"/>
+      <c r="K3" s="419"/>
+      <c r="L3" s="419"/>
+      <c r="M3" s="419"/>
+      <c r="N3" s="419"/>
+      <c r="O3" s="419"/>
+      <c r="P3" s="419"/>
+      <c r="Q3" s="419"/>
+      <c r="R3" s="419"/>
+      <c r="S3" s="419"/>
+      <c r="T3" s="420"/>
       <c r="X3" s="40"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="416" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="418" t="s">
+      <c r="A4" s="421" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="423" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="418" t="s">
+      <c r="C4" s="423" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="418" t="s">
+      <c r="D4" s="423" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="398" t="s">
+      <c r="E4" s="406" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="418" t="s">
+      <c r="F4" s="423" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="420" t="s">
+      <c r="G4" s="425" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="398" t="s">
+      <c r="H4" s="406" t="s">
         <v>234</v>
       </c>
-      <c r="I4" s="398" t="s">
+      <c r="I4" s="406" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="398"/>
-      <c r="K4" s="398" t="s">
+      <c r="J4" s="406"/>
+      <c r="K4" s="406" t="s">
         <v>184</v>
       </c>
-      <c r="L4" s="398" t="s">
+      <c r="L4" s="406" t="s">
         <v>147</v>
       </c>
-      <c r="M4" s="398" t="s">
+      <c r="M4" s="406" t="s">
         <v>186</v>
       </c>
-      <c r="N4" s="398" t="s">
+      <c r="N4" s="406" t="s">
         <v>185</v>
       </c>
-      <c r="O4" s="398" t="s">
+      <c r="O4" s="406" t="s">
         <v>420</v>
       </c>
-      <c r="P4" s="409" t="s">
+      <c r="P4" s="414" t="s">
         <v>335</v>
       </c>
-      <c r="Q4" s="410"/>
-      <c r="R4" s="409" t="s">
+      <c r="Q4" s="415"/>
+      <c r="R4" s="414" t="s">
         <v>323</v>
       </c>
-      <c r="S4" s="410"/>
-      <c r="T4" s="398" t="s">
+      <c r="S4" s="415"/>
+      <c r="T4" s="406" t="s">
         <v>261</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="417"/>
-      <c r="B5" s="419"/>
-      <c r="C5" s="419"/>
-      <c r="D5" s="419"/>
-      <c r="E5" s="399"/>
-      <c r="F5" s="419"/>
-      <c r="G5" s="421"/>
-      <c r="H5" s="399"/>
-      <c r="I5" s="399"/>
-      <c r="J5" s="399"/>
-      <c r="K5" s="399"/>
-      <c r="L5" s="399"/>
-      <c r="M5" s="399"/>
-      <c r="N5" s="399"/>
-      <c r="O5" s="399"/>
-      <c r="P5" s="411" t="str">
+      <c r="A5" s="422"/>
+      <c r="B5" s="424"/>
+      <c r="C5" s="424"/>
+      <c r="D5" s="424"/>
+      <c r="E5" s="407"/>
+      <c r="F5" s="424"/>
+      <c r="G5" s="426"/>
+      <c r="H5" s="407"/>
+      <c r="I5" s="407"/>
+      <c r="J5" s="407"/>
+      <c r="K5" s="407"/>
+      <c r="L5" s="407"/>
+      <c r="M5" s="407"/>
+      <c r="N5" s="407"/>
+      <c r="O5" s="407"/>
+      <c r="P5" s="416" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  17/04</v>
       </c>
-      <c r="Q5" s="412"/>
-      <c r="R5" s="411"/>
-      <c r="S5" s="412"/>
-      <c r="T5" s="399"/>
+      <c r="Q5" s="417"/>
+      <c r="R5" s="416"/>
+      <c r="S5" s="417"/>
+      <c r="T5" s="407"/>
     </row>
     <row r="6" spans="1:24" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="204"/>
@@ -6286,11 +6313,11 @@
         <v>0</v>
       </c>
       <c r="O6" s="209"/>
-      <c r="P6" s="400">
+      <c r="P6" s="427">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>1518529.01</v>
       </c>
-      <c r="Q6" s="400"/>
+      <c r="Q6" s="427"/>
       <c r="R6" s="272">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>1564586.01</v>
@@ -6355,11 +6382,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="74"/>
-      <c r="P7" s="401">
+      <c r="P7" s="398">
         <f t="shared" si="2"/>
         <v>1542558.02</v>
       </c>
-      <c r="Q7" s="401"/>
+      <c r="Q7" s="398"/>
       <c r="R7" s="272">
         <f t="shared" si="3"/>
         <v>1589344.02</v>
@@ -6423,11 +6450,11 @@
         <v>0</v>
       </c>
       <c r="O8" s="74"/>
-      <c r="P8" s="401">
+      <c r="P8" s="398">
         <f t="shared" si="2"/>
         <v>736705.03</v>
       </c>
-      <c r="Q8" s="401"/>
+      <c r="Q8" s="398"/>
       <c r="R8" s="272">
         <f t="shared" si="3"/>
         <v>759049.03</v>
@@ -6492,11 +6519,11 @@
         <v>0</v>
       </c>
       <c r="O9" s="74"/>
-      <c r="P9" s="401">
+      <c r="P9" s="398">
         <f t="shared" si="2"/>
         <v>3222835.04</v>
       </c>
-      <c r="Q9" s="401"/>
+      <c r="Q9" s="398"/>
       <c r="R9" s="272">
         <f t="shared" si="3"/>
         <v>3320584.04</v>
@@ -6564,11 +6591,11 @@
         <v>0</v>
       </c>
       <c r="O10" s="74"/>
-      <c r="P10" s="401">
+      <c r="P10" s="398">
         <f t="shared" si="2"/>
         <v>744528.05</v>
       </c>
-      <c r="Q10" s="401"/>
+      <c r="Q10" s="398"/>
       <c r="R10" s="272">
         <f t="shared" si="3"/>
         <v>767110.05</v>
@@ -6634,11 +6661,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="74"/>
-      <c r="P11" s="401">
+      <c r="P11" s="398">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="401"/>
+      <c r="Q11" s="398"/>
       <c r="R11" s="272">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -6705,11 +6732,11 @@
         <v>0</v>
       </c>
       <c r="O12" s="74"/>
-      <c r="P12" s="401">
+      <c r="P12" s="398">
         <f t="shared" si="2"/>
         <v>744299.07</v>
       </c>
-      <c r="Q12" s="401"/>
+      <c r="Q12" s="398"/>
       <c r="R12" s="272">
         <f t="shared" si="3"/>
         <v>766874.07</v>
@@ -6776,11 +6803,11 @@
         <v>0</v>
       </c>
       <c r="O13" s="74"/>
-      <c r="P13" s="401">
+      <c r="P13" s="398">
         <f t="shared" si="2"/>
         <v>744514.08</v>
       </c>
-      <c r="Q13" s="401"/>
+      <c r="Q13" s="398"/>
       <c r="R13" s="272">
         <f t="shared" si="3"/>
         <v>767095.08</v>
@@ -6845,11 +6872,11 @@
         <v>379177.030424</v>
       </c>
       <c r="O14" s="74"/>
-      <c r="P14" s="401">
+      <c r="P14" s="398">
         <f t="shared" si="2"/>
         <v>3585790.09</v>
       </c>
-      <c r="Q14" s="401"/>
+      <c r="Q14" s="398"/>
       <c r="R14" s="272">
         <f t="shared" si="3"/>
         <v>3694547.09</v>
@@ -6913,11 +6940,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="74"/>
-      <c r="P15" s="401">
+      <c r="P15" s="398">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="401"/>
+      <c r="Q15" s="398"/>
       <c r="R15" s="272">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -6983,11 +7010,11 @@
         <v>0</v>
       </c>
       <c r="O16" s="36"/>
-      <c r="P16" s="401">
+      <c r="P16" s="398">
         <f t="shared" si="2"/>
         <v>744528.11</v>
       </c>
-      <c r="Q16" s="401"/>
+      <c r="Q16" s="398"/>
       <c r="R16" s="272">
         <f t="shared" si="3"/>
         <v>767110.11</v>
@@ -7051,11 +7078,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="74"/>
-      <c r="P17" s="401">
+      <c r="P17" s="398">
         <f t="shared" si="2"/>
         <v>4420303.12</v>
       </c>
-      <c r="Q17" s="401"/>
+      <c r="Q17" s="398"/>
       <c r="R17" s="272">
         <f t="shared" si="3"/>
         <v>4554371.12</v>
@@ -7122,11 +7149,11 @@
       <c r="O18" s="74">
         <v>91169.89</v>
       </c>
-      <c r="P18" s="401">
+      <c r="P18" s="398">
         <f t="shared" si="2"/>
         <v>850918.13</v>
       </c>
-      <c r="Q18" s="401"/>
+      <c r="Q18" s="398"/>
       <c r="R18" s="272">
         <f t="shared" si="3"/>
         <v>876726.13</v>
@@ -7190,11 +7217,11 @@
         <v>0</v>
       </c>
       <c r="O19" s="74"/>
-      <c r="P19" s="401">
+      <c r="P19" s="398">
         <f t="shared" si="2"/>
         <v>720435.14</v>
       </c>
-      <c r="Q19" s="401"/>
+      <c r="Q19" s="398"/>
       <c r="R19" s="272">
         <f t="shared" si="3"/>
         <v>742286.14</v>
@@ -7261,11 +7288,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="74"/>
-      <c r="P20" s="401">
+      <c r="P20" s="398">
         <f t="shared" si="2"/>
         <v>743613.15</v>
       </c>
-      <c r="Q20" s="401"/>
+      <c r="Q20" s="398"/>
       <c r="R20" s="272">
         <f t="shared" si="3"/>
         <v>766167.15</v>
@@ -7330,11 +7357,11 @@
       </c>
       <c r="N21" s="74"/>
       <c r="O21" s="74"/>
-      <c r="P21" s="401">
+      <c r="P21" s="398">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="401"/>
+      <c r="Q21" s="398"/>
       <c r="R21" s="272">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7395,11 +7422,11 @@
         <v>0</v>
       </c>
       <c r="O22" s="74"/>
-      <c r="P22" s="401">
+      <c r="P22" s="398">
         <f t="shared" si="2"/>
         <v>2350329.17</v>
       </c>
-      <c r="Q22" s="401"/>
+      <c r="Q22" s="398"/>
       <c r="R22" s="272">
         <f t="shared" si="3"/>
         <v>2421615.17</v>
@@ -7465,11 +7492,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="88"/>
-      <c r="P23" s="401">
+      <c r="P23" s="398">
         <f t="shared" si="2"/>
         <v>736705.18</v>
       </c>
-      <c r="Q23" s="401"/>
+      <c r="Q23" s="398"/>
       <c r="R23" s="272">
         <f t="shared" si="3"/>
         <v>759049.18</v>
@@ -7535,11 +7562,11 @@
         <v>0</v>
       </c>
       <c r="O24" s="88"/>
-      <c r="P24" s="401">
+      <c r="P24" s="398">
         <f t="shared" si="2"/>
         <v>744528.19</v>
       </c>
-      <c r="Q24" s="401"/>
+      <c r="Q24" s="398"/>
       <c r="R24" s="272">
         <f t="shared" si="3"/>
         <v>767110.19</v>
@@ -7602,11 +7629,11 @@
         <v>0</v>
       </c>
       <c r="O25" s="88"/>
-      <c r="P25" s="401">
+      <c r="P25" s="398">
         <f t="shared" si="2"/>
         <v>744528.2</v>
       </c>
-      <c r="Q25" s="401"/>
+      <c r="Q25" s="398"/>
       <c r="R25" s="272">
         <f t="shared" si="3"/>
         <v>767110.2</v>
@@ -7667,11 +7694,11 @@
         <v>0</v>
       </c>
       <c r="O26" s="88"/>
-      <c r="P26" s="401">
+      <c r="P26" s="398">
         <f t="shared" si="2"/>
         <v>1559335.21</v>
       </c>
-      <c r="Q26" s="401"/>
+      <c r="Q26" s="398"/>
       <c r="R26" s="272">
         <f t="shared" si="3"/>
         <v>1606630.21</v>
@@ -7740,11 +7767,11 @@
         <v>0</v>
       </c>
       <c r="O27" s="88"/>
-      <c r="P27" s="401">
+      <c r="P27" s="398">
         <f t="shared" si="2"/>
         <v>744528.22</v>
       </c>
-      <c r="Q27" s="401"/>
+      <c r="Q27" s="398"/>
       <c r="R27" s="272">
         <f t="shared" si="3"/>
         <v>767110.22</v>
@@ -7810,11 +7837,11 @@
         <v>0</v>
       </c>
       <c r="O28" s="88"/>
-      <c r="P28" s="401">
+      <c r="P28" s="398">
         <f t="shared" si="2"/>
         <v>767815.23</v>
       </c>
-      <c r="Q28" s="401"/>
+      <c r="Q28" s="398"/>
       <c r="R28" s="272">
         <f t="shared" si="3"/>
         <v>791103.23</v>
@@ -7880,11 +7907,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="88"/>
-      <c r="P29" s="401">
+      <c r="P29" s="398">
         <f t="shared" si="2"/>
         <v>744528.24</v>
       </c>
-      <c r="Q29" s="401"/>
+      <c r="Q29" s="398"/>
       <c r="R29" s="272">
         <f t="shared" si="3"/>
         <v>767110.24</v>
@@ -7951,11 +7978,11 @@
         <v>0</v>
       </c>
       <c r="O30" s="88"/>
-      <c r="P30" s="401">
+      <c r="P30" s="398">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="401"/>
+      <c r="Q30" s="398"/>
       <c r="R30" s="272">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8021,11 +8048,11 @@
         <v>0</v>
       </c>
       <c r="O31" s="88"/>
-      <c r="P31" s="401">
+      <c r="P31" s="398">
         <f t="shared" si="2"/>
         <v>752356.26</v>
       </c>
-      <c r="Q31" s="401"/>
+      <c r="Q31" s="398"/>
       <c r="R31" s="272">
         <f t="shared" si="3"/>
         <v>775175.26</v>
@@ -8092,11 +8119,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="88"/>
-      <c r="P32" s="401">
+      <c r="P32" s="398">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="401"/>
+      <c r="Q32" s="398"/>
       <c r="R32" s="272">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8162,11 +8189,11 @@
         <f>I33/2</f>
         <v>181520.91881999999</v>
       </c>
-      <c r="P33" s="401">
+      <c r="P33" s="398">
         <f t="shared" si="2"/>
         <v>923797.28</v>
       </c>
-      <c r="Q33" s="401"/>
+      <c r="Q33" s="398"/>
       <c r="R33" s="272">
         <f t="shared" si="3"/>
         <v>951816.28</v>
@@ -8232,11 +8259,11 @@
         <v>0</v>
       </c>
       <c r="O34" s="88"/>
-      <c r="P34" s="401">
+      <c r="P34" s="398">
         <f t="shared" si="2"/>
         <v>752351.29</v>
       </c>
-      <c r="Q34" s="401"/>
+      <c r="Q34" s="398"/>
       <c r="R34" s="272">
         <f t="shared" si="3"/>
         <v>775170.29</v>
@@ -8303,11 +8330,11 @@
         <v>0</v>
       </c>
       <c r="O35" s="88"/>
-      <c r="P35" s="401">
+      <c r="P35" s="398">
         <f t="shared" si="2"/>
         <v>751681.3</v>
       </c>
-      <c r="Q35" s="401"/>
+      <c r="Q35" s="398"/>
       <c r="R35" s="272">
         <f t="shared" si="3"/>
         <v>774480.3</v>
@@ -8371,11 +8398,11 @@
         <v>0</v>
       </c>
       <c r="O36" s="88"/>
-      <c r="P36" s="401">
+      <c r="P36" s="398">
         <f t="shared" si="2"/>
         <v>2643433.31</v>
       </c>
-      <c r="Q36" s="401"/>
+      <c r="Q36" s="398"/>
       <c r="R36" s="272">
         <f t="shared" si="3"/>
         <v>2723609.31</v>
@@ -8442,11 +8469,11 @@
         <v>0</v>
       </c>
       <c r="O37" s="88"/>
-      <c r="P37" s="401">
+      <c r="P37" s="398">
         <f t="shared" si="2"/>
         <v>573720.31999999995</v>
       </c>
-      <c r="Q37" s="401"/>
+      <c r="Q37" s="398"/>
       <c r="R37" s="272">
         <f t="shared" si="3"/>
         <v>591121.31999999995</v>
@@ -8509,11 +8536,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="88"/>
-      <c r="P38" s="401">
+      <c r="P38" s="398">
         <f t="shared" ref="P38:P69" si="14">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="401"/>
+      <c r="Q38" s="398"/>
       <c r="R38" s="272">
         <f t="shared" ref="R38:R69" si="15">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -8573,11 +8600,11 @@
         <v>0</v>
       </c>
       <c r="O39" s="88"/>
-      <c r="P39" s="401">
+      <c r="P39" s="398">
         <f t="shared" si="14"/>
         <v>2473411.34</v>
       </c>
-      <c r="Q39" s="401"/>
+      <c r="Q39" s="398"/>
       <c r="R39" s="272">
         <f t="shared" si="15"/>
         <v>2548430.34</v>
@@ -8644,11 +8671,11 @@
         <v>0</v>
       </c>
       <c r="O40" s="88"/>
-      <c r="P40" s="401">
+      <c r="P40" s="398">
         <f t="shared" si="14"/>
         <v>736704.35</v>
       </c>
-      <c r="Q40" s="401"/>
+      <c r="Q40" s="398"/>
       <c r="R40" s="272">
         <f t="shared" si="15"/>
         <v>759049.35</v>
@@ -8716,11 +8743,11 @@
         <v>0</v>
       </c>
       <c r="O41" s="88"/>
-      <c r="P41" s="401">
+      <c r="P41" s="398">
         <f t="shared" si="14"/>
         <v>748020.36</v>
       </c>
-      <c r="Q41" s="401"/>
+      <c r="Q41" s="398"/>
       <c r="R41" s="272">
         <f t="shared" si="15"/>
         <v>770708.36</v>
@@ -8783,11 +8810,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="88"/>
-      <c r="P42" s="401">
+      <c r="P42" s="398">
         <f t="shared" si="14"/>
         <v>1526106.37</v>
       </c>
-      <c r="Q42" s="401"/>
+      <c r="Q42" s="398"/>
       <c r="R42" s="272">
         <f t="shared" si="15"/>
         <v>1572393.37</v>
@@ -8853,11 +8880,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="88"/>
-      <c r="P43" s="401">
+      <c r="P43" s="398">
         <f t="shared" si="14"/>
         <v>751681.38</v>
       </c>
-      <c r="Q43" s="401"/>
+      <c r="Q43" s="398"/>
       <c r="R43" s="272">
         <f t="shared" si="15"/>
         <v>774480.38</v>
@@ -8925,11 +8952,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="88"/>
-      <c r="P44" s="401">
+      <c r="P44" s="398">
         <f t="shared" si="14"/>
         <v>872758.39</v>
       </c>
-      <c r="Q44" s="401"/>
+      <c r="Q44" s="398"/>
       <c r="R44" s="272">
         <f t="shared" si="15"/>
         <v>899229.39</v>
@@ -8996,11 +9023,11 @@
         <v>0</v>
       </c>
       <c r="O45" s="88"/>
-      <c r="P45" s="401">
+      <c r="P45" s="398">
         <f t="shared" si="14"/>
         <v>728593.4</v>
       </c>
-      <c r="Q45" s="401"/>
+      <c r="Q45" s="398"/>
       <c r="R45" s="272">
         <f t="shared" si="15"/>
         <v>750692.4</v>
@@ -9064,11 +9091,11 @@
         <v>0</v>
       </c>
       <c r="O46" s="88"/>
-      <c r="P46" s="401">
+      <c r="P46" s="398">
         <f t="shared" si="14"/>
         <v>728882.41</v>
       </c>
-      <c r="Q46" s="401"/>
+      <c r="Q46" s="398"/>
       <c r="R46" s="272">
         <f t="shared" si="15"/>
         <v>750989.41</v>
@@ -9135,11 +9162,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="88"/>
-      <c r="P47" s="401">
+      <c r="P47" s="398">
         <f t="shared" si="14"/>
         <v>728882.42</v>
       </c>
-      <c r="Q47" s="401"/>
+      <c r="Q47" s="398"/>
       <c r="R47" s="272">
         <f t="shared" si="15"/>
         <v>750989.42</v>
@@ -9207,11 +9234,11 @@
         <v>0</v>
       </c>
       <c r="O48" s="88"/>
-      <c r="P48" s="401">
+      <c r="P48" s="398">
         <f t="shared" si="14"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="401"/>
+      <c r="Q48" s="398"/>
       <c r="R48" s="272">
         <f t="shared" si="15"/>
         <v>699669.43</v>
@@ -9275,11 +9302,11 @@
         <v>0</v>
       </c>
       <c r="O49" s="88"/>
-      <c r="P49" s="401">
+      <c r="P49" s="398">
         <f t="shared" si="14"/>
         <v>895905.44</v>
       </c>
-      <c r="Q49" s="401"/>
+      <c r="Q49" s="398"/>
       <c r="R49" s="272">
         <f t="shared" si="15"/>
         <v>923078.44</v>
@@ -9345,11 +9372,11 @@
         <v>395312.22320800001</v>
       </c>
       <c r="O50" s="88"/>
-      <c r="P50" s="401">
+      <c r="P50" s="398">
         <f t="shared" si="14"/>
         <v>1987415.45</v>
       </c>
-      <c r="Q50" s="401"/>
+      <c r="Q50" s="398"/>
       <c r="R50" s="272">
         <f t="shared" si="15"/>
         <v>2047694.45</v>
@@ -9413,11 +9440,11 @@
         <v>0</v>
       </c>
       <c r="O51" s="88"/>
-      <c r="P51" s="401">
+      <c r="P51" s="398">
         <f t="shared" si="14"/>
         <v>1451367.46</v>
       </c>
-      <c r="Q51" s="401"/>
+      <c r="Q51" s="398"/>
       <c r="R51" s="272">
         <f t="shared" si="15"/>
         <v>1495387.46</v>
@@ -9482,11 +9509,11 @@
         <v>0</v>
       </c>
       <c r="O52" s="88"/>
-      <c r="P52" s="401">
+      <c r="P52" s="398">
         <f t="shared" si="14"/>
         <v>3158183.47</v>
       </c>
-      <c r="Q52" s="401"/>
+      <c r="Q52" s="398"/>
       <c r="R52" s="272">
         <f t="shared" si="15"/>
         <v>3253971.47</v>
@@ -9557,11 +9584,11 @@
         <f>I53*0.1</f>
         <v>36304.183764000001</v>
       </c>
-      <c r="P53" s="401">
+      <c r="P53" s="398">
         <f t="shared" si="14"/>
         <v>1125839.48</v>
       </c>
-      <c r="Q53" s="401"/>
+      <c r="Q53" s="398"/>
       <c r="R53" s="272">
         <f t="shared" si="15"/>
         <v>1159986.48</v>
@@ -9626,11 +9653,11 @@
         <v>0</v>
       </c>
       <c r="O54" s="88"/>
-      <c r="P54" s="401">
+      <c r="P54" s="398">
         <f t="shared" si="14"/>
         <v>728882.49</v>
       </c>
-      <c r="Q54" s="401"/>
+      <c r="Q54" s="398"/>
       <c r="R54" s="272">
         <f t="shared" si="15"/>
         <v>750989.49</v>
@@ -9697,11 +9724,11 @@
         <v>0</v>
       </c>
       <c r="O55" s="88"/>
-      <c r="P55" s="401">
+      <c r="P55" s="398">
         <f t="shared" si="14"/>
         <v>728882.5</v>
       </c>
-      <c r="Q55" s="401"/>
+      <c r="Q55" s="398"/>
       <c r="R55" s="272">
         <f t="shared" si="15"/>
         <v>750990.5</v>
@@ -9767,11 +9794,11 @@
         <v>363041.83763999998</v>
       </c>
       <c r="O56" s="88"/>
-      <c r="P56" s="401">
+      <c r="P56" s="398">
         <f t="shared" si="14"/>
         <v>2245180.5099999998</v>
       </c>
-      <c r="Q56" s="401"/>
+      <c r="Q56" s="398"/>
       <c r="R56" s="272">
         <f t="shared" si="15"/>
         <v>2313277.5099999998</v>
@@ -9839,11 +9866,11 @@
         <v>0</v>
       </c>
       <c r="O57" s="88"/>
-      <c r="P57" s="401">
+      <c r="P57" s="398">
         <f t="shared" si="14"/>
         <v>712950.52</v>
       </c>
-      <c r="Q57" s="401"/>
+      <c r="Q57" s="398"/>
       <c r="R57" s="272">
         <f t="shared" si="15"/>
         <v>734574.52</v>
@@ -9908,11 +9935,11 @@
         <v>0</v>
       </c>
       <c r="O58" s="88"/>
-      <c r="P58" s="401">
+      <c r="P58" s="398">
         <f t="shared" si="14"/>
         <v>3399941.53</v>
       </c>
-      <c r="Q58" s="401"/>
+      <c r="Q58" s="398"/>
       <c r="R58" s="272">
         <f t="shared" si="15"/>
         <v>3503062.53</v>
@@ -9977,11 +10004,11 @@
         <v>0</v>
       </c>
       <c r="O59" s="88"/>
-      <c r="P59" s="401">
+      <c r="P59" s="398">
         <f t="shared" si="14"/>
         <v>751681.54</v>
       </c>
-      <c r="Q59" s="401"/>
+      <c r="Q59" s="398"/>
       <c r="R59" s="272">
         <f t="shared" si="15"/>
         <v>774480.54</v>
@@ -10048,11 +10075,11 @@
         <v>0</v>
       </c>
       <c r="O60" s="88"/>
-      <c r="P60" s="401">
+      <c r="P60" s="398">
         <f t="shared" si="14"/>
         <v>728882.55</v>
       </c>
-      <c r="Q60" s="401"/>
+      <c r="Q60" s="398"/>
       <c r="R60" s="272">
         <f t="shared" si="15"/>
         <v>750990.55</v>
@@ -10123,11 +10150,11 @@
         <f>(I61*0.1)*2</f>
         <v>72608.367528000002</v>
       </c>
-      <c r="P61" s="401">
+      <c r="P61" s="398">
         <f t="shared" si="14"/>
         <v>1225512.56</v>
       </c>
-      <c r="Q61" s="401"/>
+      <c r="Q61" s="398"/>
       <c r="R61" s="272">
         <f t="shared" si="15"/>
         <v>1262682.56</v>
@@ -10192,11 +10219,11 @@
         <v>0</v>
       </c>
       <c r="O62" s="88"/>
-      <c r="P62" s="401">
+      <c r="P62" s="398">
         <f t="shared" si="14"/>
         <v>1526567.57</v>
       </c>
-      <c r="Q62" s="401"/>
+      <c r="Q62" s="398"/>
       <c r="R62" s="272">
         <f t="shared" si="15"/>
         <v>1572868.57</v>
@@ -10260,11 +10287,11 @@
         <v>0</v>
       </c>
       <c r="O63" s="88"/>
-      <c r="P63" s="401">
+      <c r="P63" s="398">
         <f t="shared" si="14"/>
         <v>728882.58</v>
       </c>
-      <c r="Q63" s="401"/>
+      <c r="Q63" s="398"/>
       <c r="R63" s="272">
         <f t="shared" si="15"/>
         <v>750990.58</v>
@@ -10328,11 +10355,11 @@
         <v>0</v>
       </c>
       <c r="O64" s="88"/>
-      <c r="P64" s="401">
+      <c r="P64" s="398">
         <f t="shared" si="14"/>
         <v>691468.59</v>
       </c>
-      <c r="Q64" s="401"/>
+      <c r="Q64" s="398"/>
       <c r="R64" s="272">
         <f t="shared" si="15"/>
         <v>712441.59</v>
@@ -10399,11 +10426,11 @@
         <v>0</v>
       </c>
       <c r="O65" s="88"/>
-      <c r="P65" s="401">
+      <c r="P65" s="398">
         <f t="shared" si="14"/>
         <v>750827.6</v>
       </c>
-      <c r="Q65" s="401"/>
+      <c r="Q65" s="398"/>
       <c r="R65" s="272">
         <f t="shared" si="15"/>
         <v>773600.6</v>
@@ -10471,11 +10498,11 @@
         <v>0</v>
       </c>
       <c r="O66" s="88"/>
-      <c r="P66" s="401">
+      <c r="P66" s="398">
         <f t="shared" si="14"/>
         <v>751038.61</v>
       </c>
-      <c r="Q66" s="401"/>
+      <c r="Q66" s="398"/>
       <c r="R66" s="272">
         <f t="shared" si="15"/>
         <v>773818.61</v>
@@ -10546,11 +10573,11 @@
         <f>I67/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P67" s="401">
+      <c r="P67" s="398">
         <f t="shared" si="14"/>
         <v>921295.62</v>
       </c>
-      <c r="Q67" s="401"/>
+      <c r="Q67" s="398"/>
       <c r="R67" s="272">
         <f t="shared" si="15"/>
         <v>949239.62</v>
@@ -10615,11 +10642,11 @@
         <v>0</v>
       </c>
       <c r="O68" s="88"/>
-      <c r="P68" s="401">
+      <c r="P68" s="398">
         <f t="shared" si="14"/>
         <v>751681.63</v>
       </c>
-      <c r="Q68" s="401"/>
+      <c r="Q68" s="398"/>
       <c r="R68" s="272">
         <f t="shared" si="15"/>
         <v>774480.63</v>
@@ -10687,11 +10714,11 @@
         <v>0</v>
       </c>
       <c r="O69" s="88"/>
-      <c r="P69" s="401">
+      <c r="P69" s="398">
         <f t="shared" si="14"/>
         <v>706943.64</v>
       </c>
-      <c r="Q69" s="401"/>
+      <c r="Q69" s="398"/>
       <c r="R69" s="272">
         <f t="shared" si="15"/>
         <v>728385.64</v>
@@ -10759,11 +10786,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="88"/>
-      <c r="P70" s="401">
+      <c r="P70" s="398">
         <f t="shared" ref="P70:P101" si="22">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="401"/>
+      <c r="Q70" s="398"/>
       <c r="R70" s="272">
         <f t="shared" ref="R70:R101" si="23">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -10827,11 +10854,11 @@
         <v>0</v>
       </c>
       <c r="O71" s="88"/>
-      <c r="P71" s="401">
+      <c r="P71" s="398">
         <f t="shared" si="22"/>
         <v>728882.66</v>
       </c>
-      <c r="Q71" s="401"/>
+      <c r="Q71" s="398"/>
       <c r="R71" s="272">
         <f t="shared" si="23"/>
         <v>750990.66</v>
@@ -10896,11 +10923,11 @@
         <v>0</v>
       </c>
       <c r="O72" s="88"/>
-      <c r="P72" s="401">
+      <c r="P72" s="398">
         <f t="shared" si="22"/>
         <v>1518273.67</v>
       </c>
-      <c r="Q72" s="401"/>
+      <c r="Q72" s="398"/>
       <c r="R72" s="272">
         <f t="shared" si="23"/>
         <v>1564323.67</v>
@@ -10965,11 +10992,11 @@
         <v>363041.83763999998</v>
       </c>
       <c r="O73" s="88"/>
-      <c r="P73" s="401">
+      <c r="P73" s="398">
         <f t="shared" si="22"/>
         <v>4559265.68</v>
       </c>
-      <c r="Q73" s="401"/>
+      <c r="Q73" s="398"/>
       <c r="R73" s="272">
         <f t="shared" si="23"/>
         <v>4697548.68</v>
@@ -11032,11 +11059,11 @@
         <v>0</v>
       </c>
       <c r="O74" s="36"/>
-      <c r="P74" s="401">
+      <c r="P74" s="398">
         <f t="shared" si="22"/>
         <v>658475.68999999994</v>
       </c>
-      <c r="Q74" s="401"/>
+      <c r="Q74" s="398"/>
       <c r="R74" s="272">
         <f t="shared" si="23"/>
         <v>678447.69</v>
@@ -11102,11 +11129,11 @@
         <v>0</v>
       </c>
       <c r="O75" s="88"/>
-      <c r="P75" s="401">
+      <c r="P75" s="398">
         <f t="shared" si="22"/>
         <v>1372860.7</v>
       </c>
-      <c r="Q75" s="401"/>
+      <c r="Q75" s="398"/>
       <c r="R75" s="272">
         <f t="shared" si="23"/>
         <v>1414500.7</v>
@@ -11170,11 +11197,11 @@
         <v>0</v>
       </c>
       <c r="O76" s="88"/>
-      <c r="P76" s="401">
+      <c r="P76" s="398">
         <f t="shared" si="22"/>
         <v>4028209.71</v>
       </c>
-      <c r="Q76" s="401"/>
+      <c r="Q76" s="398"/>
       <c r="R76" s="272">
         <f t="shared" si="23"/>
         <v>4150385.71</v>
@@ -11240,11 +11267,11 @@
         <v>0</v>
       </c>
       <c r="O77" s="88"/>
-      <c r="P77" s="401">
+      <c r="P77" s="398">
         <f t="shared" si="22"/>
         <v>690051.72</v>
       </c>
-      <c r="Q77" s="401"/>
+      <c r="Q77" s="398"/>
       <c r="R77" s="272">
         <f t="shared" si="23"/>
         <v>710981.72</v>
@@ -11311,11 +11338,11 @@
         <v>0</v>
       </c>
       <c r="O78" s="88"/>
-      <c r="P78" s="401">
+      <c r="P78" s="398">
         <f t="shared" si="22"/>
         <v>711343.73</v>
       </c>
-      <c r="Q78" s="401"/>
+      <c r="Q78" s="398"/>
       <c r="R78" s="272">
         <f t="shared" si="23"/>
         <v>732919.73</v>
@@ -11379,11 +11406,11 @@
         <v>0</v>
       </c>
       <c r="O79" s="88"/>
-      <c r="P79" s="401">
+      <c r="P79" s="398">
         <f t="shared" si="22"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="401"/>
+      <c r="Q79" s="398"/>
       <c r="R79" s="272">
         <f t="shared" si="23"/>
         <v>766168.74</v>
@@ -11450,11 +11477,11 @@
         <f>I80/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P80" s="401">
+      <c r="P80" s="398">
         <f t="shared" si="22"/>
         <v>884796.75</v>
       </c>
-      <c r="Q80" s="401"/>
+      <c r="Q80" s="398"/>
       <c r="R80" s="272">
         <f t="shared" si="23"/>
         <v>911633.75</v>
@@ -11521,11 +11548,11 @@
         <v>0</v>
       </c>
       <c r="O81" s="88"/>
-      <c r="P81" s="401">
+      <c r="P81" s="398">
         <f t="shared" si="22"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="401"/>
+      <c r="Q81" s="398"/>
       <c r="R81" s="272">
         <f t="shared" si="23"/>
         <v>774480.76</v>
@@ -11588,11 +11615,11 @@
         <v>0</v>
       </c>
       <c r="O82" s="88"/>
-      <c r="P82" s="401">
+      <c r="P82" s="398">
         <f t="shared" si="22"/>
         <v>854048.77</v>
       </c>
-      <c r="Q82" s="401"/>
+      <c r="Q82" s="398"/>
       <c r="R82" s="272">
         <f t="shared" si="23"/>
         <v>879952.77</v>
@@ -11658,11 +11685,11 @@
         <v>0</v>
       </c>
       <c r="O83" s="88"/>
-      <c r="P83" s="401">
+      <c r="P83" s="398">
         <f t="shared" si="22"/>
         <v>751480.78</v>
       </c>
-      <c r="Q83" s="401"/>
+      <c r="Q83" s="398"/>
       <c r="R83" s="272">
         <f t="shared" si="23"/>
         <v>774273.78</v>
@@ -11729,11 +11756,11 @@
         <v>0</v>
       </c>
       <c r="O84" s="88"/>
-      <c r="P84" s="401">
+      <c r="P84" s="398">
         <f t="shared" si="22"/>
         <v>1089017.79</v>
       </c>
-      <c r="Q84" s="401"/>
+      <c r="Q84" s="398"/>
       <c r="R84" s="272">
         <f t="shared" si="23"/>
         <v>1122048.79</v>
@@ -11802,11 +11829,11 @@
         <v>0</v>
       </c>
       <c r="O85" s="88"/>
-      <c r="P85" s="401">
+      <c r="P85" s="398">
         <f t="shared" si="22"/>
         <v>728063.8</v>
       </c>
-      <c r="Q85" s="401"/>
+      <c r="Q85" s="398"/>
       <c r="R85" s="272">
         <f t="shared" si="23"/>
         <v>750146.8</v>
@@ -11873,11 +11900,11 @@
         <v>0</v>
       </c>
       <c r="O86" s="88"/>
-      <c r="P86" s="401">
+      <c r="P86" s="398">
         <f t="shared" si="22"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="401"/>
+      <c r="Q86" s="398"/>
       <c r="R86" s="272">
         <f t="shared" si="23"/>
         <v>774480.81</v>
@@ -11943,11 +11970,11 @@
         <v>0</v>
       </c>
       <c r="O87" s="74"/>
-      <c r="P87" s="401">
+      <c r="P87" s="398">
         <f t="shared" si="22"/>
         <v>682667.82</v>
       </c>
-      <c r="Q87" s="401"/>
+      <c r="Q87" s="398"/>
       <c r="R87" s="272">
         <f t="shared" si="23"/>
         <v>703373.82</v>
@@ -12014,11 +12041,11 @@
         <v>0</v>
       </c>
       <c r="O88" s="88"/>
-      <c r="P88" s="401">
+      <c r="P88" s="398">
         <f t="shared" si="22"/>
         <v>752351.83</v>
       </c>
-      <c r="Q88" s="401"/>
+      <c r="Q88" s="398"/>
       <c r="R88" s="272">
         <f t="shared" si="23"/>
         <v>775171.83</v>
@@ -12081,11 +12108,11 @@
         <v>0</v>
       </c>
       <c r="O89" s="88"/>
-      <c r="P89" s="401">
+      <c r="P89" s="398">
         <f t="shared" si="22"/>
         <v>752351.84</v>
       </c>
-      <c r="Q89" s="401"/>
+      <c r="Q89" s="398"/>
       <c r="R89" s="272">
         <f t="shared" si="23"/>
         <v>775171.84</v>
@@ -12149,11 +12176,11 @@
         <v>0</v>
       </c>
       <c r="O90" s="88"/>
-      <c r="P90" s="401">
+      <c r="P90" s="398">
         <f t="shared" si="22"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="401"/>
+      <c r="Q90" s="398"/>
       <c r="R90" s="272">
         <f t="shared" si="23"/>
         <v>799417.85</v>
@@ -12221,11 +12248,11 @@
         <v>387244.62681599997</v>
       </c>
       <c r="O91" s="88"/>
-      <c r="P91" s="401">
+      <c r="P91" s="398">
         <f t="shared" si="22"/>
         <v>1240577.8600000001</v>
       </c>
-      <c r="Q91" s="401"/>
+      <c r="Q91" s="398"/>
       <c r="R91" s="272">
         <f t="shared" si="23"/>
         <v>1278205.8600000001</v>
@@ -12291,11 +12318,11 @@
         <v>0</v>
       </c>
       <c r="O92" s="88"/>
-      <c r="P92" s="401">
+      <c r="P92" s="398">
         <f t="shared" si="22"/>
         <v>752351.87</v>
       </c>
-      <c r="Q92" s="401"/>
+      <c r="Q92" s="398"/>
       <c r="R92" s="272">
         <f t="shared" si="23"/>
         <v>775171.87</v>
@@ -12359,11 +12386,11 @@
         <v>0</v>
       </c>
       <c r="O93" s="88"/>
-      <c r="P93" s="401">
+      <c r="P93" s="398">
         <f t="shared" si="22"/>
         <v>775884.88</v>
       </c>
-      <c r="Q93" s="401"/>
+      <c r="Q93" s="398"/>
       <c r="R93" s="272">
         <f t="shared" si="23"/>
         <v>799417.88</v>
@@ -12426,11 +12453,11 @@
         <v>0</v>
       </c>
       <c r="O94" s="88"/>
-      <c r="P94" s="401">
+      <c r="P94" s="398">
         <f t="shared" si="22"/>
         <v>752351.89</v>
       </c>
-      <c r="Q94" s="401"/>
+      <c r="Q94" s="398"/>
       <c r="R94" s="272">
         <f t="shared" si="23"/>
         <v>775171.89</v>
@@ -12496,11 +12523,11 @@
         <v>0</v>
       </c>
       <c r="O95" s="88"/>
-      <c r="P95" s="401">
+      <c r="P95" s="398">
         <f t="shared" si="22"/>
         <v>743876.9</v>
       </c>
-      <c r="Q95" s="401"/>
+      <c r="Q95" s="398"/>
       <c r="R95" s="272">
         <f t="shared" si="23"/>
         <v>766439.9</v>
@@ -12566,11 +12593,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="88"/>
-      <c r="P96" s="401">
+      <c r="P96" s="398">
         <f t="shared" si="22"/>
         <v>752351.91</v>
       </c>
-      <c r="Q96" s="401"/>
+      <c r="Q96" s="398"/>
       <c r="R96" s="272">
         <f t="shared" si="23"/>
         <v>775171.91</v>
@@ -12639,11 +12666,11 @@
         <f>1780*100</f>
         <v>178000</v>
       </c>
-      <c r="P97" s="401">
+      <c r="P97" s="398">
         <f t="shared" si="22"/>
         <v>1840080.92</v>
       </c>
-      <c r="Q97" s="401"/>
+      <c r="Q97" s="398"/>
       <c r="R97" s="272">
         <f t="shared" si="23"/>
         <v>1895891.92</v>
@@ -12709,11 +12736,11 @@
         <v>0</v>
       </c>
       <c r="O98" s="60"/>
-      <c r="P98" s="401">
+      <c r="P98" s="398">
         <f t="shared" si="22"/>
         <v>238871.93</v>
       </c>
-      <c r="Q98" s="401"/>
+      <c r="Q98" s="398"/>
       <c r="R98" s="272">
         <f t="shared" si="23"/>
         <v>246117.93</v>
@@ -12780,11 +12807,11 @@
         <v>0</v>
       </c>
       <c r="O99" s="60"/>
-      <c r="P99" s="401">
+      <c r="P99" s="398">
         <f t="shared" si="22"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="401"/>
+      <c r="Q99" s="398"/>
       <c r="R99" s="272">
         <f t="shared" si="23"/>
         <v>799418.94</v>
@@ -12850,11 +12877,11 @@
         <v>0</v>
       </c>
       <c r="O100" s="88"/>
-      <c r="P100" s="401">
+      <c r="P100" s="398">
         <f t="shared" si="22"/>
         <v>4049080.95</v>
       </c>
-      <c r="Q100" s="401"/>
+      <c r="Q100" s="398"/>
       <c r="R100" s="272">
         <f t="shared" si="23"/>
         <v>4171890.95</v>
@@ -12917,11 +12944,11 @@
         <v>0</v>
       </c>
       <c r="O101" s="88"/>
-      <c r="P101" s="401">
+      <c r="P101" s="398">
         <f t="shared" si="22"/>
         <v>752388.96</v>
       </c>
-      <c r="Q101" s="401"/>
+      <c r="Q101" s="398"/>
       <c r="R101" s="272">
         <f t="shared" si="23"/>
         <v>775209.96</v>
@@ -12987,11 +13014,11 @@
         <v>0</v>
       </c>
       <c r="O102" s="88"/>
-      <c r="P102" s="401">
+      <c r="P102" s="398">
         <f t="shared" ref="P102:P133" si="32">ROUND(SUM(G102:O102),0) + S102</f>
         <v>752269.97</v>
       </c>
-      <c r="Q102" s="401"/>
+      <c r="Q102" s="398"/>
       <c r="R102" s="272">
         <f t="shared" ref="R102:R133" si="33">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>775086.97</v>
@@ -13057,11 +13084,11 @@
         <v>0</v>
       </c>
       <c r="O103" s="88"/>
-      <c r="P103" s="401">
+      <c r="P103" s="398">
         <f t="shared" si="32"/>
         <v>752350.98</v>
       </c>
-      <c r="Q103" s="401"/>
+      <c r="Q103" s="398"/>
       <c r="R103" s="272">
         <f t="shared" si="33"/>
         <v>775170.98</v>
@@ -13125,11 +13152,11 @@
         <v>0</v>
       </c>
       <c r="O104" s="88"/>
-      <c r="P104" s="401">
+      <c r="P104" s="398">
         <f t="shared" si="32"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="401"/>
+      <c r="Q104" s="398"/>
       <c r="R104" s="272">
         <f t="shared" si="33"/>
         <v>799418.99</v>
@@ -13195,11 +13222,11 @@
         <v>0</v>
       </c>
       <c r="O105" s="88"/>
-      <c r="P105" s="401">
+      <c r="P105" s="398">
         <f t="shared" si="32"/>
         <v>752351</v>
       </c>
-      <c r="Q105" s="401"/>
+      <c r="Q105" s="398"/>
       <c r="R105" s="272">
         <f t="shared" si="33"/>
         <v>775171</v>
@@ -13262,11 +13289,11 @@
         <v>0</v>
       </c>
       <c r="O106" s="88"/>
-      <c r="P106" s="401">
+      <c r="P106" s="398">
         <f t="shared" si="32"/>
         <v>752351.01</v>
       </c>
-      <c r="Q106" s="401"/>
+      <c r="Q106" s="398"/>
       <c r="R106" s="272">
         <f t="shared" si="33"/>
         <v>775171.01</v>
@@ -13329,11 +13356,11 @@
         <v>0</v>
       </c>
       <c r="O107" s="88"/>
-      <c r="P107" s="401">
+      <c r="P107" s="398">
         <f t="shared" si="32"/>
         <v>775118.02</v>
       </c>
-      <c r="Q107" s="401"/>
+      <c r="Q107" s="398"/>
       <c r="R107" s="272">
         <f t="shared" si="33"/>
         <v>798628.02</v>
@@ -13399,11 +13426,11 @@
         <v>0</v>
       </c>
       <c r="O108" s="88"/>
-      <c r="P108" s="401">
+      <c r="P108" s="398">
         <f t="shared" si="32"/>
         <v>728092.03</v>
       </c>
-      <c r="Q108" s="401"/>
+      <c r="Q108" s="398"/>
       <c r="R108" s="272">
         <f t="shared" si="33"/>
         <v>750176.03</v>
@@ -13467,11 +13494,11 @@
         <v>0</v>
       </c>
       <c r="O109" s="88"/>
-      <c r="P109" s="401">
+      <c r="P109" s="398">
         <f t="shared" si="32"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="401"/>
+      <c r="Q109" s="398"/>
       <c r="R109" s="272">
         <f t="shared" si="33"/>
         <v>791106.04</v>
@@ -13537,11 +13564,11 @@
         <v>0</v>
       </c>
       <c r="O110" s="88"/>
-      <c r="P110" s="401">
+      <c r="P110" s="398">
         <f t="shared" si="32"/>
         <v>705414.05</v>
       </c>
-      <c r="Q110" s="401"/>
+      <c r="Q110" s="398"/>
       <c r="R110" s="272">
         <f t="shared" si="33"/>
         <v>726810.05</v>
@@ -13610,11 +13637,11 @@
         <v>270455.26692913822</v>
       </c>
       <c r="O111" s="88"/>
-      <c r="P111" s="401">
+      <c r="P111" s="398">
         <f t="shared" si="32"/>
         <v>1769526.06</v>
       </c>
-      <c r="Q111" s="401"/>
+      <c r="Q111" s="398"/>
       <c r="R111" s="272">
         <f t="shared" si="33"/>
         <v>1823197.06</v>
@@ -13680,11 +13707,11 @@
         <v>0</v>
       </c>
       <c r="O112" s="88"/>
-      <c r="P112" s="401">
+      <c r="P112" s="398">
         <f t="shared" si="32"/>
         <v>766866.07</v>
       </c>
-      <c r="Q112" s="401"/>
+      <c r="Q112" s="398"/>
       <c r="R112" s="272">
         <f t="shared" si="33"/>
         <v>790126.07</v>
@@ -13750,11 +13777,11 @@
         <v>0</v>
       </c>
       <c r="O113" s="88"/>
-      <c r="P113" s="401">
+      <c r="P113" s="398">
         <f t="shared" si="32"/>
         <v>721059.08</v>
       </c>
-      <c r="Q113" s="401"/>
+      <c r="Q113" s="398"/>
       <c r="R113" s="272">
         <f t="shared" si="33"/>
         <v>742930.08</v>
@@ -13817,11 +13844,11 @@
         <v>0</v>
       </c>
       <c r="O114" s="88"/>
-      <c r="P114" s="401">
+      <c r="P114" s="398">
         <f t="shared" si="32"/>
         <v>1511441.09</v>
       </c>
-      <c r="Q114" s="401"/>
+      <c r="Q114" s="398"/>
       <c r="R114" s="272">
         <f t="shared" si="33"/>
         <v>1557284.09</v>
@@ -13887,11 +13914,11 @@
         <v>0</v>
       </c>
       <c r="O115" s="88"/>
-      <c r="P115" s="401">
+      <c r="P115" s="398">
         <f t="shared" si="32"/>
         <v>1524957.1</v>
       </c>
-      <c r="Q115" s="401"/>
+      <c r="Q115" s="398"/>
       <c r="R115" s="272">
         <f t="shared" si="33"/>
         <v>1571210.1</v>
@@ -13959,11 +13986,11 @@
         <v>0</v>
       </c>
       <c r="O116" s="88"/>
-      <c r="P116" s="401">
+      <c r="P116" s="398">
         <f t="shared" si="32"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="401"/>
+      <c r="Q116" s="398"/>
       <c r="R116" s="272">
         <f t="shared" si="33"/>
         <v>774482.11</v>
@@ -14026,11 +14053,11 @@
         <v>0</v>
       </c>
       <c r="O117" s="88"/>
-      <c r="P117" s="401">
+      <c r="P117" s="398">
         <f t="shared" si="32"/>
         <v>725114.12</v>
       </c>
-      <c r="Q117" s="401"/>
+      <c r="Q117" s="398"/>
       <c r="R117" s="272">
         <f t="shared" si="33"/>
         <v>747108.12</v>
@@ -14096,11 +14123,11 @@
         <v>0</v>
       </c>
       <c r="O118" s="88"/>
-      <c r="P118" s="401">
+      <c r="P118" s="398">
         <f t="shared" si="32"/>
         <v>744528.13</v>
       </c>
-      <c r="Q118" s="401"/>
+      <c r="Q118" s="398"/>
       <c r="R118" s="272">
         <f t="shared" si="33"/>
         <v>767111.13</v>
@@ -14163,11 +14190,11 @@
         <v>0</v>
       </c>
       <c r="O119" s="88"/>
-      <c r="P119" s="401">
+      <c r="P119" s="398">
         <f t="shared" si="32"/>
         <v>728882.14</v>
       </c>
-      <c r="Q119" s="401"/>
+      <c r="Q119" s="398"/>
       <c r="R119" s="272">
         <f t="shared" si="33"/>
         <v>750990.14</v>
@@ -14231,11 +14258,11 @@
         <v>0</v>
       </c>
       <c r="O120" s="88"/>
-      <c r="P120" s="401">
+      <c r="P120" s="398">
         <f t="shared" si="32"/>
         <v>849222.15</v>
       </c>
-      <c r="Q120" s="401"/>
+      <c r="Q120" s="398"/>
       <c r="R120" s="272">
         <f t="shared" si="33"/>
         <v>874980.15</v>
@@ -14302,11 +14329,11 @@
         <v>0</v>
       </c>
       <c r="O121" s="88"/>
-      <c r="P121" s="401">
+      <c r="P121" s="398">
         <f t="shared" si="32"/>
         <v>803799.16</v>
       </c>
-      <c r="Q121" s="401"/>
+      <c r="Q121" s="398"/>
       <c r="R121" s="272">
         <f t="shared" si="33"/>
         <v>828179.16</v>
@@ -14369,11 +14396,11 @@
         <v>0</v>
       </c>
       <c r="O122" s="88"/>
-      <c r="P122" s="401">
+      <c r="P122" s="398">
         <f t="shared" si="32"/>
         <v>854048.17</v>
       </c>
-      <c r="Q122" s="401"/>
+      <c r="Q122" s="398"/>
       <c r="R122" s="272">
         <f t="shared" si="33"/>
         <v>879952.17</v>
@@ -14440,11 +14467,11 @@
         <v>0</v>
       </c>
       <c r="O123" s="88"/>
-      <c r="P123" s="401">
+      <c r="P123" s="398">
         <f t="shared" si="32"/>
         <v>856559.18</v>
       </c>
-      <c r="Q123" s="401"/>
+      <c r="Q123" s="398"/>
       <c r="R123" s="272">
         <f t="shared" si="33"/>
         <v>882540.18</v>
@@ -14510,11 +14537,11 @@
         <v>0</v>
       </c>
       <c r="O124" s="88"/>
-      <c r="P124" s="401">
+      <c r="P124" s="398">
         <f t="shared" si="32"/>
         <v>827956.19</v>
       </c>
-      <c r="Q124" s="401"/>
+      <c r="Q124" s="398"/>
       <c r="R124" s="272">
         <f t="shared" si="33"/>
         <v>853069.19</v>
@@ -14581,11 +14608,11 @@
         <v>0</v>
       </c>
       <c r="O125" s="88"/>
-      <c r="P125" s="401">
+      <c r="P125" s="398">
         <f t="shared" si="32"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="401"/>
+      <c r="Q125" s="398"/>
       <c r="R125" s="272">
         <f t="shared" si="33"/>
         <v>782793.2</v>
@@ -14652,11 +14679,11 @@
         <v>0</v>
       </c>
       <c r="O126" s="88"/>
-      <c r="P126" s="401">
+      <c r="P126" s="398">
         <f t="shared" si="32"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="401"/>
+      <c r="Q126" s="398"/>
       <c r="R126" s="272">
         <f t="shared" si="33"/>
         <v>782793.21</v>
@@ -14722,11 +14749,11 @@
         <v>0</v>
       </c>
       <c r="O127" s="74"/>
-      <c r="P127" s="401">
+      <c r="P127" s="398">
         <f t="shared" si="32"/>
         <v>736705.22</v>
       </c>
-      <c r="Q127" s="401"/>
+      <c r="Q127" s="398"/>
       <c r="R127" s="272">
         <f t="shared" si="33"/>
         <v>759050.22</v>
@@ -14790,11 +14817,11 @@
         <v>0</v>
       </c>
       <c r="O128" s="88"/>
-      <c r="P128" s="401">
+      <c r="P128" s="398">
         <f t="shared" si="32"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="401"/>
+      <c r="Q128" s="398"/>
       <c r="R128" s="272">
         <f t="shared" si="33"/>
         <v>782793.23</v>
@@ -14860,11 +14887,11 @@
         <v>0</v>
       </c>
       <c r="O129" s="88"/>
-      <c r="P129" s="401">
+      <c r="P129" s="398">
         <f t="shared" si="32"/>
         <v>736705.24</v>
       </c>
-      <c r="Q129" s="401"/>
+      <c r="Q129" s="398"/>
       <c r="R129" s="272">
         <f t="shared" si="33"/>
         <v>759051.24</v>
@@ -14928,11 +14955,11 @@
         <v>0</v>
       </c>
       <c r="O130" s="88"/>
-      <c r="P130" s="401">
+      <c r="P130" s="398">
         <f t="shared" si="32"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="401"/>
+      <c r="Q130" s="398"/>
       <c r="R130" s="272">
         <f t="shared" si="33"/>
         <v>782793.25</v>
@@ -14999,11 +15026,11 @@
         <v>0</v>
       </c>
       <c r="O131" s="88"/>
-      <c r="P131" s="401">
+      <c r="P131" s="398">
         <f t="shared" si="32"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="401"/>
+      <c r="Q131" s="398"/>
       <c r="R131" s="272">
         <f t="shared" si="33"/>
         <v>782793.26</v>
@@ -15064,11 +15091,11 @@
         <v>0</v>
       </c>
       <c r="O132" s="88"/>
-      <c r="P132" s="401">
+      <c r="P132" s="398">
         <f t="shared" si="32"/>
         <v>1680082.27</v>
       </c>
-      <c r="Q132" s="401"/>
+      <c r="Q132" s="398"/>
       <c r="R132" s="272">
         <f t="shared" si="33"/>
         <v>1731040.27</v>
@@ -15135,11 +15162,11 @@
         <v>339029.8362611382</v>
       </c>
       <c r="O133" s="88"/>
-      <c r="P133" s="401">
+      <c r="P133" s="398">
         <f t="shared" si="32"/>
         <v>9465986.2799999993</v>
       </c>
-      <c r="Q133" s="401"/>
+      <c r="Q133" s="398"/>
       <c r="R133" s="272">
         <f t="shared" si="33"/>
         <v>9753091.2799999993</v>
@@ -15202,11 +15229,11 @@
         <v>0</v>
       </c>
       <c r="O134" s="88"/>
-      <c r="P134" s="401">
+      <c r="P134" s="398">
         <f t="shared" ref="P134:P144" si="39">ROUND(SUM(G134:O134),0) + S134</f>
         <v>854048.29</v>
       </c>
-      <c r="Q134" s="401"/>
+      <c r="Q134" s="398"/>
       <c r="R134" s="272">
         <f t="shared" ref="R134:R144" si="40">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>879953.29</v>
@@ -15272,11 +15299,11 @@
         <v>0</v>
       </c>
       <c r="O135" s="88"/>
-      <c r="P135" s="401">
+      <c r="P135" s="398">
         <f t="shared" si="39"/>
         <v>847809.3</v>
       </c>
-      <c r="Q135" s="401"/>
+      <c r="Q135" s="398"/>
       <c r="R135" s="272">
         <f t="shared" si="40"/>
         <v>873524.3</v>
@@ -15343,11 +15370,11 @@
         <v>0</v>
       </c>
       <c r="O136" s="88"/>
-      <c r="P136" s="401">
+      <c r="P136" s="398">
         <f t="shared" si="39"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="401"/>
+      <c r="Q136" s="398"/>
       <c r="R136" s="272">
         <f t="shared" si="40"/>
         <v>907478.31</v>
@@ -15413,11 +15440,11 @@
         <v>0</v>
       </c>
       <c r="O137" s="88"/>
-      <c r="P137" s="401">
+      <c r="P137" s="398">
         <f t="shared" si="39"/>
         <v>846226.32</v>
       </c>
-      <c r="Q137" s="401"/>
+      <c r="Q137" s="398"/>
       <c r="R137" s="272">
         <f t="shared" si="40"/>
         <v>871893.32</v>
@@ -15484,11 +15511,11 @@
         <v>0</v>
       </c>
       <c r="O138" s="88"/>
-      <c r="P138" s="401">
+      <c r="P138" s="398">
         <f t="shared" si="39"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="401"/>
+      <c r="Q138" s="398"/>
       <c r="R138" s="272">
         <f t="shared" si="40"/>
         <v>932415.33</v>
@@ -15554,11 +15581,11 @@
         <v>0</v>
       </c>
       <c r="O139" s="88"/>
-      <c r="P139" s="401">
+      <c r="P139" s="398">
         <f t="shared" si="39"/>
         <v>791466.34</v>
       </c>
-      <c r="Q139" s="401"/>
+      <c r="Q139" s="398"/>
       <c r="R139" s="272">
         <f t="shared" si="40"/>
         <v>815473.34</v>
@@ -15624,11 +15651,11 @@
         <v>0</v>
       </c>
       <c r="O140" s="88"/>
-      <c r="P140" s="401">
+      <c r="P140" s="398">
         <f t="shared" si="39"/>
         <v>854048.35</v>
       </c>
-      <c r="Q140" s="401"/>
+      <c r="Q140" s="398"/>
       <c r="R140" s="272">
         <f t="shared" si="40"/>
         <v>879953.35</v>
@@ -15692,11 +15719,11 @@
         <v>0</v>
       </c>
       <c r="O141" s="88"/>
-      <c r="P141" s="401">
+      <c r="P141" s="398">
         <f t="shared" si="39"/>
         <v>3751757.36</v>
       </c>
-      <c r="Q141" s="401"/>
+      <c r="Q141" s="398"/>
       <c r="R141" s="272">
         <f t="shared" si="40"/>
         <v>3865549.36</v>
@@ -15762,11 +15789,11 @@
         <v>0</v>
       </c>
       <c r="O142" s="88"/>
-      <c r="P142" s="401">
+      <c r="P142" s="398">
         <f t="shared" si="39"/>
         <v>799288.37</v>
       </c>
-      <c r="Q142" s="401"/>
+      <c r="Q142" s="398"/>
       <c r="R142" s="272">
         <f t="shared" si="40"/>
         <v>823532.37</v>
@@ -15829,11 +15856,11 @@
         <v>0</v>
       </c>
       <c r="O143" s="88"/>
-      <c r="P143" s="401">
+      <c r="P143" s="398">
         <f t="shared" si="39"/>
         <v>885340.38</v>
       </c>
-      <c r="Q143" s="401"/>
+      <c r="Q143" s="398"/>
       <c r="R143" s="272">
         <f t="shared" si="40"/>
         <v>912194.38</v>
@@ -15899,11 +15926,11 @@
         <v>0</v>
       </c>
       <c r="O144" s="88"/>
-      <c r="P144" s="401">
+      <c r="P144" s="398">
         <f t="shared" si="39"/>
         <v>880691.39</v>
       </c>
-      <c r="Q144" s="401"/>
+      <c r="Q144" s="398"/>
       <c r="R144" s="272">
         <f t="shared" si="40"/>
         <v>907404.39</v>
@@ -15943,8 +15970,8 @@
       <c r="M145" s="74"/>
       <c r="N145" s="74"/>
       <c r="O145" s="88"/>
-      <c r="P145" s="401"/>
-      <c r="Q145" s="401"/>
+      <c r="P145" s="398"/>
+      <c r="Q145" s="398"/>
       <c r="R145" s="273"/>
       <c r="S145" s="13">
         <f t="shared" si="41"/>
@@ -15978,8 +16005,8 @@
       <c r="M146" s="74"/>
       <c r="N146" s="74"/>
       <c r="O146" s="88"/>
-      <c r="P146" s="401"/>
-      <c r="Q146" s="401"/>
+      <c r="P146" s="398"/>
+      <c r="Q146" s="398"/>
       <c r="R146" s="273"/>
       <c r="S146" s="13">
         <f t="shared" si="41"/>
@@ -16006,8 +16033,8 @@
       <c r="M147" s="74"/>
       <c r="N147" s="74"/>
       <c r="O147" s="88"/>
-      <c r="P147" s="401"/>
-      <c r="Q147" s="401"/>
+      <c r="P147" s="398"/>
+      <c r="Q147" s="398"/>
       <c r="R147" s="273"/>
       <c r="S147" s="13">
         <f t="shared" si="41"/>
@@ -16034,8 +16061,8 @@
       <c r="M148" s="74"/>
       <c r="N148" s="74"/>
       <c r="O148" s="88"/>
-      <c r="P148" s="401"/>
-      <c r="Q148" s="401"/>
+      <c r="P148" s="398"/>
+      <c r="Q148" s="398"/>
       <c r="R148" s="273"/>
       <c r="S148" s="13">
         <f t="shared" si="41"/>
@@ -16095,11 +16122,11 @@
         <v>246252.47775313823</v>
       </c>
       <c r="O149" s="88"/>
-      <c r="P149" s="401">
+      <c r="P149" s="398">
         <f t="shared" ref="P149:P158" si="49">ROUND(SUM(G149:O149),0) + S149</f>
         <v>882923.46</v>
       </c>
-      <c r="Q149" s="401"/>
+      <c r="Q149" s="398"/>
       <c r="R149" s="272">
         <f t="shared" ref="R149:R158" si="50">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>909704.46</v>
@@ -16160,11 +16187,11 @@
         <v>0</v>
       </c>
       <c r="O150" s="88"/>
-      <c r="P150" s="401">
+      <c r="P150" s="398">
         <f t="shared" si="49"/>
         <v>707760.55</v>
       </c>
-      <c r="Q150" s="401"/>
+      <c r="Q150" s="398"/>
       <c r="R150" s="272">
         <f t="shared" si="50"/>
         <v>729228.55</v>
@@ -16231,11 +16258,11 @@
         <v>0</v>
       </c>
       <c r="O151" s="74"/>
-      <c r="P151" s="401">
+      <c r="P151" s="398">
         <f t="shared" si="49"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="401"/>
+      <c r="Q151" s="398"/>
       <c r="R151" s="272">
         <f t="shared" si="50"/>
         <v>782794.58</v>
@@ -16299,11 +16326,11 @@
         <v>0</v>
       </c>
       <c r="O152" s="74"/>
-      <c r="P152" s="401">
+      <c r="P152" s="398">
         <f t="shared" si="49"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="401"/>
+      <c r="Q152" s="398"/>
       <c r="R152" s="272">
         <f t="shared" si="50"/>
         <v>782794.59</v>
@@ -16367,11 +16394,11 @@
         <v>0</v>
       </c>
       <c r="O153" s="74"/>
-      <c r="P153" s="401">
+      <c r="P153" s="398">
         <f t="shared" si="49"/>
         <v>759750.63</v>
       </c>
-      <c r="Q153" s="401"/>
+      <c r="Q153" s="398"/>
       <c r="R153" s="272">
         <f t="shared" si="50"/>
         <v>782795.63</v>
@@ -16435,11 +16462,11 @@
         <v>0</v>
       </c>
       <c r="O154" s="74"/>
-      <c r="P154" s="401">
+      <c r="P154" s="398">
         <f t="shared" si="49"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="401"/>
+      <c r="Q154" s="398"/>
       <c r="R154" s="272">
         <f t="shared" si="50"/>
         <v>766170.68</v>
@@ -16502,11 +16529,11 @@
         <v>0</v>
       </c>
       <c r="O155" s="74"/>
-      <c r="P155" s="401">
+      <c r="P155" s="398">
         <f t="shared" si="49"/>
         <v>736704.73</v>
       </c>
-      <c r="Q155" s="401"/>
+      <c r="Q155" s="398"/>
       <c r="R155" s="272">
         <f t="shared" si="50"/>
         <v>759050.73</v>
@@ -16572,11 +16599,11 @@
         <v>0</v>
       </c>
       <c r="O156" s="74"/>
-      <c r="P156" s="401">
+      <c r="P156" s="398">
         <f t="shared" si="49"/>
         <v>736704.75</v>
       </c>
-      <c r="Q156" s="401"/>
+      <c r="Q156" s="398"/>
       <c r="R156" s="272">
         <f t="shared" si="50"/>
         <v>759050.75</v>
@@ -16643,11 +16670,11 @@
         <v>0</v>
       </c>
       <c r="O157" s="74"/>
-      <c r="P157" s="401">
+      <c r="P157" s="398">
         <f t="shared" si="49"/>
         <v>759750.76</v>
       </c>
-      <c r="Q157" s="401"/>
+      <c r="Q157" s="398"/>
       <c r="R157" s="272">
         <f t="shared" si="50"/>
         <v>782795.76</v>
@@ -16711,11 +16738,11 @@
         <v>0</v>
       </c>
       <c r="O158" s="74"/>
-      <c r="P158" s="401">
+      <c r="P158" s="398">
         <f t="shared" si="49"/>
         <v>783953.04</v>
       </c>
-      <c r="Q158" s="401"/>
+      <c r="Q158" s="398"/>
       <c r="R158" s="272">
         <f t="shared" si="50"/>
         <v>807732.04</v>
@@ -16748,8 +16775,8 @@
       <c r="M159" s="22"/>
       <c r="N159" s="22"/>
       <c r="O159" s="74"/>
-      <c r="P159" s="426"/>
-      <c r="Q159" s="426"/>
+      <c r="P159" s="403"/>
+      <c r="Q159" s="403"/>
       <c r="R159" s="183"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -16770,8 +16797,8 @@
       <c r="M160" s="194"/>
       <c r="N160" s="194"/>
       <c r="O160" s="269"/>
-      <c r="P160" s="427"/>
-      <c r="Q160" s="427"/>
+      <c r="P160" s="404"/>
+      <c r="Q160" s="404"/>
       <c r="R160" s="186"/>
       <c r="S160" s="13"/>
       <c r="T160" s="195"/>
@@ -16825,264 +16852,198 @@
         <f t="shared" si="54"/>
         <v>890374.81218400015</v>
       </c>
-      <c r="P161" s="424">
+      <c r="P161" s="401">
         <f>SUM(P6:P160)</f>
         <v>169388305.07000002</v>
       </c>
-      <c r="Q161" s="425"/>
+      <c r="Q161" s="402"/>
       <c r="R161" s="187">
         <f>SUM(R6:R160)</f>
         <v>174525973.07000002</v>
       </c>
-      <c r="S161" s="424"/>
-      <c r="T161" s="425"/>
+      <c r="S161" s="401"/>
+      <c r="T161" s="402"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B162" s="422" t="s">
+      <c r="B162" s="399" t="s">
         <v>324</v>
       </c>
-      <c r="C162" s="422"/>
-      <c r="D162" s="422"/>
-      <c r="E162" s="422"/>
-      <c r="F162" s="422"/>
-      <c r="G162" s="422"/>
-      <c r="H162" s="422"/>
-      <c r="I162" s="422"/>
-      <c r="J162" s="422"/>
-      <c r="K162" s="422"/>
-      <c r="L162" s="422"/>
-      <c r="M162" s="422"/>
-      <c r="N162" s="422"/>
-      <c r="O162" s="422"/>
-      <c r="P162" s="422"/>
-      <c r="Q162" s="422"/>
-      <c r="R162" s="422"/>
-      <c r="S162" s="422"/>
-      <c r="T162" s="422"/>
+      <c r="C162" s="399"/>
+      <c r="D162" s="399"/>
+      <c r="E162" s="399"/>
+      <c r="F162" s="399"/>
+      <c r="G162" s="399"/>
+      <c r="H162" s="399"/>
+      <c r="I162" s="399"/>
+      <c r="J162" s="399"/>
+      <c r="K162" s="399"/>
+      <c r="L162" s="399"/>
+      <c r="M162" s="399"/>
+      <c r="N162" s="399"/>
+      <c r="O162" s="399"/>
+      <c r="P162" s="399"/>
+      <c r="Q162" s="399"/>
+      <c r="R162" s="399"/>
+      <c r="S162" s="399"/>
+      <c r="T162" s="399"/>
     </row>
     <row r="163" spans="1:20" ht="49.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="423"/>
-      <c r="C163" s="423"/>
-      <c r="D163" s="423"/>
-      <c r="E163" s="423"/>
-      <c r="F163" s="423"/>
-      <c r="G163" s="423"/>
-      <c r="H163" s="423"/>
-      <c r="I163" s="423"/>
-      <c r="J163" s="423"/>
-      <c r="K163" s="423"/>
-      <c r="L163" s="423"/>
-      <c r="M163" s="423"/>
-      <c r="N163" s="423"/>
-      <c r="O163" s="423"/>
-      <c r="P163" s="423"/>
-      <c r="Q163" s="423"/>
-      <c r="R163" s="423"/>
-      <c r="S163" s="423"/>
-      <c r="T163" s="423"/>
+      <c r="B163" s="400"/>
+      <c r="C163" s="400"/>
+      <c r="D163" s="400"/>
+      <c r="E163" s="400"/>
+      <c r="F163" s="400"/>
+      <c r="G163" s="400"/>
+      <c r="H163" s="400"/>
+      <c r="I163" s="400"/>
+      <c r="J163" s="400"/>
+      <c r="K163" s="400"/>
+      <c r="L163" s="400"/>
+      <c r="M163" s="400"/>
+      <c r="N163" s="400"/>
+      <c r="O163" s="400"/>
+      <c r="P163" s="400"/>
+      <c r="Q163" s="400"/>
+      <c r="R163" s="400"/>
+      <c r="S163" s="400"/>
+      <c r="T163" s="400"/>
     </row>
     <row r="164" spans="1:20" ht="13.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B164" s="423" t="s">
+      <c r="B164" s="400" t="s">
         <v>262</v>
       </c>
-      <c r="C164" s="423"/>
-      <c r="D164" s="423"/>
-      <c r="E164" s="423"/>
-      <c r="F164" s="423"/>
-      <c r="G164" s="423"/>
-      <c r="H164" s="423"/>
-      <c r="I164" s="423"/>
-      <c r="J164" s="423"/>
-      <c r="K164" s="423"/>
-      <c r="L164" s="423"/>
-      <c r="M164" s="423"/>
-      <c r="N164" s="423"/>
-      <c r="O164" s="423"/>
-      <c r="P164" s="423"/>
-      <c r="Q164" s="423"/>
-      <c r="R164" s="423"/>
-      <c r="S164" s="423"/>
-      <c r="T164" s="423"/>
+      <c r="C164" s="400"/>
+      <c r="D164" s="400"/>
+      <c r="E164" s="400"/>
+      <c r="F164" s="400"/>
+      <c r="G164" s="400"/>
+      <c r="H164" s="400"/>
+      <c r="I164" s="400"/>
+      <c r="J164" s="400"/>
+      <c r="K164" s="400"/>
+      <c r="L164" s="400"/>
+      <c r="M164" s="400"/>
+      <c r="N164" s="400"/>
+      <c r="O164" s="400"/>
+      <c r="P164" s="400"/>
+      <c r="Q164" s="400"/>
+      <c r="R164" s="400"/>
+      <c r="S164" s="400"/>
+      <c r="T164" s="400"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="423"/>
-      <c r="C165" s="423"/>
-      <c r="D165" s="423"/>
-      <c r="E165" s="423"/>
-      <c r="F165" s="423"/>
-      <c r="G165" s="423"/>
-      <c r="H165" s="423"/>
-      <c r="I165" s="423"/>
-      <c r="J165" s="423"/>
-      <c r="K165" s="423"/>
-      <c r="L165" s="423"/>
-      <c r="M165" s="423"/>
-      <c r="N165" s="423"/>
-      <c r="O165" s="423"/>
-      <c r="P165" s="423"/>
-      <c r="Q165" s="423"/>
-      <c r="R165" s="423"/>
-      <c r="S165" s="423"/>
-      <c r="T165" s="423"/>
+      <c r="B165" s="400"/>
+      <c r="C165" s="400"/>
+      <c r="D165" s="400"/>
+      <c r="E165" s="400"/>
+      <c r="F165" s="400"/>
+      <c r="G165" s="400"/>
+      <c r="H165" s="400"/>
+      <c r="I165" s="400"/>
+      <c r="J165" s="400"/>
+      <c r="K165" s="400"/>
+      <c r="L165" s="400"/>
+      <c r="M165" s="400"/>
+      <c r="N165" s="400"/>
+      <c r="O165" s="400"/>
+      <c r="P165" s="400"/>
+      <c r="Q165" s="400"/>
+      <c r="R165" s="400"/>
+      <c r="S165" s="400"/>
+      <c r="T165" s="400"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B166" s="423"/>
-      <c r="C166" s="423"/>
-      <c r="D166" s="423"/>
-      <c r="E166" s="423"/>
-      <c r="F166" s="423"/>
-      <c r="G166" s="423"/>
-      <c r="H166" s="423"/>
-      <c r="I166" s="423"/>
-      <c r="J166" s="423"/>
-      <c r="K166" s="423"/>
-      <c r="L166" s="423"/>
-      <c r="M166" s="423"/>
-      <c r="N166" s="423"/>
-      <c r="O166" s="423"/>
-      <c r="P166" s="423"/>
-      <c r="Q166" s="423"/>
-      <c r="R166" s="423"/>
-      <c r="S166" s="423"/>
-      <c r="T166" s="423"/>
+      <c r="B166" s="400"/>
+      <c r="C166" s="400"/>
+      <c r="D166" s="400"/>
+      <c r="E166" s="400"/>
+      <c r="F166" s="400"/>
+      <c r="G166" s="400"/>
+      <c r="H166" s="400"/>
+      <c r="I166" s="400"/>
+      <c r="J166" s="400"/>
+      <c r="K166" s="400"/>
+      <c r="L166" s="400"/>
+      <c r="M166" s="400"/>
+      <c r="N166" s="400"/>
+      <c r="O166" s="400"/>
+      <c r="P166" s="400"/>
+      <c r="Q166" s="400"/>
+      <c r="R166" s="400"/>
+      <c r="S166" s="400"/>
+      <c r="T166" s="400"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="423"/>
-      <c r="C167" s="423"/>
-      <c r="D167" s="423"/>
-      <c r="E167" s="423"/>
-      <c r="F167" s="423"/>
-      <c r="G167" s="423"/>
-      <c r="H167" s="423"/>
-      <c r="I167" s="423"/>
-      <c r="J167" s="423"/>
-      <c r="K167" s="423"/>
-      <c r="L167" s="423"/>
-      <c r="M167" s="423"/>
-      <c r="N167" s="423"/>
-      <c r="O167" s="423"/>
-      <c r="P167" s="423"/>
-      <c r="Q167" s="423"/>
-      <c r="R167" s="423"/>
-      <c r="S167" s="423"/>
-      <c r="T167" s="423"/>
+      <c r="B167" s="400"/>
+      <c r="C167" s="400"/>
+      <c r="D167" s="400"/>
+      <c r="E167" s="400"/>
+      <c r="F167" s="400"/>
+      <c r="G167" s="400"/>
+      <c r="H167" s="400"/>
+      <c r="I167" s="400"/>
+      <c r="J167" s="400"/>
+      <c r="K167" s="400"/>
+      <c r="L167" s="400"/>
+      <c r="M167" s="400"/>
+      <c r="N167" s="400"/>
+      <c r="O167" s="400"/>
+      <c r="P167" s="400"/>
+      <c r="Q167" s="400"/>
+      <c r="R167" s="400"/>
+      <c r="S167" s="400"/>
+      <c r="T167" s="400"/>
     </row>
   </sheetData>
   <mergeCells count="186">
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="P28:Q28"/>
     <mergeCell ref="P29:Q29"/>
@@ -17107,54 +17068,120 @@
     <mergeCell ref="P33:Q33"/>
     <mergeCell ref="P34:Q34"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -17169,7 +17196,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D69DBA-AA88-413A-80A7-A9BAAE7F2C32}">
-  <dimension ref="C2:N270"/>
+  <dimension ref="C2:N296"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="10.88671875" customWidth="1"/>
@@ -20105,38 +20132,333 @@
       <c r="I270" s="437"/>
       <c r="J270" s="438"/>
     </row>
+    <row r="272" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="273" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C273" s="350" t="s">
+        <v>159</v>
+      </c>
+      <c r="D273" s="351">
+        <f>D264+1</f>
+        <v>31</v>
+      </c>
+      <c r="E273" s="64"/>
+      <c r="F273" s="64"/>
+      <c r="G273" s="64"/>
+      <c r="H273" s="64"/>
+      <c r="I273" s="64"/>
+      <c r="J273" s="66"/>
+    </row>
+    <row r="274" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C274" s="352" t="s">
+        <v>160</v>
+      </c>
+      <c r="D274" s="353"/>
+      <c r="E274" s="220">
+        <v>45945</v>
+      </c>
+      <c r="F274" s="36"/>
+      <c r="G274" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H274" s="90"/>
+      <c r="I274" s="67"/>
+      <c r="J274" s="68"/>
+    </row>
+    <row r="275" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C275" s="352" t="s">
+        <v>161</v>
+      </c>
+      <c r="D275" s="353" t="s">
+        <v>162</v>
+      </c>
+      <c r="E275" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F275" s="36"/>
+      <c r="G275" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H275" s="428">
+        <v>67</v>
+      </c>
+      <c r="I275" s="428"/>
+      <c r="J275" s="429"/>
+    </row>
+    <row r="276" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C276" s="352" t="s">
+        <v>164</v>
+      </c>
+      <c r="D276" s="353"/>
+      <c r="E276" s="36"/>
+      <c r="F276" s="36"/>
+      <c r="G276" s="36"/>
+      <c r="H276" s="36"/>
+      <c r="I276" s="36"/>
+      <c r="J276" s="69"/>
+    </row>
+    <row r="277" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C277" s="430" t="s">
+        <v>519</v>
+      </c>
+      <c r="D277" s="431"/>
+      <c r="E277" s="431"/>
+      <c r="F277" s="431"/>
+      <c r="G277" s="431"/>
+      <c r="H277" s="431"/>
+      <c r="I277" s="431"/>
+      <c r="J277" s="432"/>
+    </row>
+    <row r="278" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C278" s="433"/>
+      <c r="D278" s="434"/>
+      <c r="E278" s="434"/>
+      <c r="F278" s="434"/>
+      <c r="G278" s="434"/>
+      <c r="H278" s="434"/>
+      <c r="I278" s="434"/>
+      <c r="J278" s="435"/>
+    </row>
+    <row r="279" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C279" s="436"/>
+      <c r="D279" s="437"/>
+      <c r="E279" s="437"/>
+      <c r="F279" s="437"/>
+      <c r="G279" s="437"/>
+      <c r="H279" s="437"/>
+      <c r="I279" s="437"/>
+      <c r="J279" s="438"/>
+    </row>
+    <row r="280" spans="3:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" spans="3:10" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="282" spans="3:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C282" s="350" t="s">
+        <v>159</v>
+      </c>
+      <c r="D282" s="351">
+        <f>D273+1</f>
+        <v>32</v>
+      </c>
+      <c r="E282" s="64"/>
+      <c r="F282" s="64"/>
+      <c r="G282" s="64"/>
+      <c r="H282" s="64"/>
+      <c r="I282" s="64"/>
+      <c r="J282" s="66"/>
+    </row>
+    <row r="283" spans="3:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C283" s="352" t="s">
+        <v>160</v>
+      </c>
+      <c r="D283" s="353"/>
+      <c r="E283" s="220">
+        <v>45945</v>
+      </c>
+      <c r="F283" s="36"/>
+      <c r="G283" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H283" s="90"/>
+      <c r="I283" s="67"/>
+      <c r="J283" s="68"/>
+    </row>
+    <row r="284" spans="3:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C284" s="352" t="s">
+        <v>161</v>
+      </c>
+      <c r="D284" s="353" t="s">
+        <v>162</v>
+      </c>
+      <c r="E284" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F284" s="36"/>
+      <c r="G284" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H284" s="428">
+        <v>12</v>
+      </c>
+      <c r="I284" s="428"/>
+      <c r="J284" s="429"/>
+    </row>
+    <row r="285" spans="3:10" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C285" s="352" t="s">
+        <v>164</v>
+      </c>
+      <c r="D285" s="353"/>
+      <c r="E285" s="36"/>
+      <c r="F285" s="36"/>
+      <c r="G285" s="36"/>
+      <c r="H285" s="36"/>
+      <c r="I285" s="36"/>
+      <c r="J285" s="69"/>
+    </row>
+    <row r="286" spans="3:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C286" s="430" t="s">
+        <v>522</v>
+      </c>
+      <c r="D286" s="431"/>
+      <c r="E286" s="431"/>
+      <c r="F286" s="431"/>
+      <c r="G286" s="431"/>
+      <c r="H286" s="431"/>
+      <c r="I286" s="431"/>
+      <c r="J286" s="432"/>
+    </row>
+    <row r="287" spans="3:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C287" s="433"/>
+      <c r="D287" s="434"/>
+      <c r="E287" s="434"/>
+      <c r="F287" s="434"/>
+      <c r="G287" s="434"/>
+      <c r="H287" s="434"/>
+      <c r="I287" s="434"/>
+      <c r="J287" s="435"/>
+    </row>
+    <row r="288" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C288" s="436"/>
+      <c r="D288" s="437"/>
+      <c r="E288" s="437"/>
+      <c r="F288" s="437"/>
+      <c r="G288" s="437"/>
+      <c r="H288" s="437"/>
+      <c r="I288" s="437"/>
+      <c r="J288" s="438"/>
+    </row>
+    <row r="289" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C289" s="455"/>
+      <c r="D289" s="455"/>
+      <c r="E289" s="455"/>
+      <c r="F289" s="455"/>
+      <c r="G289" s="455"/>
+      <c r="H289" s="455"/>
+      <c r="I289" s="455"/>
+      <c r="J289" s="455"/>
+    </row>
+    <row r="290" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="K290" s="453" t="s">
+        <v>521</v>
+      </c>
+      <c r="L290" s="454"/>
+      <c r="M290" s="454"/>
+    </row>
+    <row r="291" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C291" s="352" t="s">
+        <v>160</v>
+      </c>
+      <c r="D291" s="353"/>
+      <c r="E291" s="220">
+        <v>45945</v>
+      </c>
+      <c r="F291" s="36"/>
+      <c r="G291" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H291" s="90"/>
+      <c r="I291" s="67"/>
+      <c r="J291" s="68"/>
+      <c r="K291" s="453"/>
+      <c r="L291" s="454"/>
+      <c r="M291" s="454"/>
+    </row>
+    <row r="292" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C292" s="352" t="s">
+        <v>161</v>
+      </c>
+      <c r="D292" s="353" t="s">
+        <v>162</v>
+      </c>
+      <c r="E292" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F292" s="36"/>
+      <c r="G292" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="H292" s="428">
+        <v>17</v>
+      </c>
+      <c r="I292" s="428"/>
+      <c r="J292" s="429"/>
+      <c r="K292" s="453"/>
+      <c r="L292" s="454"/>
+      <c r="M292" s="454"/>
+    </row>
+    <row r="293" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C293" s="352" t="s">
+        <v>164</v>
+      </c>
+      <c r="D293" s="353"/>
+      <c r="E293" s="36"/>
+      <c r="F293" s="36"/>
+      <c r="G293" s="36"/>
+      <c r="H293" s="36"/>
+      <c r="I293" s="36"/>
+      <c r="J293" s="69"/>
+      <c r="K293" s="453"/>
+      <c r="L293" s="454"/>
+      <c r="M293" s="454"/>
+    </row>
+    <row r="294" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C294" s="430" t="s">
+        <v>520</v>
+      </c>
+      <c r="D294" s="431"/>
+      <c r="E294" s="431"/>
+      <c r="F294" s="431"/>
+      <c r="G294" s="431"/>
+      <c r="H294" s="431"/>
+      <c r="I294" s="431"/>
+      <c r="J294" s="432"/>
+      <c r="K294" s="453"/>
+      <c r="L294" s="454"/>
+      <c r="M294" s="454"/>
+    </row>
+    <row r="295" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C295" s="433"/>
+      <c r="D295" s="434"/>
+      <c r="E295" s="434"/>
+      <c r="F295" s="434"/>
+      <c r="G295" s="434"/>
+      <c r="H295" s="434"/>
+      <c r="I295" s="434"/>
+      <c r="J295" s="435"/>
+      <c r="K295" s="453"/>
+      <c r="L295" s="454"/>
+      <c r="M295" s="454"/>
+    </row>
+    <row r="296" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C296" s="436"/>
+      <c r="D296" s="437"/>
+      <c r="E296" s="437"/>
+      <c r="F296" s="437"/>
+      <c r="G296" s="437"/>
+      <c r="H296" s="437"/>
+      <c r="I296" s="437"/>
+      <c r="J296" s="438"/>
+    </row>
   </sheetData>
-  <mergeCells count="59">
-    <mergeCell ref="H266:J266"/>
-    <mergeCell ref="C268:J270"/>
-    <mergeCell ref="H239:J239"/>
-    <mergeCell ref="C241:J243"/>
-    <mergeCell ref="C142:J144"/>
-    <mergeCell ref="H122:J122"/>
-    <mergeCell ref="C124:J126"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="C133:J135"/>
-    <mergeCell ref="H140:J140"/>
-    <mergeCell ref="H149:J149"/>
-    <mergeCell ref="C151:J153"/>
-    <mergeCell ref="H158:J158"/>
-    <mergeCell ref="C160:J162"/>
-    <mergeCell ref="H167:J167"/>
-    <mergeCell ref="C169:J171"/>
-    <mergeCell ref="H176:J176"/>
-    <mergeCell ref="C178:J180"/>
-    <mergeCell ref="C115:J117"/>
-    <mergeCell ref="H95:J95"/>
-    <mergeCell ref="C97:J99"/>
-    <mergeCell ref="H104:J104"/>
-    <mergeCell ref="C106:J108"/>
-    <mergeCell ref="H113:J113"/>
-    <mergeCell ref="C88:J90"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="C70:J72"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="C79:J81"/>
-    <mergeCell ref="H86:J86"/>
+  <mergeCells count="66">
+    <mergeCell ref="H275:J275"/>
+    <mergeCell ref="C277:J279"/>
+    <mergeCell ref="H292:J292"/>
+    <mergeCell ref="C294:J296"/>
+    <mergeCell ref="K290:M295"/>
+    <mergeCell ref="H284:J284"/>
+    <mergeCell ref="C286:J288"/>
+    <mergeCell ref="C259:J261"/>
+    <mergeCell ref="H184:J184"/>
+    <mergeCell ref="C186:J188"/>
+    <mergeCell ref="H230:J230"/>
+    <mergeCell ref="C232:J234"/>
+    <mergeCell ref="H193:J193"/>
+    <mergeCell ref="C195:J197"/>
+    <mergeCell ref="H221:J221"/>
+    <mergeCell ref="C223:J225"/>
+    <mergeCell ref="H212:J212"/>
+    <mergeCell ref="C214:J216"/>
+    <mergeCell ref="H202:J202"/>
+    <mergeCell ref="C204:J206"/>
     <mergeCell ref="H59:J59"/>
     <mergeCell ref="C61:J63"/>
     <mergeCell ref="C52:J54"/>
@@ -20150,22 +20472,39 @@
     <mergeCell ref="H41:J41"/>
     <mergeCell ref="C43:J45"/>
     <mergeCell ref="H32:J32"/>
+    <mergeCell ref="C88:J90"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="C70:J72"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="C79:J81"/>
+    <mergeCell ref="H86:J86"/>
+    <mergeCell ref="C115:J117"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="C97:J99"/>
+    <mergeCell ref="H104:J104"/>
+    <mergeCell ref="C106:J108"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="C124:J126"/>
+    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="C133:J135"/>
+    <mergeCell ref="H140:J140"/>
+    <mergeCell ref="H266:J266"/>
+    <mergeCell ref="C268:J270"/>
+    <mergeCell ref="H239:J239"/>
+    <mergeCell ref="C241:J243"/>
+    <mergeCell ref="C142:J144"/>
+    <mergeCell ref="H149:J149"/>
+    <mergeCell ref="C151:J153"/>
+    <mergeCell ref="H158:J158"/>
+    <mergeCell ref="C160:J162"/>
+    <mergeCell ref="H167:J167"/>
+    <mergeCell ref="C169:J171"/>
+    <mergeCell ref="H176:J176"/>
+    <mergeCell ref="C178:J180"/>
     <mergeCell ref="H248:J248"/>
     <mergeCell ref="C250:J252"/>
     <mergeCell ref="H257:J257"/>
-    <mergeCell ref="C259:J261"/>
-    <mergeCell ref="H184:J184"/>
-    <mergeCell ref="C186:J188"/>
-    <mergeCell ref="H230:J230"/>
-    <mergeCell ref="C232:J234"/>
-    <mergeCell ref="H193:J193"/>
-    <mergeCell ref="C195:J197"/>
-    <mergeCell ref="H221:J221"/>
-    <mergeCell ref="C223:J225"/>
-    <mergeCell ref="H212:J212"/>
-    <mergeCell ref="C214:J216"/>
-    <mergeCell ref="H202:J202"/>
-    <mergeCell ref="C204:J206"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
